--- a/MoneyKeel/documents/other/moneykeel_calc_plan_launch-answer-list_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_launch-answer-list_v01.xlsx
@@ -1759,7 +1759,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>DEC-0476</t>
+          <t>DEC-0469</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>DEC-0477</t>
+          <t>DEC-0470</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>DEC-0482</t>
+          <t>DEC-0475</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>DEC-0483</t>
+          <t>DEC-0476</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>DEC-0485</t>
+          <t>DEC-0478</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>DEC-0486</t>
+          <t>DEC-0479</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>DEC-0490</t>
+          <t>DEC-0483</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>DEC-0504</t>
+          <t>DEC-0497</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>DEC-0517</t>
+          <t>DEC-0510</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>DEC-0510</t>
+          <t>DEC-0503</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>DEC-0519</t>
+          <t>DEC-0512</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>DEC-0476</t>
+          <t>DEC-0469</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>DEC-0477</t>
+          <t>DEC-0470</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>DEC-0482</t>
+          <t>DEC-0475</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>DEC-0483</t>
+          <t>DEC-0476</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>DEC-0485</t>
+          <t>DEC-0478</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>DEC-0510</t>
+          <t>DEC-0503</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>DEC-0519</t>
+          <t>DEC-0512</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>DEC-0486</t>
+          <t>DEC-0479</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>DEC-0490</t>
+          <t>DEC-0483</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>DEC-0504</t>
+          <t>DEC-0497</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>DEC-0517</t>
+          <t>DEC-0510</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">

--- a/MoneyKeel/documents/other/moneykeel_calc_plan_launch-answer-list_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_launch-answer-list_v01.xlsx
@@ -14,10 +14,10 @@
     <sheet name="Performance" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'EVERYTHING'!$A$1:$I$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'EVERYTHING'!$A$1:$I$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Net worth'!$A$1:$I$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Cash flow'!$A$1:$I$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Performance'!$A$1:$I$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Performance'!$A$1:$I$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -534,14 +534,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
     <col width="51" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="52" customWidth="1" min="6" max="6"/>
     <col width="42" customWidth="1" min="7" max="7"/>
     <col width="52" customWidth="1" min="8" max="8"/>
@@ -551,7 +551,7 @@
     <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>48 things to answer</t>
+          <t>49 things to answer</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr"/>
     </row>
-    <row r="18" ht="45" customHeight="1">
+    <row r="18" ht="60" customHeight="1">
       <c r="A18" s="3" t="n">
         <v>15</v>
       </c>
@@ -1211,7 +1211,9 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Q33 — Which index should each asset class be compared against, and should the person be able to change it?</t>
+          <t>1. Is this row right — the words on screen, the formula, the inputs, the decisions and what it says when it cannot be computed? Say yes, or say what changes.
+Q33 — Which index should each asset class be compared against, and should the person be able to change it?
+Q51 — Home reads "you +3.69% · market +2.83% · ahead by 0.85%". The two sides are not measured the same way: YOUR figure counts the dividends and interest you received (your ruling of 2026-09-25, one meaning of return), while the MARKET figure is the index's PRICE only, because no price feed we have gives an index's dividends. So "</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -1226,7 +1228,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>MK-PF-M-008 — HONEST COMPARISON</t>
+          <t>MK-PF-M-008 — market +X%</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -1493,12 +1495,13 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Net worth</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>VERIFY 48 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
+          <t>1. Is this row right — the words on screen, the formula, the inputs, the decisions and what it says when it cannot be computed? Say yes, or say what changes.
+Q52 — MK-PF-F-026 moneyWeightedReturn is a true personal return — it solves for the rate that makes what you paid in, on the days you paid it in, equal what you have now. It is built, correct and reached by NO SCREEN: the card that showed it was removed by the Performance design you approved on 2026-09-25. The Return the screen does show is a different calculation (Modified Dietz) that also calls itself money-weighted. Do we delete the u</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -1508,22 +1511,22 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>networth</t>
+          <t>multiple_screens</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>all 48 unverified rows on this tab</t>
+          <t>MK-XS-M-004 — ▲ up/▼ down $X (Y%) this month · Return · YOUR RETURN</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>ROW VERIFIED — founder, date and how</t>
+          <t>YOUR ANSWER — use the same number</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>The module cannot be called launch-ready: a TESTED row is proved to match the code, not proved to be right.</t>
+          <t>The figure stays DRAFT, and it is on MORE THAN ONE screen — so the answer settles what every screen showing it says.</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr"/>
@@ -1534,12 +1537,12 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Net worth</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>VERIFY 12 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
+          <t>VERIFY 48 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -1549,12 +1552,12 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>performance</t>
+          <t>networth</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>all 12 unverified rows on this tab</t>
+          <t>all 48 unverified rows on this tab</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -1575,12 +1578,12 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Cash flow</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>VERIFY 53 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
+          <t>VERIFY 11 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -1590,12 +1593,12 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>cashflow</t>
+          <t>performance</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>all 53 unverified rows on this tab</t>
+          <t>all 11 unverified rows on this tab</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -1610,43 +1613,43 @@
       </c>
       <c r="I27" s="3" t="inlineStr"/>
     </row>
-    <row r="28" ht="45" customHeight="1">
+    <row r="28" ht="60" customHeight="1">
       <c r="A28" s="3" t="n">
         <v>25</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Net worth</t>
+          <t>Cash flow</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>8 decisions on this module are recorded in MY words, not yours — confirm or correct: DEC-0019, DEC-0037, DEC-0038, DEC-0045, DEC-0047, DEC-0052, DEC-0061, DEC-0069</t>
+          <t>VERIFY 53 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_log_wording-asks_v01.xlsx</t>
+          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Wording asks</t>
+          <t>cashflow</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>DEC-0019, DEC-0037, DEC-0038, DEC-0045, DEC-0047, DEC-0052, DEC-0061, DEC-0069</t>
+          <t>all 53 unverified rows on this tab</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>YOUR WORDING / YES · NO · CHANGE</t>
+          <t>ROW VERIFIED — founder, date and how</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>The decision stays marked as my reconstruction, so anything built on it rests on my reading of what you meant.</t>
+          <t>The module cannot be called launch-ready: a TESTED row is proved to match the code, not proved to be right.</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr"/>
@@ -1657,12 +1660,12 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Net worth</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>2 decisions on this module are recorded in MY words, not yours — confirm or correct: DEC-0030, DEC-0229</t>
+          <t>8 decisions on this module are recorded in MY words, not yours — confirm or correct: DEC-0019, DEC-0037, DEC-0038, DEC-0045, DEC-0047, DEC-0052, DEC-0061, DEC-0069</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -1677,7 +1680,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>DEC-0030, DEC-0229</t>
+          <t>DEC-0019, DEC-0037, DEC-0038, DEC-0045, DEC-0047, DEC-0052, DEC-0061, DEC-0069</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -1698,12 +1701,12 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Cash flow</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>7 decisions on this module are recorded in MY words, not yours — confirm or correct: DEC-0004, DEC-0177, DEC-0178, DEC-0179, DEC-0197, DEC-0201, DEC-0205</t>
+          <t>2 decisions on this module are recorded in MY words, not yours — confirm or correct: DEC-0030, DEC-0229</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -1718,7 +1721,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>DEC-0004, DEC-0177, DEC-0178, DEC-0179, DEC-0197, DEC-0201, DEC-0205</t>
+          <t>DEC-0030, DEC-0229</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -1733,43 +1736,43 @@
       </c>
       <c r="I30" s="3" t="inlineStr"/>
     </row>
-    <row r="31" ht="30" customHeight="1">
+    <row r="31" ht="45" customHeight="1">
       <c r="A31" s="3" t="n">
         <v>28</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Net worth</t>
+          <t>Cash flow</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Plain line - means line graph?</t>
+          <t>7 decisions on this module are recorded in MY words, not yours — confirm or correct: DEC-0004, DEC-0177, DEC-0178, DEC-0179, DEC-0197, DEC-0201, DEC-0205</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
+          <t>moneykeel_log_wording-asks_v01.xlsx</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>networth</t>
+          <t>Wording asks</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>DEC-0469</t>
+          <t>DEC-0004, DEC-0177, DEC-0178, DEC-0179, DEC-0197, DEC-0201, DEC-0205</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>Open question on this decision — for him</t>
+          <t>YOUR WORDING / YES · NO · CHANGE</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
+          <t>The decision stays marked as my reconstruction, so anything built on it rests on my reading of what you meant.</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr"/>
@@ -1785,7 +1788,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: what does screen look like for manual update?</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Plain line - means line graph?</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -1800,7 +1803,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>DEC-0470</t>
+          <t>DEC-0469</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -1815,7 +1818,7 @@
       </c>
       <c r="I32" s="3" t="inlineStr"/>
     </row>
-    <row r="33" ht="45" customHeight="1">
+    <row r="33" ht="30" customHeight="1">
       <c r="A33" s="3" t="n">
         <v>30</v>
       </c>
@@ -1826,7 +1829,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: do we capture only balance or all individual portfolio holding e.g. AMZN 100 stocks ….</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: what does screen look like for manual update?</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -1841,7 +1844,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>DEC-0475</t>
+          <t>DEC-0470</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -1856,7 +1859,7 @@
       </c>
       <c r="I33" s="3" t="inlineStr"/>
     </row>
-    <row r="34" ht="60" customHeight="1">
+    <row r="34" ht="45" customHeight="1">
       <c r="A34" s="3" t="n">
         <v>31</v>
       </c>
@@ -1867,7 +1870,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: When dividend is captured is it automatically added to income or cash? Similarly, is there a way captical gain is captured and displayed somewhere?</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: do we capture only balance or all individual portfolio holding e.g. AMZN 100 stocks ….</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -1882,7 +1885,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>DEC-0476</t>
+          <t>DEC-0475</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -1897,7 +1900,7 @@
       </c>
       <c r="I34" s="3" t="inlineStr"/>
     </row>
-    <row r="35" ht="30" customHeight="1">
+    <row r="35" ht="60" customHeight="1">
       <c r="A35" s="3" t="n">
         <v>32</v>
       </c>
@@ -1908,7 +1911,7 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Is this manual, imported or connected and captured via Plaid?</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: When dividend is captured is it automatically added to income or cash? Similarly, is there a way captical gain is captured and displayed somewhere?</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -1923,7 +1926,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>DEC-0478</t>
+          <t>DEC-0476</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -1938,18 +1941,18 @@
       </c>
       <c r="I35" s="3" t="inlineStr"/>
     </row>
-    <row r="36" ht="60" customHeight="1">
+    <row r="36" ht="30" customHeight="1">
       <c r="A36" s="3" t="n">
         <v>33</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Net worth</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Total return captures both realized and unrealized gains? Is there any place we display realized P/L, unrealized P/L, total dividend, and total interest separately?</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Is this manual, imported or connected and captured via Plaid?</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -1959,12 +1962,12 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>performance</t>
+          <t>networth</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>DEC-0479</t>
+          <t>DEC-0478</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -1979,7 +1982,7 @@
       </c>
       <c r="I36" s="3" t="inlineStr"/>
     </row>
-    <row r="37" ht="30" customHeight="1">
+    <row r="37" ht="60" customHeight="1">
       <c r="A37" s="3" t="n">
         <v>34</v>
       </c>
@@ -1990,7 +1993,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: stocks with dividends - will it also show dividends received?</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Total return captures both realized and unrealized gains? Is there any place we display realized P/L, unrealized P/L, total dividend, and total interest separately?</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -2005,7 +2008,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>DEC-0483</t>
+          <t>DEC-0479</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -2031,7 +2034,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: What's the level of details displayed and how?r</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: stocks with dividends - will it also show dividends received?</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -2046,7 +2049,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>DEC-0497</t>
+          <t>DEC-0483</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -2072,7 +2075,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Invest: what level of detail, and how?</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: What's the level of details displayed and how?r</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -2087,7 +2090,7 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>DEC-0510</t>
+          <t>DEC-0497</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -2102,18 +2105,18 @@
       </c>
       <c r="I39" s="3" t="inlineStr"/>
     </row>
-    <row r="40" ht="45" customHeight="1">
+    <row r="40" ht="30" customHeight="1">
       <c r="A40" s="3" t="n">
         <v>37</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Cash flow</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: How is income + spending captured, at what frequency, and what about cash / unconnected cards?</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Invest: what level of detail, and how?</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -2123,12 +2126,12 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>cashflow</t>
+          <t>performance</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>DEC-0503</t>
+          <t>DEC-0510</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -2143,7 +2146,7 @@
       </c>
       <c r="I40" s="3" t="inlineStr"/>
     </row>
-    <row r="41" ht="30" customHeight="1">
+    <row r="41" ht="45" customHeight="1">
       <c r="A41" s="3" t="n">
         <v>38</v>
       </c>
@@ -2154,7 +2157,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Are the month bars cash flows -- inflow / outflow?</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: How is income + spending captured, at what frequency, and what about cash / unconnected cards?</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -2169,7 +2172,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>DEC-0512</t>
+          <t>DEC-0503</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -2184,43 +2187,43 @@
       </c>
       <c r="I41" s="3" t="inlineStr"/>
     </row>
-    <row r="42" ht="60" customHeight="1">
+    <row r="42" ht="30" customHeight="1">
       <c r="A42" s="3" t="n">
         <v>39</v>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Net worth</t>
+          <t>Cash flow</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Commit — the branch was 278 files behind on 2026-09-14; committed since: 983805a (catch-up), f0e1d6d (Net worth v08), c4f2679 (the Since crash), 727e22a (Performance v14). Nothing is pushed — the branch taxonomy-v1.0.7 is local only.</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Are the month bars cash flows -- inflow / outflow?</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
+          <t>moneykeel_log_decisions_v01.xlsx</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Workplan</t>
+          <t>cashflow</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Commit — the branch was 278 files behind on 2026-09-14; committed sinc</t>
+          <t>DEC-0512</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>Status / Comments</t>
+          <t>Open question on this decision — for him</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Founder: say when to PUSH. (Note 2026-09-26: the Xcode licence has not been accepted on this Mac, so the normal git refuses to run — "sudo xcodebuild -license accept" once, then git works everywhere again.)</t>
+          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr"/>
@@ -2236,7 +2239,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>EIGHT live mocks still DRAW words the canon retired (measured 2026-09-26 over the drawn frames, not the commentary): cash-flow this-month v06 ("In (take-home)", "spending") · income end-to-end v07 ("A usual month", "Gross a year") · look-ahead v03 ("/mo") · money-four-tabs v01 ("In (take-home)", "Out (", "/mo", "spending") · account-detail v01 ("Connected ·") · empty-state-pattern v01 ("WHAT YOU O</t>
+          <t>Commit — the branch was 278 files behind on 2026-09-14; committed since: 983805a (catch-up), f0e1d6d (Net worth v08), c4f2679 (the Since crash), 727e22a (Performance v14). Nothing is pushed — the branch taxonomy-v1.0.7 is local only.</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
@@ -2251,7 +2254,7 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>EIGHT live mocks still DRAW words the canon retired (measured 2026-09-</t>
+          <t>Commit — the branch was 278 files behind on 2026-09-14; committed sinc</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -2261,7 +2264,7 @@
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>Founder: say whether each gets a new version on the canon now (old archived), or at its next change. Plan v05 already carries its list inside the file as mark 14 and is fixed when v06 is drawn.</t>
+          <t>Founder: say when to PUSH. (Note 2026-09-26: the Xcode licence has not been accepted on this Mac, so the normal git refuses to run — "sudo xcodebuild -license accept" once, then git works everywhere again.)</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr"/>
@@ -2272,12 +2275,12 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Cash flow</t>
+          <t>Net worth</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Stand-in ages when the birth year is missing: the Retirement cockpit and Insights assume 45, the cash-flow model and the draw steer assume 68, the onboarding helper 35 (or 65 for the retirement age). Your rule R2 says an unknown input gives no number and a reason.</t>
+          <t>EIGHT live mocks still DRAW words the canon retired (measured 2026-09-26 over the drawn frames, not the commentary): cash-flow this-month v06 ("In (take-home)", "spending") · income end-to-end v07 ("A usual month", "Gross a year") · look-ahead v03 ("/mo") · money-four-tabs v01 ("In (take-home)", "Out (", "/mo", "spending") · account-detail v01 ("Connected ·") · empty-state-pattern v01 ("WHAT YOU O</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -2292,7 +2295,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Stand-in ages when the birth year is missing: the Retirement cockpit a</t>
+          <t>EIGHT live mocks still DRAW words the canon retired (measured 2026-09-</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -2302,7 +2305,7 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Founder: say what those screens show when the birth year is missing (ask for it in place? show the door?); then Claude: mock first, then code</t>
+          <t>Founder: say whether each gets a new version on the canon now (old archived), or at its next change. Plan v05 already carries its list inside the file as mark 14 and is fixed when v06 is drawn.</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr"/>
@@ -2318,7 +2321,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Q-CF-2 'how much have I spent this month, against the plan, and what is left' — eight figures DRAFTED on MK-CF-O-003 thisMonth: expected inflow, planned outflow, planned surplus, each planned line, inflow so far, outflow so far, surplus so far, each received line (MK-CF-M-047…054)</t>
+          <t>Stand-in ages when the birth year is missing: the Retirement cockpit and Insights assume 45, the cash-flow model and the draw steer assume 68, the onboarding helper 35 (or 65 for the retirement age). Your rule R2 says an unknown input gives no number and a reason.</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -2333,7 +2336,7 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>Q-CF-2 'how much have I spent this month, against the plan, and what i</t>
+          <t>Stand-in ages when the birth year is missing: the Retirement cockpit a</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
@@ -2343,7 +2346,7 @@
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>Founder: read the eight rows on the master's cashflow tab (Row status says DRAFT) and say yes, or say what changes. Claude: the moment you do, the Cash flow screen, the month detail screen and Home's cell move behind the door and stop working figures out themselves</t>
+          <t>Founder: say what those screens show when the birth year is missing (ask for it in place? show the door?); then Claude: mock first, then code</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr"/>
@@ -2354,12 +2357,12 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Net worth</t>
+          <t>Cash flow</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>One door, one term: the three ways to add an account read 'Link it (read-only)', 'Add by hand' and 'Import from a file' on every screen, under the heading 'How do you want to add an account?' — Home, Sharpen your plan, the Plan tab, Net worth (first day and the add sheet), the Connect an account screen and Performance</t>
+          <t>Q-CF-2 'how much have I spent this month, against the plan, and what is left' — eight figures DRAFTED on MK-CF-O-003 thisMonth: expected inflow, planned outflow, planned surplus, each planned line, inflow so far, outflow so far, surplus so far, each received line (MK-CF-M-047…054)</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
@@ -2374,7 +2377,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>One door, one term: the three ways to add an account read 'Link it (re</t>
+          <t>Q-CF-2 'how much have I spent this month, against the plan, and what i</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -2384,7 +2387,7 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Founder: approve the mock MoneyKeel/documents/home-screen/moneykeel_pres_mock_ways-to-add-an-account_v10.html (every affected screen, before and after). Claude: then build all of it the same day, with the tests and the canon row</t>
+          <t>Founder: read the eight rows on the master's cashflow tab (Row status says DRAFT) and say yes, or say what changes. Claude: the moment you do, the Cash flow screen, the month detail screen and Home's cell move behind the door and stop working figures out themselves</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr"/>
@@ -2400,7 +2403,7 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Nothing recorded which design each screen was built from. The Build 53 Net worth and Performance finals (networth-FINAL.html, performance-FINAL.html, the two Net worth PDFs, Net worth screens 01 to 11) were filed under networth-and-performance/archive/ on 2026-09-01, which marks them replaced. They were not replaced. Six hours of mocks then started from the wrong files. CORRECTION 2026-09-14: Buil</t>
+          <t>One door, one term: the three ways to add an account read 'Link it (read-only)', 'Add by hand' and 'Import from a file' on every screen, under the heading 'How do you want to add an account?' — Home, Sharpen your plan, the Plan tab, Net worth (first day and the add sheet), the Connect an account screen and Performance</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
@@ -2415,7 +2418,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>Nothing recorded which design each screen was built from. The Build 53</t>
+          <t>One door, one term: the three ways to add an account read 'Link it (re</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
@@ -2425,7 +2428,7 @@
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>Claude: done 2026-09-14 — Build 53 files matched by exact content and recorded in MoneyKeel/documents/standards/moneykeel_pres_spec_design-each-screen-was-built-from_v01.md. Founder: (1) confirm Net worth = v5 + square corners; (2) say whether to draw Net worth v6 from the Build 53 code (v5 with squ</t>
+          <t>Founder: approve the mock MoneyKeel/documents/home-screen/moneykeel_pres_mock_ways-to-add-an-account_v10.html (every affected screen, before and after). Claude: then build all of it the same day, with the tests and the canon row</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr"/>
@@ -2441,7 +2444,7 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Net worth v07 — the three ways to add an account on Net worth (first day, the add sheet, the add button), plus every ruling since Build 53 that touches the screen (empty state, Debts, Emergency fund, Stocks / Funds, /month, you entered, expenses, odds to the nearest 5), each marked</t>
+          <t>Nothing recorded which design each screen was built from. The Build 53 Net worth and Performance finals (networth-FINAL.html, performance-FINAL.html, the two Net worth PDFs, Net worth screens 01 to 11) were filed under networth-and-performance/archive/ on 2026-09-01, which marks them replaced. They were not replaced. Six hours of mocks then started from the wrong files. CORRECTION 2026-09-14: Buil</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
@@ -2456,7 +2459,7 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>Net worth v07 — the three ways to add an account on Net worth (first d</t>
+          <t>Nothing recorded which design each screen was built from. The Build 53</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -2466,7 +2469,7 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Founder: say yes to v08, or name a mark. Also: today's money for the retirement figures and tax on taxable withdrawals (recommended); whether dark/light bars replace the Plan tab's quiet labels. Claude: once approved, record v08 as the current Net worth design, archive v06, then build marks 1–4 and </t>
+          <t>Claude: done 2026-09-14 — Build 53 files matched by exact content and recorded in MoneyKeel/documents/standards/moneykeel_pres_spec_design-each-screen-was-built-from_v01.md. Founder: (1) confirm Net worth = v5 + square corners; (2) say whether to draw Net worth v6 from the Build 53 code (v5 with squ</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr"/>
@@ -2482,7 +2485,7 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>The retirement sentence (Net worth, Plan, Home) prints future dollars without saying so, and the odds calculation charges no tax on withdrawals from taxable accounts — found checking the founder's question on v07 ($4.1M at 65 is about $2.0M in today's money)</t>
+          <t>Net worth v07 — the three ways to add an account on Net worth (first day, the add sheet, the add button), plus every ruling since Build 53 that touches the screen (empty state, Debts, Emergency fund, Stocks / Funds, /month, you entered, expenses, odds to the nearest 5), each marked</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
@@ -2497,7 +2500,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The retirement sentence (Net worth, Plan, Home) prints future dollars </t>
+          <t>Net worth v07 — the three ways to add an account on Net worth (first d</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
@@ -2507,7 +2510,7 @@
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>Founder: say whether to show today's money and to tax taxable withdrawals (recommended). Claude: then write both as findings on the master rows (MK-XS-M-002 and the pot/leftover figures) before any code.</t>
+          <t xml:space="preserve">Founder: say yes to v08, or name a mark. Also: today's money for the retirement figures and tax on taxable withdrawals (recommended); whether dark/light bars replace the Plan tab's quiet labels. Claude: once approved, record v08 as the current Net worth design, archive v06, then build marks 1–4 and </t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr"/>
@@ -2518,12 +2521,12 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Cash flow</t>
+          <t>Net worth</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Two word collisions found building v08: Cash flow's 'Add by hand' adds an EXPENSE (the same words as the account door), and Settings still says 'Disconnect' beside 'Linked accounts'</t>
+          <t>The retirement sentence (Net worth, Plan, Home) prints future dollars without saying so, and the odds calculation charges no tax on withdrawals from taxable accounts — found checking the founder's question on v07 ($4.1M at 65 is about $2.0M in today's money)</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
@@ -2538,7 +2541,7 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>Two word collisions found building v08: Cash flow's 'Add by hand' adds</t>
+          <t xml:space="preserve">The retirement sentence (Net worth, Plan, Home) prints future dollars </t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -2548,7 +2551,7 @@
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>Founder: say whether Cash flow's door should read differently (for example 'Add an expense by hand') and whether Disconnect becomes 'Unlink'.</t>
+          <t>Founder: say whether to show today's money and to tax taxable withdrawals (recommended). Claude: then write both as findings on the master rows (MK-XS-M-002 and the pot/leftover figures) before any code.</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr"/>
@@ -2559,43 +2562,84 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Net worth</t>
+          <t>Cash flow</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
+          <t>Two word collisions found building v08: Cash flow's 'Add by hand' adds an EXPENSE (the same words as the account door), and Settings still says 'Disconnect' beside 'Linked accounts'</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>Workplan</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>Two word collisions found building v08: Cash flow's 'Add by hand' adds</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>Status / Comments</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>Founder: say whether Cash flow's door should read differently (for example 'Add an expense by hand') and whether Disconnect becomes 'Unlink'.</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Net worth</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
           <t>LAUNCH ANSWER LIST — 61 things need you for Net worth, Cash flow and Performance to be launch-ready</t>
         </is>
       </c>
-      <c r="D51" s="3" t="inlineStr">
+      <c r="D52" s="3" t="inlineStr">
         <is>
           <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
         </is>
       </c>
-      <c r="E51" s="3" t="inlineStr">
+      <c r="E52" s="3" t="inlineStr">
         <is>
           <t>Workplan</t>
         </is>
       </c>
-      <c r="F51" s="3" t="inlineStr">
+      <c r="F52" s="3" t="inlineStr">
         <is>
           <t>LAUNCH ANSWER LIST — 61 things need you for Net worth, Cash flow and P</t>
         </is>
       </c>
-      <c r="G51" s="3" t="inlineStr">
+      <c r="G52" s="3" t="inlineStr">
         <is>
           <t>Status / Comments</t>
         </is>
       </c>
-      <c r="H51" s="3" t="inlineStr">
+      <c r="H52" s="3" t="inlineStr">
         <is>
           <t>His ask, 2026-09-29: ‘Give me a list of files, tabs, and rows I need to answer for NW, CF, Performance sections of the app to be complete.’ Open MoneyKeel/documents/other/moneykeel_calc_plan_launch-answer-list_v01.xlsx. Five tabs: Read me, EVERYTHING, and one per module. Every line names its FILE, i</t>
         </is>
       </c>
-      <c r="I51" s="3" t="inlineStr"/>
+      <c r="I52" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I51"/>
+  <autoFilter ref="A1:I52"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3274,7 +3318,7 @@
     </row>
     <row r="18" ht="60" customHeight="1">
       <c r="A18" s="3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
@@ -3315,7 +3359,7 @@
     </row>
     <row r="19" ht="45" customHeight="1">
       <c r="A19" s="3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
@@ -3356,7 +3400,7 @@
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
@@ -3397,7 +3441,7 @@
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
@@ -3438,7 +3482,7 @@
     </row>
     <row r="22" ht="45" customHeight="1">
       <c r="A22" s="3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
@@ -3479,7 +3523,7 @@
     </row>
     <row r="23" ht="60" customHeight="1">
       <c r="A23" s="3" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
@@ -3520,7 +3564,7 @@
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="3" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
@@ -3561,7 +3605,7 @@
     </row>
     <row r="25" ht="60" customHeight="1">
       <c r="A25" s="3" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
@@ -3602,7 +3646,7 @@
     </row>
     <row r="26" ht="60" customHeight="1">
       <c r="A26" s="3" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
@@ -3643,7 +3687,7 @@
     </row>
     <row r="27" ht="60" customHeight="1">
       <c r="A27" s="3" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
@@ -3684,7 +3728,7 @@
     </row>
     <row r="28" ht="60" customHeight="1">
       <c r="A28" s="3" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
@@ -3725,7 +3769,7 @@
     </row>
     <row r="29" ht="60" customHeight="1">
       <c r="A29" s="3" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
@@ -3766,7 +3810,7 @@
     </row>
     <row r="30" ht="60" customHeight="1">
       <c r="A30" s="3" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
@@ -3807,7 +3851,7 @@
     </row>
     <row r="31" ht="60" customHeight="1">
       <c r="A31" s="3" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
@@ -4193,7 +4237,7 @@
     </row>
     <row r="10" ht="60" customHeight="1">
       <c r="A10" s="3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
@@ -4234,7 +4278,7 @@
     </row>
     <row r="11" ht="45" customHeight="1">
       <c r="A11" s="3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
@@ -4275,7 +4319,7 @@
     </row>
     <row r="12" ht="45" customHeight="1">
       <c r="A12" s="3" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
@@ -4316,7 +4360,7 @@
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="3" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
@@ -4357,7 +4401,7 @@
     </row>
     <row r="14" ht="60" customHeight="1">
       <c r="A14" s="3" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
@@ -4398,7 +4442,7 @@
     </row>
     <row r="15" ht="60" customHeight="1">
       <c r="A15" s="3" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
@@ -4439,7 +4483,7 @@
     </row>
     <row r="16" ht="60" customHeight="1">
       <c r="A16" s="3" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
@@ -4490,15 +4534,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
     <col width="51" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
     <col width="42" customWidth="1" min="7" max="7"/>
     <col width="52" customWidth="1" min="8" max="8"/>
     <col width="40" customWidth="1" min="9" max="9"/>
@@ -4507,7 +4551,7 @@
     <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>7 things to answer for Performance</t>
+          <t>8 things to answer for Performance</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -4577,7 +4621,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="45" customHeight="1">
+    <row r="4" ht="60" customHeight="1">
       <c r="A4" s="3" t="n">
         <v>15</v>
       </c>
@@ -4588,7 +4632,9 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Q33 — Which index should each asset class be compared against, and should the person be able to change it?</t>
+          <t>1. Is this row right — the words on screen, the formula, the inputs, the decisions and what it says when it cannot be computed? Say yes, or say what changes.
+Q33 — Which index should each asset class be compared against, and should the person be able to change it?
+Q51 — Home reads "you +3.69% · market +2.83% · ahead by 0.85%". The two sides are not measured the same way: YOUR figure counts the dividends and interest you received (your ruling of 2026-09-25, one meaning of return), while the MARKET figure is the index's PRICE only, because no price feed we have gives an index's dividends. So "</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -4603,7 +4649,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>MK-PF-M-008 — HONEST COMPARISON</t>
+          <t>MK-PF-M-008 — market +X%</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -4620,7 +4666,7 @@
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -4629,7 +4675,8 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>VERIFY 12 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
+          <t>1. Is this row right — the words on screen, the formula, the inputs, the decisions and what it says when it cannot be computed? Say yes, or say what changes.
+Q52 — MK-PF-F-026 moneyWeightedReturn is a true personal return — it solves for the rate that makes what you paid in, on the days you paid it in, equal what you have now. It is built, correct and reached by NO SCREEN: the card that showed it was removed by the Performance design you approved on 2026-09-25. The Return the screen does show is a different calculation (Modified Dietz) that also calls itself money-weighted. Do we delete the u</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -4639,109 +4686,109 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
+          <t>multiple_screens</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-M-004 — ▲ up/▼ down $X (Y%) this month · Return · YOUR RETURN</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>YOUR ANSWER — use the same number</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>The figure stays DRAFT, and it is on MORE THAN ONE screen — so the answer settles what every screen showing it says.</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>VERIFY 11 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
           <t>performance</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>all 12 unverified rows on this tab</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>all 11 unverified rows on this tab</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>ROW VERIFIED — founder, date and how</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>The module cannot be called launch-ready: a TESTED row is proved to match the code, not proved to be right.</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr"/>
-    </row>
-    <row r="6" ht="45" customHeight="1">
-      <c r="A6" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7" ht="45" customHeight="1">
+      <c r="A7" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>2 decisions on this module are recorded in MY words, not yours — confirm or correct: DEC-0030, DEC-0229</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>moneykeel_log_wording-asks_v01.xlsx</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>Wording asks</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>DEC-0030, DEC-0229</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>YOUR WORDING / YES · NO · CHANGE</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>The decision stays marked as my reconstruction, so anything built on it rests on my reading of what you meant.</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr"/>
-    </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Total return captures both realized and unrealized gains? Is there any place we display realized P/L, unrealized P/L, total dividend, and total interest separately?</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>performance</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>DEC-0479</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>Open question on this decision — for him</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
-        </is>
-      </c>
       <c r="I7" s="3" t="inlineStr"/>
     </row>
-    <row r="8" ht="30" customHeight="1">
+    <row r="8" ht="60" customHeight="1">
       <c r="A8" s="3" t="n">
         <v>34</v>
       </c>
@@ -4752,7 +4799,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: stocks with dividends - will it also show dividends received?</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Total return captures both realized and unrealized gains? Is there any place we display realized P/L, unrealized P/L, total dividend, and total interest separately?</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -4767,7 +4814,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>DEC-0483</t>
+          <t>DEC-0479</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -4793,7 +4840,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: What's the level of details displayed and how?r</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: stocks with dividends - will it also show dividends received?</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -4808,7 +4855,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>DEC-0497</t>
+          <t>DEC-0483</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -4834,38 +4881,79 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: What's the level of details displayed and how?r</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>moneykeel_log_decisions_v01.xlsx</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>performance</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>DEC-0497</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Open question on this decision — for him</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
           <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Invest: what level of detail, and how?</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>moneykeel_log_decisions_v01.xlsx</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>performance</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>DEC-0510</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>Open question on this decision — for him</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr"/>
+      <c r="I11" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I10"/>
+  <autoFilter ref="A1:I11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_launch-answer-list_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_launch-answer-list_v01.xlsx
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>8 decisions on this module are recorded in MY words, not yours — confirm or correct: DEC-0019, DEC-0037, DEC-0038, DEC-0045, DEC-0047, DEC-0052, DEC-0061, DEC-0069</t>
+          <t>7 decisions on this module are recorded in MY words, not yours — confirm or correct: DEC-0019, DEC-0038, DEC-0045, DEC-0047, DEC-0052, DEC-0061, DEC-0069</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>DEC-0019, DEC-0037, DEC-0038, DEC-0045, DEC-0047, DEC-0052, DEC-0061, DEC-0069</t>
+          <t>DEC-0019, DEC-0038, DEC-0045, DEC-0047, DEC-0052, DEC-0061, DEC-0069</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>7 decisions on this module are recorded in MY words, not yours — confirm or correct: DEC-0004, DEC-0177, DEC-0178, DEC-0179, DEC-0197, DEC-0201, DEC-0205</t>
+          <t>6 decisions on this module are recorded in MY words, not yours — confirm or correct: DEC-0177, DEC-0178, DEC-0179, DEC-0197, DEC-0201, DEC-0205</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>DEC-0004, DEC-0177, DEC-0178, DEC-0179, DEC-0197, DEC-0201, DEC-0205</t>
+          <t>DEC-0177, DEC-0178, DEC-0179, DEC-0197, DEC-0201, DEC-0205</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>8 decisions on this module are recorded in MY words, not yours — confirm or correct: DEC-0019, DEC-0037, DEC-0038, DEC-0045, DEC-0047, DEC-0052, DEC-0061, DEC-0069</t>
+          <t>7 decisions on this module are recorded in MY words, not yours — confirm or correct: DEC-0019, DEC-0038, DEC-0045, DEC-0047, DEC-0052, DEC-0061, DEC-0069</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>DEC-0019, DEC-0037, DEC-0038, DEC-0045, DEC-0047, DEC-0052, DEC-0061, DEC-0069</t>
+          <t>DEC-0019, DEC-0038, DEC-0045, DEC-0047, DEC-0052, DEC-0061, DEC-0069</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -4287,7 +4287,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>7 decisions on this module are recorded in MY words, not yours — confirm or correct: DEC-0004, DEC-0177, DEC-0178, DEC-0179, DEC-0197, DEC-0201, DEC-0205</t>
+          <t>6 decisions on this module are recorded in MY words, not yours — confirm or correct: DEC-0177, DEC-0178, DEC-0179, DEC-0197, DEC-0201, DEC-0205</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>DEC-0004, DEC-0177, DEC-0178, DEC-0179, DEC-0197, DEC-0201, DEC-0205</t>
+          <t>DEC-0177, DEC-0178, DEC-0179, DEC-0197, DEC-0201, DEC-0205</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">

--- a/MoneyKeel/documents/other/moneykeel_calc_plan_launch-answer-list_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_launch-answer-list_v01.xlsx
@@ -14,10 +14,10 @@
     <sheet name="Performance" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'EVERYTHING'!$A$1:$I$52</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Net worth'!$A$1:$I$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Cash flow'!$A$1:$I$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Performance'!$A$1:$I$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'EVERYTHING'!$A$1:$I$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Net worth'!$A$1:$I$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Cash flow'!$A$1:$I$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Performance'!$A$1:$I$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -551,7 +551,7 @@
     <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>49 things to answer</t>
+          <t>50 things to answer</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -632,7 +632,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Q32 — The trend survives on a new device but the walk behind it does not. Should the trend say so, or show quietly?</t>
+          <t>1. Is this row right — the words on screen, the formula, the inputs, the decisions and what it says when it cannot be computed? Say yes, or say what changes.</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr"/>
     </row>
-    <row r="5" ht="45" customHeight="1">
+    <row r="5" ht="60" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>2</v>
       </c>
@@ -673,7 +673,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Q14 — What should a MIXED account be called on screen, when it holds several classes at once?</t>
+          <t>Q17 — "Return on cash + investments" counts money you paid in as a gain. Is the LABEL wrong, or the FORMULA? Fixing the formula means removing deposits and withdrawals before measuring.</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-008 — each account and its balance</t>
+          <t>MK-NW-M-002 — Return on cash + investments</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr"/>
     </row>
-    <row r="6" ht="45" customHeight="1">
+    <row r="6" ht="60" customHeight="1">
       <c r="A6" s="3" t="n">
         <v>3</v>
       </c>
@@ -714,7 +714,8 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Q18 — Net worth projects the pot WITHOUT your big costs; Cash flow, Budget, Goals and Social Security timing all include them. Which is right for the Net worth screen?</t>
+          <t>1. Is this row right — the words on screen, the formula, the inputs, the decisions and what it says when it cannot be computed? Say yes, or say what changes.
+Q32 — The trend survives on a new device but the walk behind it does not. Should the trend say so, or show quietly?</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -729,7 +730,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-015 — YOUR RETIREMENT PLAN — on track for $X by age Y</t>
+          <t>MK-NW-M-003 — the trend line</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -744,7 +745,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr"/>
     </row>
-    <row r="7" ht="60" customHeight="1">
+    <row r="7" ht="45" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>4</v>
       </c>
@@ -755,7 +756,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Q17 — "Return on cash + investments" counts money you paid in as a gain. Is the LABEL wrong, or the FORMULA? Fixing the formula means removing deposits and withdrawals before measuring.</t>
+          <t>1. Is this row right — the words on screen, the formula, the inputs, the decisions and what it says when it cannot be computed? Say yes, or say what changes.</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -770,7 +771,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-002 — Return on cash + investments</t>
+          <t>MK-NW-M-006 — 🏠 PERSONAL PROPERTY</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -829,7 +830,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr"/>
     </row>
-    <row r="9" ht="45" customHeight="1">
+    <row r="9" ht="60" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>6</v>
       </c>
@@ -840,7 +841,8 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Q15 — An institution word we do not recognise: refuse the line and ask you, or book it as unclassified with no direction? The old sign-guess is what minted the $1.4 million.</t>
+          <t>1. Is this row right — the words on screen, the formula, the inputs, the decisions and what it says when it cannot be computed? Say yes, or say what changes.
+Q14 — What should a MIXED account be called on screen, when it holds several classes at once?</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -855,7 +857,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-019 — Income</t>
+          <t>MK-NW-M-008 — each account and its balance</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -870,7 +872,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr"/>
     </row>
-    <row r="10" ht="45" customHeight="1">
+    <row r="10" ht="60" customHeight="1">
       <c r="A10" s="3" t="n">
         <v>7</v>
       </c>
@@ -881,7 +883,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Q01 — Is Quantity for a bond the FACE amount (e.g. 227,000) with the price quoted per $100 of face, or the number of bonds? It decides how value and gain are worked out.</t>
+          <t>Q53 — "Monthly debt payments" on the Net worth screen: the MINIMUM each debt obliges, or what ACTUALLY leaves your account? They part whenever someone pays more than a minimum. On one card — $200 minimum, paid $600 — the minimum reads $200 and the actual reads $600. Both are real figures: the minimum is the obligation a lender can demand (it is what debt-to-income is measured on), the actual is the money that leaves. The screen shows the MINIMUM today, and the label reads like the actual. Which belongs under those words — or should the line say which it is, or show both?</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -896,7 +898,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-023 — Face value</t>
+          <t>MK-NW-M-012 — Monthly debt payments</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -922,7 +924,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Q04 — "Annual income" on a bond: the last twelve months actually received, or the forward estimate from today\'s coupon? Both are defensible and they differ.</t>
+          <t>1. Is this row right — the words on screen, the formula, the inputs, the decisions and what it says when it cannot be computed? Say yes, or say what changes.</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -937,7 +939,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-024 — Interest payments</t>
+          <t>MK-NW-M-015 — YOUR RETIREMENT PLAN — on track for $X by age Y</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -963,7 +965,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Q05 — Accrued interest: do we work it out ourselves — which needs a day-count rule per bond type — or only show what the institution gives us?</t>
+          <t>1. Is this row right — the words on screen, the formula, the inputs, the decisions and what it says when it cannot be computed? Say yes, or say what changes.</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -978,7 +980,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-026 — Yield if held to maturity</t>
+          <t>MK-NW-M-016 — Net worth so far (setup)</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -993,7 +995,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr"/>
     </row>
-    <row r="13" ht="60" customHeight="1">
+    <row r="13" ht="45" customHeight="1">
       <c r="A13" s="3" t="n">
         <v>10</v>
       </c>
@@ -1004,7 +1006,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Q34 — Approve the exact wording for the average-price rule (info dot + column Q): 'Shares with no recorded purchase price are left out of the average. N of your shares are in that position.' — and the refusal: 'Average not available — none of these shares has a recorded price.'</t>
+          <t>Q15 — An institution word we do not recognise: refuse the line and ask you, or book it as unclassified with no direction? The old sign-guess is what minted the $1.4 million.</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -1019,7 +1021,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-032 — Price paid (average)</t>
+          <t>MK-NW-M-019 — Income</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1034,7 +1036,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr"/>
     </row>
-    <row r="14" ht="60" customHeight="1">
+    <row r="14" ht="45" customHeight="1">
       <c r="A14" s="3" t="n">
         <v>11</v>
       </c>
@@ -1045,8 +1047,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Q35 — Approve the exact label and the canon phrase for the twelve-month window. Proposed: 'Dividends received (trailing twelve months)' here, and 'trailing twelve months' in the other four places (spelled out — no initialism).
-Q36 — Dividends on this card: THIS account only, matching 'Realized from sales' beside it? Recommended: yes.</t>
+          <t>Q01 — Is Quantity for a bond the FACE amount (e.g. 227,000) with the price quoted per $100 of face, or the number of bonds? It decides how value and gain are worked out.</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -1061,7 +1062,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-034 — Dividends received (12 mo)</t>
+          <t>MK-NW-M-023 — Face value</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -1076,7 +1077,7 @@
       </c>
       <c r="I14" s="3" t="inlineStr"/>
     </row>
-    <row r="15" ht="60" customHeight="1">
+    <row r="15" ht="45" customHeight="1">
       <c r="A15" s="3" t="n">
         <v>12</v>
       </c>
@@ -1087,7 +1088,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Q37 — For a connected account: log an 'Opening holding' row per broker lot at first sync (dated the lot's purchase date, at the broker's cost) so every later sale is covered — recommended — or keep 'not counted + say so' for pre-history purchases?</t>
+          <t>Q04 — "Annual income" on a bond: the last twelve months actually received, or the forward estimate from today\'s coupon? Both are defensible and they differ.</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -1102,7 +1103,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-035 — Realized gain from your buys and sells</t>
+          <t>MK-NW-M-024 — Interest payments</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1117,7 +1118,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr"/>
     </row>
-    <row r="16" ht="60" customHeight="1">
+    <row r="16" ht="45" customHeight="1">
       <c r="A16" s="3" t="n">
         <v>13</v>
       </c>
@@ -1128,7 +1129,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Q20 — A lot with no recorded purchase price is skipped, so its gain is simply absent. Should the screen SAY so — "gain not counted for N shares, no purchase price on record" — rather than quietly reporting less?</t>
+          <t>Q05 — Accrued interest: do we work it out ourselves — which needs a day-count rule per bond type — or only show what the institution gives us?</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -1143,7 +1144,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-036 — Gain — long-term (held over 1 yr)</t>
+          <t>MK-NW-M-026 — Yield if held to maturity</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -1169,8 +1170,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Q03 — Certificates of deposit: under Fixed Income, or their own class? They carry a term, a rate and an early-withdrawal penalty that a bond does not.
-Q38 — Your bond display rule, three specifics before the mock: (1) 'quantity' for a bond = the number of bonds (each of face $1,000), or the total face amount? (2) 'earned interest' = the INTEREST rows recorded in the ledger for this bond — the only source we have — yes? (3) 'current price' = price per $100 of face as brokers quote it, or the dollar value of the position? Then I mock the bond card and screen before any code.</t>
+          <t>Q34 — Approve the exact wording for the average-price rule (info dot + column Q): 'Shares with no recorded purchase price are left out of the average. N of your shares are in that position.' — and the refusal: 'Average not available — none of these shares has a recorded price.'</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-041 — total value of your bonds</t>
+          <t>MK-NW-M-032 — Price paid (average)</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -1206,193 +1206,195 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
+          <t>Net worth</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Q35 — Approve the exact label and the canon phrase for the twelve-month window. Proposed: 'Dividends received (trailing twelve months)' here, and 'trailing twelve months' in the other four places (spelled out — no initialism).
+Q36 — Dividends on this card: THIS account only, matching 'Realized from sales' beside it? Recommended: yes.</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>networth</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-M-034 — Dividends received (12 mo)</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>YOUR ANSWER — use the same number</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Net worth</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Q37 — For a connected account: log an 'Opening holding' row per broker lot at first sync (dated the lot's purchase date, at the broker's cost) so every later sale is covered — recommended — or keep 'not counted + say so' for pre-history purchases?</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>networth</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-M-035 — Realized gain from your buys and sells</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>YOUR ANSWER — use the same number</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Net worth</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Q20 — A lot with no recorded purchase price is skipped, so its gain is simply absent. Should the screen SAY so — "gain not counted for N shares, no purchase price on record" — rather than quietly reporting less?</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>networth</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-M-036 — Gain — long-term (held over 1 yr)</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>YOUR ANSWER — use the same number</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Net worth</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Q03 — Certificates of deposit: under Fixed Income, or their own class? They carry a term, a rate and an early-withdrawal penalty that a bond does not.
+Q38 — Your bond display rule, three specifics before the mock: (1) 'quantity' for a bond = the number of bonds (each of face $1,000), or the total face amount? (2) 'earned interest' = the INTEREST rows recorded in the ledger for this bond — the only source we have — yes? (3) 'current price' = price per $100 of face as brokers quote it, or the dollar value of the position? Then I mock the bond card and screen before any code.</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>networth</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-M-041 — total value of your bonds</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>YOUR ANSWER — use the same number</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>1. Is this row right — the words on screen, the formula, the inputs, the decisions and what it says when it cannot be computed? Say yes, or say what changes.
 Q33 — Which index should each asset class be compared against, and should the person be able to change it?
 Q51 — Home reads "you +3.69% · market +2.83% · ahead by 0.85%". The two sides are not measured the same way: YOUR figure counts the dividends and interest you received (your ruling of 2026-09-25, one meaning of return), while the MARKET figure is the index's PRICE only, because no price feed we have gives an index's dividends. So "</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>performance</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>MK-PF-M-008 — market +X%</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>YOUR ANSWER — use the same number</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr"/>
-    </row>
-    <row r="19" ht="45" customHeight="1">
-      <c r="A19" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Cash flow</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>1. Is this row right — the words on screen, the formula, the inputs, the decisions and what it says when it cannot be computed? Say yes, or say what changes.</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>cashflow</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>MK-CF-M-049 — = Planned surplus</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>YOUR ANSWER — use the same number</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr"/>
-    </row>
-    <row r="20" ht="45" customHeight="1">
-      <c r="A20" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Cash flow</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>1. Is this row right — the words on screen, the formula, the inputs, the decisions and what it says when it cannot be computed? Say yes, or say what changes.</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>cashflow</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>MK-CF-M-050 — each planned line</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>YOUR ANSWER — use the same number</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr"/>
-    </row>
-    <row r="21" ht="45" customHeight="1">
-      <c r="A21" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Cash flow</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>1. Is this row right — the words on screen, the formula, the inputs, the decisions and what it says when it cannot be computed? Say yes, or say what changes.</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>cashflow</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>MK-CF-M-051 — Inflow</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>YOUR ANSWER — use the same number</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr"/>
-    </row>
-    <row r="22" ht="45" customHeight="1">
-      <c r="A22" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Cash flow</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>1. Is this row right — the words on screen, the formula, the inputs, the decisions and what it says when it cannot be computed? Say yes, or say what changes.</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>cashflow</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>MK-CF-M-052 — Outflow (expenses + debt)</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -1433,7 +1435,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>MK-CF-M-053 — = Surplus</t>
+          <t>MK-CF-M-049 — = Planned surplus</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -1474,7 +1476,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>MK-CF-M-054 — each received line</t>
+          <t>MK-CF-M-050 — each planned line</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -1489,331 +1491,331 @@
       </c>
       <c r="I24" s="3" t="inlineStr"/>
     </row>
-    <row r="25" ht="60" customHeight="1">
+    <row r="25" ht="45" customHeight="1">
       <c r="A25" s="3" t="n">
         <v>22</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
+          <t>Cash flow</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>1. Is this row right — the words on screen, the formula, the inputs, the decisions and what it says when it cannot be computed? Say yes, or say what changes.</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>cashflow</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>MK-CF-M-051 — Inflow</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>YOUR ANSWER — use the same number</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26" ht="45" customHeight="1">
+      <c r="A26" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Cash flow</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>1. Is this row right — the words on screen, the formula, the inputs, the decisions and what it says when it cannot be computed? Say yes, or say what changes.</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>cashflow</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>MK-CF-M-052 — Outflow (expenses + debt)</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>YOUR ANSWER — use the same number</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27" ht="45" customHeight="1">
+      <c r="A27" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Cash flow</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>1. Is this row right — the words on screen, the formula, the inputs, the decisions and what it says when it cannot be computed? Say yes, or say what changes.</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>cashflow</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>MK-CF-M-053 — = Surplus</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>YOUR ANSWER — use the same number</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28" ht="45" customHeight="1">
+      <c r="A28" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Cash flow</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>1. Is this row right — the words on screen, the formula, the inputs, the decisions and what it says when it cannot be computed? Say yes, or say what changes.</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>cashflow</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>MK-CF-M-054 — each received line</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>YOUR ANSWER — use the same number</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>1. Is this row right — the words on screen, the formula, the inputs, the decisions and what it says when it cannot be computed? Say yes, or say what changes.
 Q52 — MK-PF-F-026 moneyWeightedReturn is a true personal return — it solves for the rate that makes what you paid in, on the days you paid it in, equal what you have now. It is built, correct and reached by NO SCREEN: the card that showed it was removed by the Performance design you approved on 2026-09-25. The Return the screen does show is a different calculation (Modified Dietz) that also calls itself money-weighted. Do we delete the u</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>multiple_screens</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>MK-XS-M-004 — ▲ up/▼ down $X (Y%) this month · Return · YOUR RETURN</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>YOUR ANSWER — use the same number</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>YOUR ANSWER — use the same number</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
         <is>
           <t>The figure stays DRAFT, and it is on MORE THAN ONE screen — so the answer settles what every screen showing it says.</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr"/>
-    </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>VERIFY 48 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>networth</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>all 48 unverified rows on this tab</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>ROW VERIFIED — founder, date and how</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>The module cannot be called launch-ready: a TESTED row is proved to match the code, not proved to be right.</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr"/>
-    </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>VERIFY 11 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>performance</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>all 11 unverified rows on this tab</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>ROW VERIFIED — founder, date and how</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>The module cannot be called launch-ready: a TESTED row is proved to match the code, not proved to be right.</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr"/>
-    </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Cash flow</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>VERIFY 53 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>cashflow</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>all 53 unverified rows on this tab</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>ROW VERIFIED — founder, date and how</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>The module cannot be called launch-ready: a TESTED row is proved to match the code, not proved to be right.</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr"/>
-    </row>
-    <row r="29" ht="45" customHeight="1">
-      <c r="A29" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>7 decisions on this module are recorded in MY words, not yours — confirm or correct: DEC-0019, DEC-0038, DEC-0045, DEC-0047, DEC-0052, DEC-0061, DEC-0069</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_log_wording-asks_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>Wording asks</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>DEC-0019, DEC-0038, DEC-0045, DEC-0047, DEC-0052, DEC-0061, DEC-0069</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>YOUR WORDING / YES · NO · CHANGE</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>The decision stays marked as my reconstruction, so anything built on it rests on my reading of what you meant.</t>
-        </is>
-      </c>
       <c r="I29" s="3" t="inlineStr"/>
     </row>
-    <row r="30" ht="45" customHeight="1">
+    <row r="30" ht="60" customHeight="1">
       <c r="A30" s="3" t="n">
         <v>27</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Net worth</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>2 decisions on this module are recorded in MY words, not yours — confirm or correct: DEC-0030, DEC-0229</t>
+          <t>VERIFY 48 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_log_wording-asks_v01.xlsx</t>
+          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Wording asks</t>
+          <t>networth</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>DEC-0030, DEC-0229</t>
+          <t>all 48 unverified rows on this tab</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>YOUR WORDING / YES · NO · CHANGE</t>
+          <t>ROW VERIFIED — founder, date and how</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>The decision stays marked as my reconstruction, so anything built on it rests on my reading of what you meant.</t>
+          <t>The module cannot be called launch-ready: a TESTED row is proved to match the code, not proved to be right.</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr"/>
     </row>
-    <row r="31" ht="45" customHeight="1">
+    <row r="31" ht="60" customHeight="1">
       <c r="A31" s="3" t="n">
         <v>28</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Cash flow</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>6 decisions on this module are recorded in MY words, not yours — confirm or correct: DEC-0177, DEC-0178, DEC-0179, DEC-0197, DEC-0201, DEC-0205</t>
+          <t>VERIFY 11 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_log_wording-asks_v01.xlsx</t>
+          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Wording asks</t>
+          <t>performance</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>DEC-0177, DEC-0178, DEC-0179, DEC-0197, DEC-0201, DEC-0205</t>
+          <t>all 11 unverified rows on this tab</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>YOUR WORDING / YES · NO · CHANGE</t>
+          <t>ROW VERIFIED — founder, date and how</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>The decision stays marked as my reconstruction, so anything built on it rests on my reading of what you meant.</t>
+          <t>The module cannot be called launch-ready: a TESTED row is proved to match the code, not proved to be right.</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr"/>
     </row>
-    <row r="32" ht="30" customHeight="1">
+    <row r="32" ht="60" customHeight="1">
       <c r="A32" s="3" t="n">
         <v>29</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Net worth</t>
+          <t>Cash flow</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Plain line - means line graph?</t>
+          <t>VERIFY 53 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
+          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>networth</t>
+          <t>cashflow</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>DEC-0469</t>
+          <t>all 53 unverified rows on this tab</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>Open question on this decision — for him</t>
+          <t>ROW VERIFIED — founder, date and how</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
+          <t>The module cannot be called launch-ready: a TESTED row is proved to match the code, not proved to be right.</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr"/>
@@ -1829,7 +1831,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: what does screen look like for manual update?</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Plain line - means line graph?</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -1844,7 +1846,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>DEC-0470</t>
+          <t>DEC-0469</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -1859,7 +1861,7 @@
       </c>
       <c r="I33" s="3" t="inlineStr"/>
     </row>
-    <row r="34" ht="45" customHeight="1">
+    <row r="34" ht="30" customHeight="1">
       <c r="A34" s="3" t="n">
         <v>31</v>
       </c>
@@ -1870,7 +1872,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: do we capture only balance or all individual portfolio holding e.g. AMZN 100 stocks ….</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: what does screen look like for manual update?</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -1885,7 +1887,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>DEC-0475</t>
+          <t>DEC-0470</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -1900,7 +1902,7 @@
       </c>
       <c r="I34" s="3" t="inlineStr"/>
     </row>
-    <row r="35" ht="60" customHeight="1">
+    <row r="35" ht="45" customHeight="1">
       <c r="A35" s="3" t="n">
         <v>32</v>
       </c>
@@ -1911,7 +1913,7 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: When dividend is captured is it automatically added to income or cash? Similarly, is there a way captical gain is captured and displayed somewhere?</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: do we capture only balance or all individual portfolio holding e.g. AMZN 100 stocks ….</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -1926,7 +1928,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>DEC-0476</t>
+          <t>DEC-0475</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -1941,7 +1943,7 @@
       </c>
       <c r="I35" s="3" t="inlineStr"/>
     </row>
-    <row r="36" ht="30" customHeight="1">
+    <row r="36" ht="60" customHeight="1">
       <c r="A36" s="3" t="n">
         <v>33</v>
       </c>
@@ -1952,7 +1954,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Is this manual, imported or connected and captured via Plaid?</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: When dividend is captured is it automatically added to income or cash? Similarly, is there a way captical gain is captured and displayed somewhere?</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -1967,7 +1969,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>DEC-0478</t>
+          <t>DEC-0476</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -1982,18 +1984,18 @@
       </c>
       <c r="I36" s="3" t="inlineStr"/>
     </row>
-    <row r="37" ht="60" customHeight="1">
+    <row r="37" ht="30" customHeight="1">
       <c r="A37" s="3" t="n">
         <v>34</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Net worth</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Total return captures both realized and unrealized gains? Is there any place we display realized P/L, unrealized P/L, total dividend, and total interest separately?</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Is this manual, imported or connected and captured via Plaid?</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -2003,12 +2005,12 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>performance</t>
+          <t>networth</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>DEC-0479</t>
+          <t>DEC-0478</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -2023,7 +2025,7 @@
       </c>
       <c r="I37" s="3" t="inlineStr"/>
     </row>
-    <row r="38" ht="30" customHeight="1">
+    <row r="38" ht="60" customHeight="1">
       <c r="A38" s="3" t="n">
         <v>35</v>
       </c>
@@ -2034,7 +2036,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: stocks with dividends - will it also show dividends received?</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Total return captures both realized and unrealized gains? Is there any place we display realized P/L, unrealized P/L, total dividend, and total interest separately?</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -2049,7 +2051,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>DEC-0483</t>
+          <t>DEC-0479</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -2075,7 +2077,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: What's the level of details displayed and how?r</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: stocks with dividends - will it also show dividends received?</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -2090,7 +2092,7 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>DEC-0497</t>
+          <t>DEC-0483</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -2116,7 +2118,7 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Invest: what level of detail, and how?</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: What's the level of details displayed and how?r</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -2131,7 +2133,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>DEC-0510</t>
+          <t>DEC-0497</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -2146,18 +2148,18 @@
       </c>
       <c r="I40" s="3" t="inlineStr"/>
     </row>
-    <row r="41" ht="45" customHeight="1">
+    <row r="41" ht="30" customHeight="1">
       <c r="A41" s="3" t="n">
         <v>38</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Cash flow</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: How is income + spending captured, at what frequency, and what about cash / unconnected cards?</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Invest: what level of detail, and how?</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -2167,12 +2169,12 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>cashflow</t>
+          <t>performance</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>DEC-0503</t>
+          <t>DEC-0510</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -2187,7 +2189,7 @@
       </c>
       <c r="I41" s="3" t="inlineStr"/>
     </row>
-    <row r="42" ht="30" customHeight="1">
+    <row r="42" ht="45" customHeight="1">
       <c r="A42" s="3" t="n">
         <v>39</v>
       </c>
@@ -2198,7 +2200,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Are the month bars cash flows -- inflow / outflow?</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: How is income + spending captured, at what frequency, and what about cash / unconnected cards?</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -2213,7 +2215,7 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>DEC-0512</t>
+          <t>DEC-0503</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -2228,43 +2230,43 @@
       </c>
       <c r="I42" s="3" t="inlineStr"/>
     </row>
-    <row r="43" ht="60" customHeight="1">
+    <row r="43" ht="30" customHeight="1">
       <c r="A43" s="3" t="n">
         <v>40</v>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Net worth</t>
+          <t>Cash flow</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Commit — the branch was 278 files behind on 2026-09-14; committed since: 983805a (catch-up), f0e1d6d (Net worth v08), c4f2679 (the Since crash), 727e22a (Performance v14). Nothing is pushed — the branch taxonomy-v1.0.7 is local only.</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Are the month bars cash flows -- inflow / outflow?</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
+          <t>moneykeel_log_decisions_v01.xlsx</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Workplan</t>
+          <t>cashflow</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>Commit — the branch was 278 files behind on 2026-09-14; committed sinc</t>
+          <t>DEC-0512</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>Status / Comments</t>
+          <t>Open question on this decision — for him</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>Founder: say when to PUSH. (Note 2026-09-26: the Xcode licence has not been accepted on this Mac, so the normal git refuses to run — "sudo xcodebuild -license accept" once, then git works everywhere again.)</t>
+          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr"/>
@@ -2280,7 +2282,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>EIGHT live mocks still DRAW words the canon retired (measured 2026-09-26 over the drawn frames, not the commentary): cash-flow this-month v06 ("In (take-home)", "spending") · income end-to-end v07 ("A usual month", "Gross a year") · look-ahead v03 ("/mo") · money-four-tabs v01 ("In (take-home)", "Out (", "/mo", "spending") · account-detail v01 ("Connected ·") · empty-state-pattern v01 ("WHAT YOU O</t>
+          <t>Commit — the branch was 278 files behind on 2026-09-14; committed since: 983805a (catch-up), f0e1d6d (Net worth v08), c4f2679 (the Since crash), 727e22a (Performance v14). Nothing is pushed — the branch taxonomy-v1.0.7 is local only.</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -2295,7 +2297,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>EIGHT live mocks still DRAW words the canon retired (measured 2026-09-</t>
+          <t>Commit — the branch was 278 files behind on 2026-09-14; committed sinc</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -2305,7 +2307,7 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Founder: say whether each gets a new version on the canon now (old archived), or at its next change. Plan v05 already carries its list inside the file as mark 14 and is fixed when v06 is drawn.</t>
+          <t>Founder: say when to PUSH. (Note 2026-09-26: the Xcode licence has not been accepted on this Mac, so the normal git refuses to run — "sudo xcodebuild -license accept" once, then git works everywhere again.)</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr"/>
@@ -2316,12 +2318,12 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Cash flow</t>
+          <t>Net worth</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Stand-in ages when the birth year is missing: the Retirement cockpit and Insights assume 45, the cash-flow model and the draw steer assume 68, the onboarding helper 35 (or 65 for the retirement age). Your rule R2 says an unknown input gives no number and a reason.</t>
+          <t>EIGHT live mocks still DRAW words the canon retired (measured 2026-09-26 over the drawn frames, not the commentary): cash-flow this-month v06 ("In (take-home)", "spending") · income end-to-end v07 ("A usual month", "Gross a year") · look-ahead v03 ("/mo") · money-four-tabs v01 ("In (take-home)", "Out (", "/mo", "spending") · account-detail v01 ("Connected ·") · empty-state-pattern v01 ("WHAT YOU O</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -2336,7 +2338,7 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>Stand-in ages when the birth year is missing: the Retirement cockpit a</t>
+          <t>EIGHT live mocks still DRAW words the canon retired (measured 2026-09-</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
@@ -2346,7 +2348,7 @@
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>Founder: say what those screens show when the birth year is missing (ask for it in place? show the door?); then Claude: mock first, then code</t>
+          <t>Founder: say whether each gets a new version on the canon now (old archived), or at its next change. Plan v05 already carries its list inside the file as mark 14 and is fixed when v06 is drawn.</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr"/>
@@ -2362,7 +2364,7 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Q-CF-2 'how much have I spent this month, against the plan, and what is left' — eight figures DRAFTED on MK-CF-O-003 thisMonth: expected inflow, planned outflow, planned surplus, each planned line, inflow so far, outflow so far, surplus so far, each received line (MK-CF-M-047…054)</t>
+          <t>Stand-in ages when the birth year is missing: the Retirement cockpit and Insights assume 45, the cash-flow model and the draw steer assume 68, the onboarding helper 35 (or 65 for the retirement age). Your rule R2 says an unknown input gives no number and a reason.</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
@@ -2377,7 +2379,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Q-CF-2 'how much have I spent this month, against the plan, and what i</t>
+          <t>Stand-in ages when the birth year is missing: the Retirement cockpit a</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -2387,7 +2389,7 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Founder: read the eight rows on the master's cashflow tab (Row status says DRAFT) and say yes, or say what changes. Claude: the moment you do, the Cash flow screen, the month detail screen and Home's cell move behind the door and stop working figures out themselves</t>
+          <t>Founder: say what those screens show when the birth year is missing (ask for it in place? show the door?); then Claude: mock first, then code</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr"/>
@@ -2398,12 +2400,12 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Net worth</t>
+          <t>Cash flow</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>One door, one term: the three ways to add an account read 'Link it (read-only)', 'Add by hand' and 'Import from a file' on every screen, under the heading 'How do you want to add an account?' — Home, Sharpen your plan, the Plan tab, Net worth (first day and the add sheet), the Connect an account screen and Performance</t>
+          <t>Q-CF-2 'how much have I spent this month, against the plan, and what is left' — eight figures DRAFTED on MK-CF-O-003 thisMonth: expected inflow, planned outflow, planned surplus, each planned line, inflow so far, outflow so far, surplus so far, each received line (MK-CF-M-047…054)</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
@@ -2418,7 +2420,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>One door, one term: the three ways to add an account read 'Link it (re</t>
+          <t>Q-CF-2 'how much have I spent this month, against the plan, and what i</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
@@ -2428,7 +2430,7 @@
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>Founder: approve the mock MoneyKeel/documents/home-screen/moneykeel_pres_mock_ways-to-add-an-account_v10.html (every affected screen, before and after). Claude: then build all of it the same day, with the tests and the canon row</t>
+          <t>Founder: read the eight rows on the master's cashflow tab (Row status says DRAFT) and say yes, or say what changes. Claude: the moment you do, the Cash flow screen, the month detail screen and Home's cell move behind the door and stop working figures out themselves</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr"/>
@@ -2444,7 +2446,7 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Nothing recorded which design each screen was built from. The Build 53 Net worth and Performance finals (networth-FINAL.html, performance-FINAL.html, the two Net worth PDFs, Net worth screens 01 to 11) were filed under networth-and-performance/archive/ on 2026-09-01, which marks them replaced. They were not replaced. Six hours of mocks then started from the wrong files. CORRECTION 2026-09-14: Buil</t>
+          <t>One door, one term: the three ways to add an account read 'Link it (read-only)', 'Add by hand' and 'Import from a file' on every screen, under the heading 'How do you want to add an account?' — Home, Sharpen your plan, the Plan tab, Net worth (first day and the add sheet), the Connect an account screen and Performance</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
@@ -2459,7 +2461,7 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>Nothing recorded which design each screen was built from. The Build 53</t>
+          <t>One door, one term: the three ways to add an account read 'Link it (re</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -2469,7 +2471,7 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>Claude: done 2026-09-14 — Build 53 files matched by exact content and recorded in MoneyKeel/documents/standards/moneykeel_pres_spec_design-each-screen-was-built-from_v01.md. Founder: (1) confirm Net worth = v5 + square corners; (2) say whether to draw Net worth v6 from the Build 53 code (v5 with squ</t>
+          <t>Founder: approve the mock MoneyKeel/documents/home-screen/moneykeel_pres_mock_ways-to-add-an-account_v10.html (every affected screen, before and after). Claude: then build all of it the same day, with the tests and the canon row</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr"/>
@@ -2485,7 +2487,7 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Net worth v07 — the three ways to add an account on Net worth (first day, the add sheet, the add button), plus every ruling since Build 53 that touches the screen (empty state, Debts, Emergency fund, Stocks / Funds, /month, you entered, expenses, odds to the nearest 5), each marked</t>
+          <t>Nothing recorded which design each screen was built from. The Build 53 Net worth and Performance finals (networth-FINAL.html, performance-FINAL.html, the two Net worth PDFs, Net worth screens 01 to 11) were filed under networth-and-performance/archive/ on 2026-09-01, which marks them replaced. They were not replaced. Six hours of mocks then started from the wrong files. CORRECTION 2026-09-14: Buil</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
@@ -2500,7 +2502,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>Net worth v07 — the three ways to add an account on Net worth (first d</t>
+          <t>Nothing recorded which design each screen was built from. The Build 53</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
@@ -2510,7 +2512,7 @@
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Founder: say yes to v08, or name a mark. Also: today's money for the retirement figures and tax on taxable withdrawals (recommended); whether dark/light bars replace the Plan tab's quiet labels. Claude: once approved, record v08 as the current Net worth design, archive v06, then build marks 1–4 and </t>
+          <t>Claude: done 2026-09-14 — Build 53 files matched by exact content and recorded in MoneyKeel/documents/standards/moneykeel_pres_spec_design-each-screen-was-built-from_v01.md. Founder: (1) confirm Net worth = v5 + square corners; (2) say whether to draw Net worth v6 from the Build 53 code (v5 with squ</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr"/>
@@ -2526,7 +2528,7 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>The retirement sentence (Net worth, Plan, Home) prints future dollars without saying so, and the odds calculation charges no tax on withdrawals from taxable accounts — found checking the founder's question on v07 ($4.1M at 65 is about $2.0M in today's money)</t>
+          <t>Net worth v07 — the three ways to add an account on Net worth (first day, the add sheet, the add button), plus every ruling since Build 53 that touches the screen (empty state, Debts, Emergency fund, Stocks / Funds, /month, you entered, expenses, odds to the nearest 5), each marked</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
@@ -2541,7 +2543,7 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The retirement sentence (Net worth, Plan, Home) prints future dollars </t>
+          <t>Net worth v07 — the three ways to add an account on Net worth (first d</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -2551,7 +2553,7 @@
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>Founder: say whether to show today's money and to tax taxable withdrawals (recommended). Claude: then write both as findings on the master rows (MK-XS-M-002 and the pot/leftover figures) before any code.</t>
+          <t xml:space="preserve">Founder: say yes to v08, or name a mark. Also: today's money for the retirement figures and tax on taxable withdrawals (recommended); whether dark/light bars replace the Plan tab's quiet labels. Claude: once approved, record v08 as the current Net worth design, archive v06, then build marks 1–4 and </t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr"/>
@@ -2562,12 +2564,12 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Cash flow</t>
+          <t>Net worth</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Two word collisions found building v08: Cash flow's 'Add by hand' adds an EXPENSE (the same words as the account door), and Settings still says 'Disconnect' beside 'Linked accounts'</t>
+          <t>The retirement sentence (Net worth, Plan, Home) prints future dollars without saying so, and the odds calculation charges no tax on withdrawals from taxable accounts — found checking the founder's question on v07 ($4.1M at 65 is about $2.0M in today's money)</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
@@ -2582,7 +2584,7 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>Two word collisions found building v08: Cash flow's 'Add by hand' adds</t>
+          <t xml:space="preserve">The retirement sentence (Net worth, Plan, Home) prints future dollars </t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
@@ -2592,7 +2594,7 @@
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>Founder: say whether Cash flow's door should read differently (for example 'Add an expense by hand') and whether Disconnect becomes 'Unlink'.</t>
+          <t>Founder: say whether to show today's money and to tax taxable withdrawals (recommended). Claude: then write both as findings on the master rows (MK-XS-M-002 and the pot/leftover figures) before any code.</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr"/>
@@ -2603,43 +2605,84 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Net worth</t>
+          <t>Cash flow</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
+          <t>Two word collisions found building v08: Cash flow's 'Add by hand' adds an EXPENSE (the same words as the account door), and Settings still says 'Disconnect' beside 'Linked accounts'</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Workplan</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Two word collisions found building v08: Cash flow's 'Add by hand' adds</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>Status / Comments</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Founder: say whether Cash flow's door should read differently (for example 'Add an expense by hand') and whether Disconnect becomes 'Unlink'.</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr"/>
+    </row>
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Net worth</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
           <t>LAUNCH ANSWER LIST — 61 things need you for Net worth, Cash flow and Performance to be launch-ready</t>
         </is>
       </c>
-      <c r="D52" s="3" t="inlineStr">
+      <c r="D53" s="3" t="inlineStr">
         <is>
           <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
         </is>
       </c>
-      <c r="E52" s="3" t="inlineStr">
+      <c r="E53" s="3" t="inlineStr">
         <is>
           <t>Workplan</t>
         </is>
       </c>
-      <c r="F52" s="3" t="inlineStr">
+      <c r="F53" s="3" t="inlineStr">
         <is>
           <t>LAUNCH ANSWER LIST — 61 things need you for Net worth, Cash flow and P</t>
         </is>
       </c>
-      <c r="G52" s="3" t="inlineStr">
+      <c r="G53" s="3" t="inlineStr">
         <is>
           <t>Status / Comments</t>
         </is>
       </c>
-      <c r="H52" s="3" t="inlineStr">
+      <c r="H53" s="3" t="inlineStr">
         <is>
           <t>His ask, 2026-09-29: ‘Give me a list of files, tabs, and rows I need to answer for NW, CF, Performance sections of the app to be complete.’ Open MoneyKeel/documents/other/moneykeel_calc_plan_launch-answer-list_v01.xlsx. Five tabs: Read me, EVERYTHING, and one per module. Every line names its FILE, i</t>
         </is>
       </c>
-      <c r="I52" s="3" t="inlineStr"/>
+      <c r="I53" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I52"/>
+  <autoFilter ref="A1:I53"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2650,14 +2693,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
     <col width="51" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
     <col width="52" customWidth="1" min="6" max="6"/>
     <col width="42" customWidth="1" min="7" max="7"/>
     <col width="52" customWidth="1" min="8" max="8"/>
@@ -2667,7 +2710,7 @@
     <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>28 things to answer for Net worth</t>
+          <t>31 things to answer for Net worth</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -2748,7 +2791,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Q32 — The trend survives on a new device but the walk behind it does not. Should the trend say so, or show quietly?</t>
+          <t>1. Is this row right — the words on screen, the formula, the inputs, the decisions and what it says when it cannot be computed? Say yes, or say what changes.</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -2778,7 +2821,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr"/>
     </row>
-    <row r="5" ht="45" customHeight="1">
+    <row r="5" ht="60" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>2</v>
       </c>
@@ -2789,7 +2832,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Q14 — What should a MIXED account be called on screen, when it holds several classes at once?</t>
+          <t>Q17 — "Return on cash + investments" counts money you paid in as a gain. Is the LABEL wrong, or the FORMULA? Fixing the formula means removing deposits and withdrawals before measuring.</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -2804,7 +2847,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-008 — each account and its balance</t>
+          <t>MK-NW-M-002 — Return on cash + investments</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -2819,7 +2862,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr"/>
     </row>
-    <row r="6" ht="45" customHeight="1">
+    <row r="6" ht="60" customHeight="1">
       <c r="A6" s="3" t="n">
         <v>3</v>
       </c>
@@ -2830,7 +2873,8 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Q18 — Net worth projects the pot WITHOUT your big costs; Cash flow, Budget, Goals and Social Security timing all include them. Which is right for the Net worth screen?</t>
+          <t>1. Is this row right — the words on screen, the formula, the inputs, the decisions and what it says when it cannot be computed? Say yes, or say what changes.
+Q32 — The trend survives on a new device but the walk behind it does not. Should the trend say so, or show quietly?</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -2845,7 +2889,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-015 — YOUR RETIREMENT PLAN — on track for $X by age Y</t>
+          <t>MK-NW-M-003 — the trend line</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -2860,7 +2904,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr"/>
     </row>
-    <row r="7" ht="60" customHeight="1">
+    <row r="7" ht="45" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>4</v>
       </c>
@@ -2871,7 +2915,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Q17 — "Return on cash + investments" counts money you paid in as a gain. Is the LABEL wrong, or the FORMULA? Fixing the formula means removing deposits and withdrawals before measuring.</t>
+          <t>1. Is this row right — the words on screen, the formula, the inputs, the decisions and what it says when it cannot be computed? Say yes, or say what changes.</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -2886,7 +2930,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-002 — Return on cash + investments</t>
+          <t>MK-NW-M-006 — 🏠 PERSONAL PROPERTY</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -2945,7 +2989,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr"/>
     </row>
-    <row r="9" ht="45" customHeight="1">
+    <row r="9" ht="60" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>6</v>
       </c>
@@ -2956,7 +3000,8 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Q15 — An institution word we do not recognise: refuse the line and ask you, or book it as unclassified with no direction? The old sign-guess is what minted the $1.4 million.</t>
+          <t>1. Is this row right — the words on screen, the formula, the inputs, the decisions and what it says when it cannot be computed? Say yes, or say what changes.
+Q14 — What should a MIXED account be called on screen, when it holds several classes at once?</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -2971,7 +3016,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-019 — Income</t>
+          <t>MK-NW-M-008 — each account and its balance</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -2986,7 +3031,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr"/>
     </row>
-    <row r="10" ht="45" customHeight="1">
+    <row r="10" ht="60" customHeight="1">
       <c r="A10" s="3" t="n">
         <v>7</v>
       </c>
@@ -2997,7 +3042,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Q01 — Is Quantity for a bond the FACE amount (e.g. 227,000) with the price quoted per $100 of face, or the number of bonds? It decides how value and gain are worked out.</t>
+          <t>Q53 — "Monthly debt payments" on the Net worth screen: the MINIMUM each debt obliges, or what ACTUALLY leaves your account? They part whenever someone pays more than a minimum. On one card — $200 minimum, paid $600 — the minimum reads $200 and the actual reads $600. Both are real figures: the minimum is the obligation a lender can demand (it is what debt-to-income is measured on), the actual is the money that leaves. The screen shows the MINIMUM today, and the label reads like the actual. Which belongs under those words — or should the line say which it is, or show both?</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -3012,7 +3057,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-023 — Face value</t>
+          <t>MK-NW-M-012 — Monthly debt payments</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -3038,7 +3083,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Q04 — "Annual income" on a bond: the last twelve months actually received, or the forward estimate from today\'s coupon? Both are defensible and they differ.</t>
+          <t>1. Is this row right — the words on screen, the formula, the inputs, the decisions and what it says when it cannot be computed? Say yes, or say what changes.</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -3053,7 +3098,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-024 — Interest payments</t>
+          <t>MK-NW-M-015 — YOUR RETIREMENT PLAN — on track for $X by age Y</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -3079,7 +3124,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Q05 — Accrued interest: do we work it out ourselves — which needs a day-count rule per bond type — or only show what the institution gives us?</t>
+          <t>1. Is this row right — the words on screen, the formula, the inputs, the decisions and what it says when it cannot be computed? Say yes, or say what changes.</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -3094,7 +3139,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-026 — Yield if held to maturity</t>
+          <t>MK-NW-M-016 — Net worth so far (setup)</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -3109,7 +3154,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr"/>
     </row>
-    <row r="13" ht="60" customHeight="1">
+    <row r="13" ht="45" customHeight="1">
       <c r="A13" s="3" t="n">
         <v>10</v>
       </c>
@@ -3120,7 +3165,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Q34 — Approve the exact wording for the average-price rule (info dot + column Q): 'Shares with no recorded purchase price are left out of the average. N of your shares are in that position.' — and the refusal: 'Average not available — none of these shares has a recorded price.'</t>
+          <t>Q15 — An institution word we do not recognise: refuse the line and ask you, or book it as unclassified with no direction? The old sign-guess is what minted the $1.4 million.</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -3135,7 +3180,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-032 — Price paid (average)</t>
+          <t>MK-NW-M-019 — Income</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -3150,7 +3195,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr"/>
     </row>
-    <row r="14" ht="60" customHeight="1">
+    <row r="14" ht="45" customHeight="1">
       <c r="A14" s="3" t="n">
         <v>11</v>
       </c>
@@ -3161,8 +3206,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Q35 — Approve the exact label and the canon phrase for the twelve-month window. Proposed: 'Dividends received (trailing twelve months)' here, and 'trailing twelve months' in the other four places (spelled out — no initialism).
-Q36 — Dividends on this card: THIS account only, matching 'Realized from sales' beside it? Recommended: yes.</t>
+          <t>Q01 — Is Quantity for a bond the FACE amount (e.g. 227,000) with the price quoted per $100 of face, or the number of bonds? It decides how value and gain are worked out.</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -3177,7 +3221,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-034 — Dividends received (12 mo)</t>
+          <t>MK-NW-M-023 — Face value</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -3192,7 +3236,7 @@
       </c>
       <c r="I14" s="3" t="inlineStr"/>
     </row>
-    <row r="15" ht="60" customHeight="1">
+    <row r="15" ht="45" customHeight="1">
       <c r="A15" s="3" t="n">
         <v>12</v>
       </c>
@@ -3203,7 +3247,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Q37 — For a connected account: log an 'Opening holding' row per broker lot at first sync (dated the lot's purchase date, at the broker's cost) so every later sale is covered — recommended — or keep 'not counted + say so' for pre-history purchases?</t>
+          <t>Q04 — "Annual income" on a bond: the last twelve months actually received, or the forward estimate from today\'s coupon? Both are defensible and they differ.</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -3218,7 +3262,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-035 — Realized gain from your buys and sells</t>
+          <t>MK-NW-M-024 — Interest payments</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -3233,7 +3277,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr"/>
     </row>
-    <row r="16" ht="60" customHeight="1">
+    <row r="16" ht="45" customHeight="1">
       <c r="A16" s="3" t="n">
         <v>13</v>
       </c>
@@ -3244,7 +3288,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Q20 — A lot with no recorded purchase price is skipped, so its gain is simply absent. Should the screen SAY so — "gain not counted for N shares, no purchase price on record" — rather than quietly reporting less?</t>
+          <t>Q05 — Accrued interest: do we work it out ourselves — which needs a day-count rule per bond type — or only show what the institution gives us?</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -3259,7 +3303,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-036 — Gain — long-term (held over 1 yr)</t>
+          <t>MK-NW-M-026 — Yield if held to maturity</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -3285,269 +3329,270 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
+          <t>Q34 — Approve the exact wording for the average-price rule (info dot + column Q): 'Shares with no recorded purchase price are left out of the average. N of your shares are in that position.' — and the refusal: 'Average not available — none of these shares has a recorded price.'</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>networth</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-M-032 — Price paid (average)</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>YOUR ANSWER — use the same number</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Net worth</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Q35 — Approve the exact label and the canon phrase for the twelve-month window. Proposed: 'Dividends received (trailing twelve months)' here, and 'trailing twelve months' in the other four places (spelled out — no initialism).
+Q36 — Dividends on this card: THIS account only, matching 'Realized from sales' beside it? Recommended: yes.</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>networth</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-M-034 — Dividends received (12 mo)</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>YOUR ANSWER — use the same number</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Net worth</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Q37 — For a connected account: log an 'Opening holding' row per broker lot at first sync (dated the lot's purchase date, at the broker's cost) so every later sale is covered — recommended — or keep 'not counted + say so' for pre-history purchases?</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>networth</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-M-035 — Realized gain from your buys and sells</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>YOUR ANSWER — use the same number</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Net worth</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Q20 — A lot with no recorded purchase price is skipped, so its gain is simply absent. Should the screen SAY so — "gain not counted for N shares, no purchase price on record" — rather than quietly reporting less?</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>networth</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-M-036 — Gain — long-term (held over 1 yr)</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>YOUR ANSWER — use the same number</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Net worth</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
           <t>Q03 — Certificates of deposit: under Fixed Income, or their own class? They carry a term, a rate and an early-withdrawal penalty that a bond does not.
 Q38 — Your bond display rule, three specifics before the mock: (1) 'quantity' for a bond = the number of bonds (each of face $1,000), or the total face amount? (2) 'earned interest' = the INTEREST rows recorded in the ledger for this bond — the only source we have — yes? (3) 'current price' = price per $100 of face as brokers quote it, or the dollar value of the position? Then I mock the bond card and screen before any code.</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>networth</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>MK-NW-M-041 — total value of your bonds</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>YOUR ANSWER — use the same number</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>YOUR ANSWER — use the same number</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
         <is>
           <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr"/>
-    </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="I21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Net worth</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>VERIFY 48 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>networth</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>all 48 unverified rows on this tab</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>ROW VERIFIED — founder, date and how</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>The module cannot be called launch-ready: a TESTED row is proved to match the code, not proved to be right.</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr"/>
-    </row>
-    <row r="19" ht="45" customHeight="1">
-      <c r="A19" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>7 decisions on this module are recorded in MY words, not yours — confirm or correct: DEC-0019, DEC-0038, DEC-0045, DEC-0047, DEC-0052, DEC-0061, DEC-0069</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_log_wording-asks_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>Wording asks</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>DEC-0019, DEC-0038, DEC-0045, DEC-0047, DEC-0052, DEC-0061, DEC-0069</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>YOUR WORDING / YES · NO · CHANGE</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>The decision stays marked as my reconstruction, so anything built on it rests on my reading of what you meant.</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr"/>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="I22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Net worth</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Plain line - means line graph?</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>moneykeel_log_decisions_v01.xlsx</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>networth</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>DEC-0469</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>Open question on this decision — for him</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr"/>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: what does screen look like for manual update?</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>networth</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>DEC-0470</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>Open question on this decision — for him</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr"/>
-    </row>
-    <row r="22" ht="45" customHeight="1">
-      <c r="A22" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: do we capture only balance or all individual portfolio holding e.g. AMZN 100 stocks ….</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>networth</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>DEC-0475</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>Open question on this decision — for him</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr"/>
-    </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: When dividend is captured is it automatically added to income or cash? Similarly, is there a way captical gain is captured and displayed somewhere?</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>networth</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>DEC-0476</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -3564,7 +3609,7 @@
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="3" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
@@ -3573,7 +3618,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Is this manual, imported or connected and captured via Plaid?</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: what does screen look like for manual update?</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -3588,7 +3633,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>DEC-0478</t>
+          <t>DEC-0470</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -3603,9 +3648,9 @@
       </c>
       <c r="I24" s="3" t="inlineStr"/>
     </row>
-    <row r="25" ht="60" customHeight="1">
+    <row r="25" ht="45" customHeight="1">
       <c r="A25" s="3" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
@@ -3614,39 +3659,39 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Commit — the branch was 278 files behind on 2026-09-14; committed since: 983805a (catch-up), f0e1d6d (Net worth v08), c4f2679 (the Since crash), 727e22a (Performance v14). Nothing is pushed — the branch taxonomy-v1.0.7 is local only.</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: do we capture only balance or all individual portfolio holding e.g. AMZN 100 stocks ….</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
+          <t>moneykeel_log_decisions_v01.xlsx</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Workplan</t>
+          <t>networth</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Commit — the branch was 278 files behind on 2026-09-14; committed sinc</t>
+          <t>DEC-0475</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Status / Comments</t>
+          <t>Open question on this decision — for him</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Founder: say when to PUSH. (Note 2026-09-26: the Xcode licence has not been accepted on this Mac, so the normal git refuses to run — "sudo xcodebuild -license accept" once, then git works everywhere again.)</t>
+          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr"/>
     </row>
     <row r="26" ht="60" customHeight="1">
       <c r="A26" s="3" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
@@ -3655,39 +3700,39 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>EIGHT live mocks still DRAW words the canon retired (measured 2026-09-26 over the drawn frames, not the commentary): cash-flow this-month v06 ("In (take-home)", "spending") · income end-to-end v07 ("A usual month", "Gross a year") · look-ahead v03 ("/mo") · money-four-tabs v01 ("In (take-home)", "Out (", "/mo", "spending") · account-detail v01 ("Connected ·") · empty-state-pattern v01 ("WHAT YOU O</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: When dividend is captured is it automatically added to income or cash? Similarly, is there a way captical gain is captured and displayed somewhere?</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
+          <t>moneykeel_log_decisions_v01.xlsx</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Workplan</t>
+          <t>networth</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>EIGHT live mocks still DRAW words the canon retired (measured 2026-09-</t>
+          <t>DEC-0476</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>Status / Comments</t>
+          <t>Open question on this decision — for him</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Founder: say whether each gets a new version on the canon now (old archived), or at its next change. Plan v05 already carries its list inside the file as mark 14 and is fixed when v06 is drawn.</t>
+          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr"/>
     </row>
-    <row r="27" ht="60" customHeight="1">
+    <row r="27" ht="30" customHeight="1">
       <c r="A27" s="3" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
@@ -3696,39 +3741,39 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>One door, one term: the three ways to add an account read 'Link it (read-only)', 'Add by hand' and 'Import from a file' on every screen, under the heading 'How do you want to add an account?' — Home, Sharpen your plan, the Plan tab, Net worth (first day and the add sheet), the Connect an account screen and Performance</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Is this manual, imported or connected and captured via Plaid?</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
+          <t>moneykeel_log_decisions_v01.xlsx</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Workplan</t>
+          <t>networth</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>One door, one term: the three ways to add an account read 'Link it (re</t>
+          <t>DEC-0478</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>Status / Comments</t>
+          <t>Open question on this decision — for him</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Founder: approve the mock MoneyKeel/documents/home-screen/moneykeel_pres_mock_ways-to-add-an-account_v10.html (every affected screen, before and after). Claude: then build all of it the same day, with the tests and the canon row</t>
+          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr"/>
     </row>
     <row r="28" ht="60" customHeight="1">
       <c r="A28" s="3" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
@@ -3737,7 +3782,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Nothing recorded which design each screen was built from. The Build 53 Net worth and Performance finals (networth-FINAL.html, performance-FINAL.html, the two Net worth PDFs, Net worth screens 01 to 11) were filed under networth-and-performance/archive/ on 2026-09-01, which marks them replaced. They were not replaced. Six hours of mocks then started from the wrong files. CORRECTION 2026-09-14: Buil</t>
+          <t>Commit — the branch was 278 files behind on 2026-09-14; committed since: 983805a (catch-up), f0e1d6d (Net worth v08), c4f2679 (the Since crash), 727e22a (Performance v14). Nothing is pushed — the branch taxonomy-v1.0.7 is local only.</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -3752,7 +3797,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Nothing recorded which design each screen was built from. The Build 53</t>
+          <t>Commit — the branch was 278 files behind on 2026-09-14; committed sinc</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -3762,14 +3807,14 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Claude: done 2026-09-14 — Build 53 files matched by exact content and recorded in MoneyKeel/documents/standards/moneykeel_pres_spec_design-each-screen-was-built-from_v01.md. Founder: (1) confirm Net worth = v5 + square corners; (2) say whether to draw Net worth v6 from the Build 53 code (v5 with squ</t>
+          <t>Founder: say when to PUSH. (Note 2026-09-26: the Xcode licence has not been accepted on this Mac, so the normal git refuses to run — "sudo xcodebuild -license accept" once, then git works everywhere again.)</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr"/>
     </row>
     <row r="29" ht="60" customHeight="1">
       <c r="A29" s="3" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
@@ -3778,7 +3823,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Net worth v07 — the three ways to add an account on Net worth (first day, the add sheet, the add button), plus every ruling since Build 53 that touches the screen (empty state, Debts, Emergency fund, Stocks / Funds, /month, you entered, expenses, odds to the nearest 5), each marked</t>
+          <t>EIGHT live mocks still DRAW words the canon retired (measured 2026-09-26 over the drawn frames, not the commentary): cash-flow this-month v06 ("In (take-home)", "spending") · income end-to-end v07 ("A usual month", "Gross a year") · look-ahead v03 ("/mo") · money-four-tabs v01 ("In (take-home)", "Out (", "/mo", "spending") · account-detail v01 ("Connected ·") · empty-state-pattern v01 ("WHAT YOU O</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -3793,7 +3838,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Net worth v07 — the three ways to add an account on Net worth (first d</t>
+          <t>EIGHT live mocks still DRAW words the canon retired (measured 2026-09-</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -3803,14 +3848,14 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Founder: say yes to v08, or name a mark. Also: today's money for the retirement figures and tax on taxable withdrawals (recommended); whether dark/light bars replace the Plan tab's quiet labels. Claude: once approved, record v08 as the current Net worth design, archive v06, then build marks 1–4 and </t>
+          <t>Founder: say whether each gets a new version on the canon now (old archived), or at its next change. Plan v05 already carries its list inside the file as mark 14 and is fixed when v06 is drawn.</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr"/>
     </row>
     <row r="30" ht="60" customHeight="1">
       <c r="A30" s="3" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
@@ -3819,7 +3864,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>The retirement sentence (Net worth, Plan, Home) prints future dollars without saying so, and the odds calculation charges no tax on withdrawals from taxable accounts — found checking the founder's question on v07 ($4.1M at 65 is about $2.0M in today's money)</t>
+          <t>One door, one term: the three ways to add an account read 'Link it (read-only)', 'Add by hand' and 'Import from a file' on every screen, under the heading 'How do you want to add an account?' — Home, Sharpen your plan, the Plan tab, Net worth (first day and the add sheet), the Connect an account screen and Performance</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -3834,7 +3879,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The retirement sentence (Net worth, Plan, Home) prints future dollars </t>
+          <t>One door, one term: the three ways to add an account read 'Link it (re</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -3844,14 +3889,14 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Founder: say whether to show today's money and to tax taxable withdrawals (recommended). Claude: then write both as findings on the master rows (MK-XS-M-002 and the pot/leftover figures) before any code.</t>
+          <t>Founder: approve the mock MoneyKeel/documents/home-screen/moneykeel_pres_mock_ways-to-add-an-account_v10.html (every affected screen, before and after). Claude: then build all of it the same day, with the tests and the canon row</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr"/>
     </row>
     <row r="31" ht="60" customHeight="1">
       <c r="A31" s="3" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
@@ -3860,38 +3905,161 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
+          <t>Nothing recorded which design each screen was built from. The Build 53 Net worth and Performance finals (networth-FINAL.html, performance-FINAL.html, the two Net worth PDFs, Net worth screens 01 to 11) were filed under networth-and-performance/archive/ on 2026-09-01, which marks them replaced. They were not replaced. Six hours of mocks then started from the wrong files. CORRECTION 2026-09-14: Buil</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Workplan</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Nothing recorded which design each screen was built from. The Build 53</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>Status / Comments</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Claude: done 2026-09-14 — Build 53 files matched by exact content and recorded in MoneyKeel/documents/standards/moneykeel_pres_spec_design-each-screen-was-built-from_v01.md. Founder: (1) confirm Net worth = v5 + square corners; (2) say whether to draw Net worth v6 from the Build 53 code (v5 with squ</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Net worth</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Net worth v07 — the three ways to add an account on Net worth (first day, the add sheet, the add button), plus every ruling since Build 53 that touches the screen (empty state, Debts, Emergency fund, Stocks / Funds, /month, you entered, expenses, odds to the nearest 5), each marked</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Workplan</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Net worth v07 — the three ways to add an account on Net worth (first d</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Status / Comments</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Founder: say yes to v08, or name a mark. Also: today's money for the retirement figures and tax on taxable withdrawals (recommended); whether dark/light bars replace the Plan tab's quiet labels. Claude: once approved, record v08 as the current Net worth design, archive v06, then build marks 1–4 and </t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr"/>
+    </row>
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Net worth</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>The retirement sentence (Net worth, Plan, Home) prints future dollars without saying so, and the odds calculation charges no tax on withdrawals from taxable accounts — found checking the founder's question on v07 ($4.1M at 65 is about $2.0M in today's money)</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Workplan</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The retirement sentence (Net worth, Plan, Home) prints future dollars </t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>Status / Comments</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Founder: say whether to show today's money and to tax taxable withdrawals (recommended). Claude: then write both as findings on the master rows (MK-XS-M-002 and the pot/leftover figures) before any code.</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Net worth</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
           <t>LAUNCH ANSWER LIST — 61 things need you for Net worth, Cash flow and Performance to be launch-ready</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t>Workplan</t>
         </is>
       </c>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="F34" s="3" t="inlineStr">
         <is>
           <t>LAUNCH ANSWER LIST — 61 things need you for Net worth, Cash flow and P</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="G34" s="3" t="inlineStr">
         <is>
           <t>Status / Comments</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr">
+      <c r="H34" s="3" t="inlineStr">
         <is>
           <t>His ask, 2026-09-29: ‘Give me a list of files, tabs, and rows I need to answer for NW, CF, Performance sections of the app to be complete.’ Open MoneyKeel/documents/other/moneykeel_calc_plan_launch-answer-list_v01.xlsx. Five tabs: Read me, EVERYTHING, and one per module. Every line names its FILE, i</t>
         </is>
       </c>
-      <c r="I31" s="3" t="inlineStr"/>
+      <c r="I34" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I31"/>
+  <autoFilter ref="A1:I34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3902,14 +4070,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
     <col width="51" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
     <col width="52" customWidth="1" min="6" max="6"/>
     <col width="42" customWidth="1" min="7" max="7"/>
     <col width="52" customWidth="1" min="8" max="8"/>
@@ -3919,7 +4087,7 @@
     <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>13 things to answer for Cash flow</t>
+          <t>12 things to answer for Cash flow</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -3991,7 +4159,7 @@
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="3" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
@@ -4032,7 +4200,7 @@
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="3" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -4073,7 +4241,7 @@
     </row>
     <row r="6" ht="45" customHeight="1">
       <c r="A6" s="3" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -4114,7 +4282,7 @@
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="3" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
@@ -4155,7 +4323,7 @@
     </row>
     <row r="8" ht="45" customHeight="1">
       <c r="A8" s="3" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
@@ -4196,7 +4364,7 @@
     </row>
     <row r="9" ht="45" customHeight="1">
       <c r="A9" s="3" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
@@ -4237,7 +4405,7 @@
     </row>
     <row r="10" ht="60" customHeight="1">
       <c r="A10" s="3" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
@@ -4278,7 +4446,7 @@
     </row>
     <row r="11" ht="45" customHeight="1">
       <c r="A11" s="3" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
@@ -4287,39 +4455,39 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>6 decisions on this module are recorded in MY words, not yours — confirm or correct: DEC-0177, DEC-0178, DEC-0179, DEC-0197, DEC-0201, DEC-0205</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: How is income + spending captured, at what frequency, and what about cash / unconnected cards?</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_log_wording-asks_v01.xlsx</t>
+          <t>moneykeel_log_decisions_v01.xlsx</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Wording asks</t>
+          <t>cashflow</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>DEC-0177, DEC-0178, DEC-0179, DEC-0197, DEC-0201, DEC-0205</t>
+          <t>DEC-0503</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>YOUR WORDING / YES · NO · CHANGE</t>
+          <t>Open question on this decision — for him</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>The decision stays marked as my reconstruction, so anything built on it rests on my reading of what you meant.</t>
+          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr"/>
     </row>
-    <row r="12" ht="45" customHeight="1">
+    <row r="12" ht="30" customHeight="1">
       <c r="A12" s="3" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
@@ -4328,7 +4496,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: How is income + spending captured, at what frequency, and what about cash / unconnected cards?</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Are the month bars cash flows -- inflow / outflow?</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -4343,7 +4511,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>DEC-0503</t>
+          <t>DEC-0512</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -4358,9 +4526,9 @@
       </c>
       <c r="I12" s="3" t="inlineStr"/>
     </row>
-    <row r="13" ht="30" customHeight="1">
+    <row r="13" ht="60" customHeight="1">
       <c r="A13" s="3" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
@@ -4369,39 +4537,39 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Are the month bars cash flows -- inflow / outflow?</t>
+          <t>Stand-in ages when the birth year is missing: the Retirement cockpit and Insights assume 45, the cash-flow model and the draw steer assume 68, the onboarding helper 35 (or 65 for the retirement age). Your rule R2 says an unknown input gives no number and a reason.</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
+          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>cashflow</t>
+          <t>Workplan</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>DEC-0512</t>
+          <t>Stand-in ages when the birth year is missing: the Retirement cockpit a</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Open question on this decision — for him</t>
+          <t>Status / Comments</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
+          <t>Founder: say what those screens show when the birth year is missing (ask for it in place? show the door?); then Claude: mock first, then code</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr"/>
     </row>
     <row r="14" ht="60" customHeight="1">
       <c r="A14" s="3" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
@@ -4410,7 +4578,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Stand-in ages when the birth year is missing: the Retirement cockpit and Insights assume 45, the cash-flow model and the draw steer assume 68, the onboarding helper 35 (or 65 for the retirement age). Your rule R2 says an unknown input gives no number and a reason.</t>
+          <t>Q-CF-2 'how much have I spent this month, against the plan, and what is left' — eight figures DRAFTED on MK-CF-O-003 thisMonth: expected inflow, planned outflow, planned surplus, each planned line, inflow so far, outflow so far, surplus so far, each received line (MK-CF-M-047…054)</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -4425,7 +4593,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Stand-in ages when the birth year is missing: the Retirement cockpit a</t>
+          <t>Q-CF-2 'how much have I spent this month, against the plan, and what i</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -4435,14 +4603,14 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Founder: say what those screens show when the birth year is missing (ask for it in place? show the door?); then Claude: mock first, then code</t>
+          <t>Founder: read the eight rows on the master's cashflow tab (Row status says DRAFT) and say yes, or say what changes. Claude: the moment you do, the Cash flow screen, the month detail screen and Home's cell move behind the door and stop working figures out themselves</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr"/>
     </row>
     <row r="15" ht="60" customHeight="1">
       <c r="A15" s="3" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
@@ -4451,7 +4619,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Q-CF-2 'how much have I spent this month, against the plan, and what is left' — eight figures DRAFTED on MK-CF-O-003 thisMonth: expected inflow, planned outflow, planned surplus, each planned line, inflow so far, outflow so far, surplus so far, each received line (MK-CF-M-047…054)</t>
+          <t>Two word collisions found building v08: Cash flow's 'Add by hand' adds an EXPENSE (the same words as the account door), and Settings still says 'Disconnect' beside 'Linked accounts'</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -4466,7 +4634,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Q-CF-2 'how much have I spent this month, against the plan, and what i</t>
+          <t>Two word collisions found building v08: Cash flow's 'Add by hand' adds</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -4476,54 +4644,13 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Founder: read the eight rows on the master's cashflow tab (Row status says DRAFT) and say yes, or say what changes. Claude: the moment you do, the Cash flow screen, the month detail screen and Home's cell move behind the door and stop working figures out themselves</t>
+          <t>Founder: say whether Cash flow's door should read differently (for example 'Add an expense by hand') and whether Disconnect becomes 'Unlink'.</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr"/>
     </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Cash flow</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Two word collisions found building v08: Cash flow's 'Add by hand' adds an EXPENSE (the same words as the account door), and Settings still says 'Disconnect' beside 'Linked accounts'</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>Workplan</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>Two word collisions found building v08: Cash flow's 'Add by hand' adds</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>Status / Comments</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>Founder: say whether Cash flow's door should read differently (for example 'Add an expense by hand') and whether Disconnect becomes 'Unlink'.</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I16"/>
+  <autoFilter ref="A1:I15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4534,7 +4661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -4551,7 +4678,7 @@
     <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>8 things to answer for Performance</t>
+          <t>7 things to answer for Performance</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -4623,7 +4750,7 @@
     </row>
     <row r="4" ht="60" customHeight="1">
       <c r="A4" s="3" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
@@ -4666,7 +4793,7 @@
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="3" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -4708,7 +4835,7 @@
     </row>
     <row r="6" ht="60" customHeight="1">
       <c r="A6" s="3" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -4747,9 +4874,9 @@
       </c>
       <c r="I6" s="3" t="inlineStr"/>
     </row>
-    <row r="7" ht="45" customHeight="1">
+    <row r="7" ht="60" customHeight="1">
       <c r="A7" s="3" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
@@ -4758,39 +4885,39 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>2 decisions on this module are recorded in MY words, not yours — confirm or correct: DEC-0030, DEC-0229</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Total return captures both realized and unrealized gains? Is there any place we display realized P/L, unrealized P/L, total dividend, and total interest separately?</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_log_wording-asks_v01.xlsx</t>
+          <t>moneykeel_log_decisions_v01.xlsx</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Wording asks</t>
+          <t>performance</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>DEC-0030, DEC-0229</t>
+          <t>DEC-0479</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>YOUR WORDING / YES · NO · CHANGE</t>
+          <t>Open question on this decision — for him</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>The decision stays marked as my reconstruction, so anything built on it rests on my reading of what you meant.</t>
+          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr"/>
     </row>
-    <row r="8" ht="60" customHeight="1">
+    <row r="8" ht="30" customHeight="1">
       <c r="A8" s="3" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
@@ -4799,7 +4926,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Total return captures both realized and unrealized gains? Is there any place we display realized P/L, unrealized P/L, total dividend, and total interest separately?</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: stocks with dividends - will it also show dividends received?</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -4814,7 +4941,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>DEC-0479</t>
+          <t>DEC-0483</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -4831,7 +4958,7 @@
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="3" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
@@ -4840,7 +4967,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: stocks with dividends - will it also show dividends received?</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: What's the level of details displayed and how?r</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -4855,7 +4982,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>DEC-0483</t>
+          <t>DEC-0497</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -4872,7 +4999,7 @@
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="3" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
@@ -4881,7 +5008,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: What's the level of details displayed and how?r</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Invest: what level of detail, and how?</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -4896,7 +5023,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>DEC-0497</t>
+          <t>DEC-0510</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -4911,49 +5038,8 @@
       </c>
       <c r="I10" s="3" t="inlineStr"/>
     </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="3" t="n">
-        <v>37</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Invest: what level of detail, and how?</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>performance</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>DEC-0510</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>Open question on this decision — for him</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I11"/>
+  <autoFilter ref="A1:I10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_launch-answer-list_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_launch-answer-list_v01.xlsx
@@ -14,10 +14,10 @@
     <sheet name="Performance" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'EVERYTHING'!$A$1:$I$53</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Net worth'!$A$1:$I$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Cash flow'!$A$1:$I$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Performance'!$A$1:$I$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'EVERYTHING'!$A$1:$I$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Net worth'!$A$1:$I$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Cash flow'!$A$1:$I$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Performance'!$A$1:$I$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -534,14 +534,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
     <col width="51" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
     <col width="52" customWidth="1" min="6" max="6"/>
     <col width="42" customWidth="1" min="7" max="7"/>
     <col width="52" customWidth="1" min="8" max="8"/>
@@ -551,7 +551,7 @@
     <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>50 things to answer</t>
+          <t>37 things to answer</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -621,7 +621,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="45" customHeight="1">
+    <row r="4" ht="60" customHeight="1">
       <c r="A4" s="3" t="n">
         <v>1</v>
       </c>
@@ -632,7 +632,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>1. Is this row right — the words on screen, the formula, the inputs, the decisions and what it says when it cannot be computed? Say yes, or say what changes.</t>
+          <t>Q17 — "Return on cash + investments" counts money you paid in as a gain. Is the LABEL wrong, or the FORMULA? Fixing the formula means removing deposits and withdrawals before measuring.</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-001 — Change in net worth +$X</t>
+          <t>MK-NW-M-002 — Return on cash + investments</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr"/>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="45" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>2</v>
       </c>
@@ -673,7 +673,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Q17 — "Return on cash + investments" counts money you paid in as a gain. Is the LABEL wrong, or the FORMULA? Fixing the formula means removing deposits and withdrawals before measuring.</t>
+          <t>Q32 — The trend survives on a new device but the walk behind it does not. Should the trend say so, or show quietly?</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-002 — Return on cash + investments</t>
+          <t>MK-NW-M-003 — the trend line</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -713,89 +713,6 @@
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>1. Is this row right — the words on screen, the formula, the inputs, the decisions and what it says when it cannot be computed? Say yes, or say what changes.
-Q32 — The trend survives on a new device but the walk behind it does not. Should the trend say so, or show quietly?</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>networth</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>MK-NW-M-003 — the trend line</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>YOUR ANSWER — use the same number</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr"/>
-    </row>
-    <row r="7" ht="45" customHeight="1">
-      <c r="A7" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>1. Is this row right — the words on screen, the formula, the inputs, the decisions and what it says when it cannot be computed? Say yes, or say what changes.</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>networth</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>MK-NW-M-006 — 🏠 PERSONAL PROPERTY</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>YOUR ANSWER — use the same number</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr"/>
-    </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Q10 — What order of evidence decides an asset's class? Draft: the institution's own class field, then the shape of the identifier (option symbols, nine-character bond numbers, currency codes), then words in the name, then ask you.
 Q11 — When nothing matches: refuse the line and ask, or park it as unclassified? Parking keeps the totals right and hides a gap; refusing is honest and stops the import.
@@ -803,6 +720,88 @@
 Q13 — Commodities: is a fund that </t>
         </is>
       </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>networth</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-M-007 — class rows — by class, institution or type</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>YOUR ANSWER — use the same number</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7" ht="45" customHeight="1">
+      <c r="A7" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Net worth</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Q14 — What should a MIXED account be called on screen, when it holds several classes at once?</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>networth</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-M-008 — each account and its balance</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>YOUR ANSWER — use the same number</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8" ht="45" customHeight="1">
+      <c r="A8" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Net worth</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Q15 — An institution word we do not recognise: refuse the line and ask you, or book it as unclassified with no direction? The old sign-guess is what minted the $1.4 million.</t>
+        </is>
+      </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
           <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
@@ -815,7 +814,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-007 — class rows — by class, institution or type</t>
+          <t>MK-NW-M-019 — Income</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -830,7 +829,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr"/>
     </row>
-    <row r="9" ht="60" customHeight="1">
+    <row r="9" ht="45" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>6</v>
       </c>
@@ -841,8 +840,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>1. Is this row right — the words on screen, the formula, the inputs, the decisions and what it says when it cannot be computed? Say yes, or say what changes.
-Q14 — What should a MIXED account be called on screen, when it holds several classes at once?</t>
+          <t>Q01 — Is Quantity for a bond the FACE amount (e.g. 227,000) with the price quoted per $100 of face, or the number of bonds? It decides how value and gain are worked out.</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -857,7 +855,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-008 — each account and its balance</t>
+          <t>MK-NW-M-023 — Face value</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -872,7 +870,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr"/>
     </row>
-    <row r="10" ht="60" customHeight="1">
+    <row r="10" ht="45" customHeight="1">
       <c r="A10" s="3" t="n">
         <v>7</v>
       </c>
@@ -883,7 +881,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Q53 — "Monthly debt payments" on the Net worth screen: the MINIMUM each debt obliges, or what ACTUALLY leaves your account? They part whenever someone pays more than a minimum. On one card — $200 minimum, paid $600 — the minimum reads $200 and the actual reads $600. Both are real figures: the minimum is the obligation a lender can demand (it is what debt-to-income is measured on), the actual is the money that leaves. The screen shows the MINIMUM today, and the label reads like the actual. Which belongs under those words — or should the line say which it is, or show both?</t>
+          <t>Q04 — "Annual income" on a bond: the last twelve months actually received, or the forward estimate from today\'s coupon? Both are defensible and they differ.</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -898,7 +896,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-012 — Monthly debt payments</t>
+          <t>MK-NW-M-024 — Interest payments</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -924,7 +922,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>1. Is this row right — the words on screen, the formula, the inputs, the decisions and what it says when it cannot be computed? Say yes, or say what changes.</t>
+          <t>Q05 — Accrued interest: do we work it out ourselves — which needs a day-count rule per bond type — or only show what the institution gives us?</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -939,7 +937,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-015 — YOUR RETIREMENT PLAN — on track for $X by age Y</t>
+          <t>MK-NW-M-026 — Yield if held to maturity</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -954,7 +952,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr"/>
     </row>
-    <row r="12" ht="45" customHeight="1">
+    <row r="12" ht="60" customHeight="1">
       <c r="A12" s="3" t="n">
         <v>9</v>
       </c>
@@ -965,7 +963,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>1. Is this row right — the words on screen, the formula, the inputs, the decisions and what it says when it cannot be computed? Say yes, or say what changes.</t>
+          <t>Q34 — Approve the exact wording for the average-price rule (info dot + column Q): 'Shares with no recorded purchase price are left out of the average. N of your shares are in that position.' — and the refusal: 'Average not available — none of these shares has a recorded price.'</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -980,7 +978,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-016 — Net worth so far (setup)</t>
+          <t>MK-NW-M-032 — Price paid (average)</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -995,7 +993,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr"/>
     </row>
-    <row r="13" ht="45" customHeight="1">
+    <row r="13" ht="60" customHeight="1">
       <c r="A13" s="3" t="n">
         <v>10</v>
       </c>
@@ -1006,7 +1004,8 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Q15 — An institution word we do not recognise: refuse the line and ask you, or book it as unclassified with no direction? The old sign-guess is what minted the $1.4 million.</t>
+          <t>Q35 — Approve the exact label and the canon phrase for the twelve-month window. Proposed: 'Dividends received (trailing twelve months)' here, and 'trailing twelve months' in the other four places (spelled out — no initialism).
+Q36 — Dividends on this card: THIS account only, matching 'Realized from sales' beside it? Recommended: yes.</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -1021,7 +1020,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-019 — Income</t>
+          <t>MK-NW-M-034 — Dividends received (12 mo)</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1036,7 +1035,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr"/>
     </row>
-    <row r="14" ht="45" customHeight="1">
+    <row r="14" ht="60" customHeight="1">
       <c r="A14" s="3" t="n">
         <v>11</v>
       </c>
@@ -1047,7 +1046,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Q01 — Is Quantity for a bond the FACE amount (e.g. 227,000) with the price quoted per $100 of face, or the number of bonds? It decides how value and gain are worked out.</t>
+          <t>Q37 — For a connected account: log an 'Opening holding' row per broker lot at first sync (dated the lot's purchase date, at the broker's cost) so every later sale is covered — recommended — or keep 'not counted + say so' for pre-history purchases?</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -1062,7 +1061,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-023 — Face value</t>
+          <t>MK-NW-M-035 — Realized gain from your buys and sells</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -1077,7 +1076,7 @@
       </c>
       <c r="I14" s="3" t="inlineStr"/>
     </row>
-    <row r="15" ht="45" customHeight="1">
+    <row r="15" ht="60" customHeight="1">
       <c r="A15" s="3" t="n">
         <v>12</v>
       </c>
@@ -1088,7 +1087,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Q04 — "Annual income" on a bond: the last twelve months actually received, or the forward estimate from today\'s coupon? Both are defensible and they differ.</t>
+          <t>Q20 — A lot with no recorded purchase price is skipped, so its gain is simply absent. Should the screen SAY so — "gain not counted for N shares, no purchase price on record" — rather than quietly reporting less?</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -1103,7 +1102,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-024 — Interest payments</t>
+          <t>MK-NW-M-036 — Gain — long-term (held over 1 yr)</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1118,7 +1117,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr"/>
     </row>
-    <row r="16" ht="45" customHeight="1">
+    <row r="16" ht="60" customHeight="1">
       <c r="A16" s="3" t="n">
         <v>13</v>
       </c>
@@ -1129,7 +1128,8 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Q05 — Accrued interest: do we work it out ourselves — which needs a day-count rule per bond type — or only show what the institution gives us?</t>
+          <t>Q03 — Certificates of deposit: under Fixed Income, or their own class? They carry a term, a rate and an early-withdrawal penalty that a bond does not.
+Q38 — Your bond display rule, three specifics before the mock: (1) 'quantity' for a bond = the number of bonds (each of face $1,000), or the total face amount? (2) 'earned interest' = the INTEREST rows recorded in the ledger for this bond — the only source we have — yes? (3) 'current price' = price per $100 of face as brokers quote it, or the dollar value of the position? Then I mock the bond card and screen before any code.</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-026 — Yield if held to maturity</t>
+          <t>MK-NW-M-041 — total value of your bonds</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Q34 — Approve the exact wording for the average-price rule (info dot + column Q): 'Shares with no recorded purchase price are left out of the average. N of your shares are in that position.' — and the refusal: 'Average not available — none of these shares has a recorded price.'</t>
+          <t>VERIFY 48 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-032 — Price paid (average)</t>
+          <t>all 48 unverified rows on this tab</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>YOUR ANSWER — use the same number</t>
+          <t>ROW VERIFIED — founder, date and how</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+          <t>The module cannot be called launch-ready: a TESTED row is proved to match the code, not proved to be right.</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr"/>
@@ -1206,13 +1206,12 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Net worth</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Q35 — Approve the exact label and the canon phrase for the twelve-month window. Proposed: 'Dividends received (trailing twelve months)' here, and 'trailing twelve months' in the other four places (spelled out — no initialism).
-Q36 — Dividends on this card: THIS account only, matching 'Realized from sales' beside it? Recommended: yes.</t>
+          <t>VERIFY 11 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -1222,22 +1221,22 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>networth</t>
+          <t>performance</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-034 — Dividends received (12 mo)</t>
+          <t>all 11 unverified rows on this tab</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>YOUR ANSWER — use the same number</t>
+          <t>ROW VERIFIED — founder, date and how</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+          <t>The module cannot be called launch-ready: a TESTED row is proved to match the code, not proved to be right.</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr"/>
@@ -1248,12 +1247,12 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Net worth</t>
+          <t>Cash flow</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Q37 — For a connected account: log an 'Opening holding' row per broker lot at first sync (dated the lot's purchase date, at the broker's cost) so every later sale is covered — recommended — or keep 'not counted + say so' for pre-history purchases?</t>
+          <t>VERIFY 53 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -1263,27 +1262,27 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>networth</t>
+          <t>cashflow</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-035 — Realized gain from your buys and sells</t>
+          <t>all 53 unverified rows on this tab</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>YOUR ANSWER — use the same number</t>
+          <t>ROW VERIFIED — founder, date and how</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+          <t>The module cannot be called launch-ready: a TESTED row is proved to match the code, not proved to be right.</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr"/>
     </row>
-    <row r="20" ht="60" customHeight="1">
+    <row r="20" ht="30" customHeight="1">
       <c r="A20" s="3" t="n">
         <v>17</v>
       </c>
@@ -1294,12 +1293,12 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Q20 — A lot with no recorded purchase price is skipped, so its gain is simply absent. Should the screen SAY so — "gain not counted for N shares, no purchase price on record" — rather than quietly reporting less?</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Plain line - means line graph?</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+          <t>moneykeel_log_decisions_v01.xlsx</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -1309,22 +1308,22 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-036 — Gain — long-term (held over 1 yr)</t>
+          <t>DEC-0469</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>YOUR ANSWER — use the same number</t>
+          <t>Open question on this decision — for him</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr"/>
     </row>
-    <row r="21" ht="60" customHeight="1">
+    <row r="21" ht="30" customHeight="1">
       <c r="A21" s="3" t="n">
         <v>18</v>
       </c>
@@ -1335,13 +1334,12 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Q03 — Certificates of deposit: under Fixed Income, or their own class? They carry a term, a rate and an early-withdrawal penalty that a bond does not.
-Q38 — Your bond display rule, three specifics before the mock: (1) 'quantity' for a bond = the number of bonds (each of face $1,000), or the total face amount? (2) 'earned interest' = the INTEREST rows recorded in the ledger for this bond — the only source we have — yes? (3) 'current price' = price per $100 of face as brokers quote it, or the dollar value of the position? Then I mock the bond card and screen before any code.</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: what does screen look like for manual update?</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+          <t>moneykeel_log_decisions_v01.xlsx</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -1351,389 +1349,386 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-041 — total value of your bonds</t>
+          <t>DEC-0470</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>YOUR ANSWER — use the same number</t>
+          <t>Open question on this decision — for him</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr"/>
     </row>
-    <row r="22" ht="60" customHeight="1">
+    <row r="22" ht="45" customHeight="1">
       <c r="A22" s="3" t="n">
         <v>19</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Net worth</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>1. Is this row right — the words on screen, the formula, the inputs, the decisions and what it says when it cannot be computed? Say yes, or say what changes.
-Q33 — Which index should each asset class be compared against, and should the person be able to change it?
-Q51 — Home reads "you +3.69% · market +2.83% · ahead by 0.85%". The two sides are not measured the same way: YOUR figure counts the dividends and interest you received (your ruling of 2026-09-25, one meaning of return), while the MARKET figure is the index's PRICE only, because no price feed we have gives an index's dividends. So "</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: do we capture only balance or all individual portfolio holding e.g. AMZN 100 stocks ….</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+          <t>moneykeel_log_decisions_v01.xlsx</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>performance</t>
+          <t>networth</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>MK-PF-M-008 — market +X%</t>
+          <t>DEC-0475</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>YOUR ANSWER — use the same number</t>
+          <t>Open question on this decision — for him</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr"/>
     </row>
-    <row r="23" ht="45" customHeight="1">
+    <row r="23" ht="60" customHeight="1">
       <c r="A23" s="3" t="n">
         <v>20</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Cash flow</t>
+          <t>Net worth</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>1. Is this row right — the words on screen, the formula, the inputs, the decisions and what it says when it cannot be computed? Say yes, or say what changes.</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: When dividend is captured is it automatically added to income or cash? Similarly, is there a way captical gain is captured and displayed somewhere?</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+          <t>moneykeel_log_decisions_v01.xlsx</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>cashflow</t>
+          <t>networth</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>MK-CF-M-049 — = Planned surplus</t>
+          <t>DEC-0476</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>YOUR ANSWER — use the same number</t>
+          <t>Open question on this decision — for him</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr"/>
     </row>
-    <row r="24" ht="45" customHeight="1">
+    <row r="24" ht="30" customHeight="1">
       <c r="A24" s="3" t="n">
         <v>21</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Cash flow</t>
+          <t>Net worth</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>1. Is this row right — the words on screen, the formula, the inputs, the decisions and what it says when it cannot be computed? Say yes, or say what changes.</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Is this manual, imported or connected and captured via Plaid?</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+          <t>moneykeel_log_decisions_v01.xlsx</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>cashflow</t>
+          <t>networth</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>MK-CF-M-050 — each planned line</t>
+          <t>DEC-0478</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>YOUR ANSWER — use the same number</t>
+          <t>Open question on this decision — for him</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr"/>
     </row>
-    <row r="25" ht="45" customHeight="1">
+    <row r="25" ht="60" customHeight="1">
       <c r="A25" s="3" t="n">
         <v>22</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Cash flow</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>1. Is this row right — the words on screen, the formula, the inputs, the decisions and what it says when it cannot be computed? Say yes, or say what changes.</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Total return captures both realized and unrealized gains? Is there any place we display realized P/L, unrealized P/L, total dividend, and total interest separately?</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+          <t>moneykeel_log_decisions_v01.xlsx</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>cashflow</t>
+          <t>performance</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>MK-CF-M-051 — Inflow</t>
+          <t>DEC-0479</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>YOUR ANSWER — use the same number</t>
+          <t>Open question on this decision — for him</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr"/>
     </row>
-    <row r="26" ht="45" customHeight="1">
+    <row r="26" ht="30" customHeight="1">
       <c r="A26" s="3" t="n">
         <v>23</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Cash flow</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>1. Is this row right — the words on screen, the formula, the inputs, the decisions and what it says when it cannot be computed? Say yes, or say what changes.</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: stocks with dividends - will it also show dividends received?</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+          <t>moneykeel_log_decisions_v01.xlsx</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>cashflow</t>
+          <t>performance</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>MK-CF-M-052 — Outflow (expenses + debt)</t>
+          <t>DEC-0483</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>YOUR ANSWER — use the same number</t>
+          <t>Open question on this decision — for him</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr"/>
     </row>
-    <row r="27" ht="45" customHeight="1">
+    <row r="27" ht="30" customHeight="1">
       <c r="A27" s="3" t="n">
         <v>24</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Cash flow</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>1. Is this row right — the words on screen, the formula, the inputs, the decisions and what it says when it cannot be computed? Say yes, or say what changes.</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: What's the level of details displayed and how?r</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+          <t>moneykeel_log_decisions_v01.xlsx</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>cashflow</t>
+          <t>performance</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>MK-CF-M-053 — = Surplus</t>
+          <t>DEC-0497</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>YOUR ANSWER — use the same number</t>
+          <t>Open question on this decision — for him</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr"/>
     </row>
-    <row r="28" ht="45" customHeight="1">
+    <row r="28" ht="30" customHeight="1">
       <c r="A28" s="3" t="n">
         <v>25</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Cash flow</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>1. Is this row right — the words on screen, the formula, the inputs, the decisions and what it says when it cannot be computed? Say yes, or say what changes.</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Invest: what level of detail, and how?</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+          <t>moneykeel_log_decisions_v01.xlsx</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>cashflow</t>
+          <t>performance</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>MK-CF-M-054 — each received line</t>
+          <t>DEC-0510</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>YOUR ANSWER — use the same number</t>
+          <t>Open question on this decision — for him</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr"/>
     </row>
-    <row r="29" ht="60" customHeight="1">
+    <row r="29" ht="45" customHeight="1">
       <c r="A29" s="3" t="n">
         <v>26</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Cash flow</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>1. Is this row right — the words on screen, the formula, the inputs, the decisions and what it says when it cannot be computed? Say yes, or say what changes.
-Q52 — MK-PF-F-026 moneyWeightedReturn is a true personal return — it solves for the rate that makes what you paid in, on the days you paid it in, equal what you have now. It is built, correct and reached by NO SCREEN: the card that showed it was removed by the Performance design you approved on 2026-09-25. The Return the screen does show is a different calculation (Modified Dietz) that also calls itself money-weighted. Do we delete the u</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: How is income + spending captured, at what frequency, and what about cash / unconnected cards?</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+          <t>moneykeel_log_decisions_v01.xlsx</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>multiple_screens</t>
+          <t>cashflow</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>MK-XS-M-004 — ▲ up/▼ down $X (Y%) this month · Return · YOUR RETURN</t>
+          <t>DEC-0503</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>YOUR ANSWER — use the same number</t>
+          <t>Open question on this decision — for him</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>The figure stays DRAFT, and it is on MORE THAN ONE screen — so the answer settles what every screen showing it says.</t>
+          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr"/>
     </row>
-    <row r="30" ht="60" customHeight="1">
+    <row r="30" ht="30" customHeight="1">
       <c r="A30" s="3" t="n">
         <v>27</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Net worth</t>
+          <t>Cash flow</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>VERIFY 48 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Are the month bars cash flows -- inflow / outflow?</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+          <t>moneykeel_log_decisions_v01.xlsx</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>networth</t>
+          <t>cashflow</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>all 48 unverified rows on this tab</t>
+          <t>DEC-0512</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>ROW VERIFIED — founder, date and how</t>
+          <t>Open question on this decision — for him</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>The module cannot be called launch-ready: a TESTED row is proved to match the code, not proved to be right.</t>
+          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr"/>
@@ -1744,37 +1739,37 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Net worth</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>VERIFY 11 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
+          <t>Commit — the branch was 278 files behind on 2026-09-14; committed since: 983805a (catch-up), f0e1d6d (Net worth v08), c4f2679 (the Since crash), 727e22a (Performance v14). Nothing is pushed — the branch taxonomy-v1.0.7 is local only.</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>performance</t>
+          <t>Workplan</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>all 11 unverified rows on this tab</t>
+          <t>Commit — the branch was 278 files behind on 2026-09-14; committed sinc</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>ROW VERIFIED — founder, date and how</t>
+          <t>Status / Comments</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>The module cannot be called launch-ready: a TESTED row is proved to match the code, not proved to be right.</t>
+          <t>Founder: say when to PUSH. (Note 2026-09-26: the Xcode licence has not been accepted on this Mac, so the normal git refuses to run — "sudo xcodebuild -license accept" once, then git works everywhere again.)</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr"/>
@@ -1785,124 +1780,124 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Cash flow</t>
+          <t>Net worth</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>VERIFY 53 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
+          <t>EIGHT live mocks still DRAW words the canon retired (measured 2026-09-26 over the drawn frames, not the commentary): cash-flow this-month v06 ("In (take-home)", "spending") · income end-to-end v07 ("A usual month", "Gross a year") · look-ahead v03 ("/mo") · money-four-tabs v01 ("In (take-home)", "Out (", "/mo", "spending") · account-detail v01 ("Connected ·") · empty-state-pattern v01 ("WHAT YOU O</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>cashflow</t>
+          <t>Workplan</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>all 53 unverified rows on this tab</t>
+          <t>EIGHT live mocks still DRAW words the canon retired (measured 2026-09-</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>ROW VERIFIED — founder, date and how</t>
+          <t>Status / Comments</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>The module cannot be called launch-ready: a TESTED row is proved to match the code, not proved to be right.</t>
+          <t>Founder: say whether each gets a new version on the canon now (old archived), or at its next change. Plan v05 already carries its list inside the file as mark 14 and is fixed when v06 is drawn.</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr"/>
     </row>
-    <row r="33" ht="30" customHeight="1">
+    <row r="33" ht="60" customHeight="1">
       <c r="A33" s="3" t="n">
         <v>30</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Net worth</t>
+          <t>Cash flow</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Plain line - means line graph?</t>
+          <t>Stand-in ages when the birth year is missing: the Retirement cockpit and Insights assume 45, the cash-flow model and the draw steer assume 68, the onboarding helper 35 (or 65 for the retirement age). Your rule R2 says an unknown input gives no number and a reason.</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
+          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>networth</t>
+          <t>Workplan</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>DEC-0469</t>
+          <t>Stand-in ages when the birth year is missing: the Retirement cockpit a</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>Open question on this decision — for him</t>
+          <t>Status / Comments</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
+          <t>Founder: say what those screens show when the birth year is missing (ask for it in place? show the door?); then Claude: mock first, then code</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr"/>
     </row>
-    <row r="34" ht="30" customHeight="1">
+    <row r="34" ht="60" customHeight="1">
       <c r="A34" s="3" t="n">
         <v>31</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Net worth</t>
+          <t>Cash flow</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: what does screen look like for manual update?</t>
+          <t>Q-CF-2 'how much have I spent this month, against the plan, and what is left' — eight figures DRAFTED on MK-CF-O-003 thisMonth: expected inflow, planned outflow, planned surplus, each planned line, inflow so far, outflow so far, surplus so far, each received line (MK-CF-M-047…054)</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
+          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>networth</t>
+          <t>Workplan</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>DEC-0470</t>
+          <t>Q-CF-2 'how much have I spent this month, against the plan, and what i</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>Open question on this decision — for him</t>
+          <t>Status / Comments</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
+          <t>Founder: read the eight rows on the master's cashflow tab (Row status says DRAFT) and say yes, or say what changes. Claude: the moment you do, the Cash flow screen, the month detail screen and Home's cell move behind the door and stop working figures out themselves</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr"/>
     </row>
-    <row r="35" ht="45" customHeight="1">
+    <row r="35" ht="60" customHeight="1">
       <c r="A35" s="3" t="n">
         <v>32</v>
       </c>
@@ -1913,32 +1908,32 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: do we capture only balance or all individual portfolio holding e.g. AMZN 100 stocks ….</t>
+          <t>One door, one term: the three ways to add an account read 'Link it (read-only)', 'Add by hand' and 'Import from a file' on every screen, under the heading 'How do you want to add an account?' — Home, Sharpen your plan, the Plan tab, Net worth (first day and the add sheet), the Connect an account screen and Performance</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
+          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>networth</t>
+          <t>Workplan</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>DEC-0475</t>
+          <t>One door, one term: the three ways to add an account read 'Link it (re</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>Open question on this decision — for him</t>
+          <t>Status / Comments</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
+          <t>Founder: approve the mock MoneyKeel/documents/home-screen/moneykeel_pres_mock_ways-to-add-an-account_v10.html (every affected screen, before and after). Claude: then build all of it the same day, with the tests and the canon row</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr"/>
@@ -1954,37 +1949,37 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: When dividend is captured is it automatically added to income or cash? Similarly, is there a way captical gain is captured and displayed somewhere?</t>
+          <t>Nothing recorded which design each screen was built from. The Build 53 Net worth and Performance finals (networth-FINAL.html, performance-FINAL.html, the two Net worth PDFs, Net worth screens 01 to 11) were filed under networth-and-performance/archive/ on 2026-09-01, which marks them replaced. They were not replaced. Six hours of mocks then started from the wrong files. CORRECTION 2026-09-14: Buil</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
+          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>networth</t>
+          <t>Workplan</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>DEC-0476</t>
+          <t>Nothing recorded which design each screen was built from. The Build 53</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>Open question on this decision — for him</t>
+          <t>Status / Comments</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
+          <t>Claude: done 2026-09-14 — Build 53 files matched by exact content and recorded in MoneyKeel/documents/standards/moneykeel_pres_spec_design-each-screen-was-built-from_v01.md. Founder: (1) confirm Net worth = v5 + square corners; (2) say whether to draw Net worth v6 from the Build 53 code (v5 with squ</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr"/>
     </row>
-    <row r="37" ht="30" customHeight="1">
+    <row r="37" ht="60" customHeight="1">
       <c r="A37" s="3" t="n">
         <v>34</v>
       </c>
@@ -1995,32 +1990,32 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Is this manual, imported or connected and captured via Plaid?</t>
+          <t>Net worth v07 — the three ways to add an account on Net worth (first day, the add sheet, the add button), plus every ruling since Build 53 that touches the screen (empty state, Debts, Emergency fund, Stocks / Funds, /month, you entered, expenses, odds to the nearest 5), each marked</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
+          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>networth</t>
+          <t>Workplan</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>DEC-0478</t>
+          <t>Net worth v07 — the three ways to add an account on Net worth (first d</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>Open question on this decision — for him</t>
+          <t>Status / Comments</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
+          <t xml:space="preserve">Founder: say yes to v08, or name a mark. Also: today's money for the retirement figures and tax on taxable withdrawals (recommended); whether dark/light bars replace the Plan tab's quiet labels. Claude: once approved, record v08 as the current Net worth design, archive v06, then build marks 1–4 and </t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr"/>
@@ -2031,658 +2026,125 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Net worth</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Total return captures both realized and unrealized gains? Is there any place we display realized P/L, unrealized P/L, total dividend, and total interest separately?</t>
+          <t>The retirement sentence (Net worth, Plan, Home) prints future dollars without saying so, and the odds calculation charges no tax on withdrawals from taxable accounts — found checking the founder's question on v07 ($4.1M at 65 is about $2.0M in today's money)</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
+          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>performance</t>
+          <t>Workplan</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>DEC-0479</t>
+          <t xml:space="preserve">The retirement sentence (Net worth, Plan, Home) prints future dollars </t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>Open question on this decision — for him</t>
+          <t>Status / Comments</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
+          <t>Founder: say whether to show today's money and to tax taxable withdrawals (recommended). Claude: then write both as findings on the master rows (MK-XS-M-002 and the pot/leftover figures) before any code.</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr"/>
     </row>
-    <row r="39" ht="30" customHeight="1">
+    <row r="39" ht="60" customHeight="1">
       <c r="A39" s="3" t="n">
         <v>36</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Cash flow</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: stocks with dividends - will it also show dividends received?</t>
+          <t>Two word collisions found building v08: Cash flow's 'Add by hand' adds an EXPENSE (the same words as the account door), and Settings still says 'Disconnect' beside 'Linked accounts'</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
+          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>performance</t>
+          <t>Workplan</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>DEC-0483</t>
+          <t>Two word collisions found building v08: Cash flow's 'Add by hand' adds</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>Open question on this decision — for him</t>
+          <t>Status / Comments</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
+          <t>Founder: say whether Cash flow's door should read differently (for example 'Add an expense by hand') and whether Disconnect becomes 'Unlink'.</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr"/>
     </row>
-    <row r="40" ht="30" customHeight="1">
+    <row r="40" ht="60" customHeight="1">
       <c r="A40" s="3" t="n">
         <v>37</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Net worth</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: What's the level of details displayed and how?r</t>
+          <t>LAUNCH ANSWER LIST — 61 things need you for Net worth, Cash flow and Performance to be launch-ready</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
+          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>performance</t>
+          <t>Workplan</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>DEC-0497</t>
+          <t>LAUNCH ANSWER LIST — 61 things need you for Net worth, Cash flow and P</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>Open question on this decision — for him</t>
+          <t>Status / Comments</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
+          <t>His ask, 2026-09-29: ‘Give me a list of files, tabs, and rows I need to answer for NW, CF, Performance sections of the app to be complete.’ Open MoneyKeel/documents/other/moneykeel_calc_plan_launch-answer-list_v01.xlsx. Five tabs: Read me, EVERYTHING, and one per module. Every line names its FILE, i</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr"/>
     </row>
-    <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="3" t="n">
-        <v>38</v>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Invest: what level of detail, and how?</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>performance</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>DEC-0510</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>Open question on this decision — for him</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr"/>
-    </row>
-    <row r="42" ht="45" customHeight="1">
-      <c r="A42" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>Cash flow</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: How is income + spending captured, at what frequency, and what about cash / unconnected cards?</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>cashflow</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="inlineStr">
-        <is>
-          <t>DEC-0503</t>
-        </is>
-      </c>
-      <c r="G42" s="3" t="inlineStr">
-        <is>
-          <t>Open question on this decision — for him</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
-        </is>
-      </c>
-      <c r="I42" s="3" t="inlineStr"/>
-    </row>
-    <row r="43" ht="30" customHeight="1">
-      <c r="A43" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>Cash flow</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Are the month bars cash flows -- inflow / outflow?</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>cashflow</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>DEC-0512</t>
-        </is>
-      </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t>Open question on this decision — for him</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr"/>
-    </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" s="3" t="n">
-        <v>41</v>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>Commit — the branch was 278 files behind on 2026-09-14; committed since: 983805a (catch-up), f0e1d6d (Net worth v08), c4f2679 (the Since crash), 727e22a (Performance v14). Nothing is pushed — the branch taxonomy-v1.0.7 is local only.</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>Workplan</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t>Commit — the branch was 278 files behind on 2026-09-14; committed sinc</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t>Status / Comments</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>Founder: say when to PUSH. (Note 2026-09-26: the Xcode licence has not been accepted on this Mac, so the normal git refuses to run — "sudo xcodebuild -license accept" once, then git works everywhere again.)</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="inlineStr"/>
-    </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>EIGHT live mocks still DRAW words the canon retired (measured 2026-09-26 over the drawn frames, not the commentary): cash-flow this-month v06 ("In (take-home)", "spending") · income end-to-end v07 ("A usual month", "Gross a year") · look-ahead v03 ("/mo") · money-four-tabs v01 ("In (take-home)", "Out (", "/mo", "spending") · account-detail v01 ("Connected ·") · empty-state-pattern v01 ("WHAT YOU O</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>Workplan</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t>EIGHT live mocks still DRAW words the canon retired (measured 2026-09-</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t>Status / Comments</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>Founder: say whether each gets a new version on the canon now (old archived), or at its next change. Plan v05 already carries its list inside the file as mark 14 and is fixed when v06 is drawn.</t>
-        </is>
-      </c>
-      <c r="I45" s="3" t="inlineStr"/>
-    </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" s="3" t="n">
-        <v>43</v>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>Cash flow</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>Stand-in ages when the birth year is missing: the Retirement cockpit and Insights assume 45, the cash-flow model and the draw steer assume 68, the onboarding helper 35 (or 65 for the retirement age). Your rule R2 says an unknown input gives no number and a reason.</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr">
-        <is>
-          <t>Workplan</t>
-        </is>
-      </c>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t>Stand-in ages when the birth year is missing: the Retirement cockpit a</t>
-        </is>
-      </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t>Status / Comments</t>
-        </is>
-      </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>Founder: say what those screens show when the birth year is missing (ask for it in place? show the door?); then Claude: mock first, then code</t>
-        </is>
-      </c>
-      <c r="I46" s="3" t="inlineStr"/>
-    </row>
-    <row r="47" ht="60" customHeight="1">
-      <c r="A47" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>Cash flow</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>Q-CF-2 'how much have I spent this month, against the plan, and what is left' — eight figures DRAFTED on MK-CF-O-003 thisMonth: expected inflow, planned outflow, planned surplus, each planned line, inflow so far, outflow so far, surplus so far, each received line (MK-CF-M-047…054)</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>Workplan</t>
-        </is>
-      </c>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t>Q-CF-2 'how much have I spent this month, against the plan, and what i</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="inlineStr">
-        <is>
-          <t>Status / Comments</t>
-        </is>
-      </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>Founder: read the eight rows on the master's cashflow tab (Row status says DRAFT) and say yes, or say what changes. Claude: the moment you do, the Cash flow screen, the month detail screen and Home's cell move behind the door and stop working figures out themselves</t>
-        </is>
-      </c>
-      <c r="I47" s="3" t="inlineStr"/>
-    </row>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>One door, one term: the three ways to add an account read 'Link it (read-only)', 'Add by hand' and 'Import from a file' on every screen, under the heading 'How do you want to add an account?' — Home, Sharpen your plan, the Plan tab, Net worth (first day and the add sheet), the Connect an account screen and Performance</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="inlineStr">
-        <is>
-          <t>Workplan</t>
-        </is>
-      </c>
-      <c r="F48" s="3" t="inlineStr">
-        <is>
-          <t>One door, one term: the three ways to add an account read 'Link it (re</t>
-        </is>
-      </c>
-      <c r="G48" s="3" t="inlineStr">
-        <is>
-          <t>Status / Comments</t>
-        </is>
-      </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>Founder: approve the mock MoneyKeel/documents/home-screen/moneykeel_pres_mock_ways-to-add-an-account_v10.html (every affected screen, before and after). Claude: then build all of it the same day, with the tests and the canon row</t>
-        </is>
-      </c>
-      <c r="I48" s="3" t="inlineStr"/>
-    </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" s="3" t="n">
-        <v>46</v>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>Nothing recorded which design each screen was built from. The Build 53 Net worth and Performance finals (networth-FINAL.html, performance-FINAL.html, the two Net worth PDFs, Net worth screens 01 to 11) were filed under networth-and-performance/archive/ on 2026-09-01, which marks them replaced. They were not replaced. Six hours of mocks then started from the wrong files. CORRECTION 2026-09-14: Buil</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>Workplan</t>
-        </is>
-      </c>
-      <c r="F49" s="3" t="inlineStr">
-        <is>
-          <t>Nothing recorded which design each screen was built from. The Build 53</t>
-        </is>
-      </c>
-      <c r="G49" s="3" t="inlineStr">
-        <is>
-          <t>Status / Comments</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>Claude: done 2026-09-14 — Build 53 files matched by exact content and recorded in MoneyKeel/documents/standards/moneykeel_pres_spec_design-each-screen-was-built-from_v01.md. Founder: (1) confirm Net worth = v5 + square corners; (2) say whether to draw Net worth v6 from the Build 53 code (v5 with squ</t>
-        </is>
-      </c>
-      <c r="I49" s="3" t="inlineStr"/>
-    </row>
-    <row r="50" ht="60" customHeight="1">
-      <c r="A50" s="3" t="n">
-        <v>47</v>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>Net worth v07 — the three ways to add an account on Net worth (first day, the add sheet, the add button), plus every ruling since Build 53 that touches the screen (empty state, Debts, Emergency fund, Stocks / Funds, /month, you entered, expenses, odds to the nearest 5), each marked</t>
-        </is>
-      </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="inlineStr">
-        <is>
-          <t>Workplan</t>
-        </is>
-      </c>
-      <c r="F50" s="3" t="inlineStr">
-        <is>
-          <t>Net worth v07 — the three ways to add an account on Net worth (first d</t>
-        </is>
-      </c>
-      <c r="G50" s="3" t="inlineStr">
-        <is>
-          <t>Status / Comments</t>
-        </is>
-      </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Founder: say yes to v08, or name a mark. Also: today's money for the retirement figures and tax on taxable withdrawals (recommended); whether dark/light bars replace the Plan tab's quiet labels. Claude: once approved, record v08 as the current Net worth design, archive v06, then build marks 1–4 and </t>
-        </is>
-      </c>
-      <c r="I50" s="3" t="inlineStr"/>
-    </row>
-    <row r="51" ht="60" customHeight="1">
-      <c r="A51" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>The retirement sentence (Net worth, Plan, Home) prints future dollars without saying so, and the odds calculation charges no tax on withdrawals from taxable accounts — found checking the founder's question on v07 ($4.1M at 65 is about $2.0M in today's money)</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="inlineStr">
-        <is>
-          <t>Workplan</t>
-        </is>
-      </c>
-      <c r="F51" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The retirement sentence (Net worth, Plan, Home) prints future dollars </t>
-        </is>
-      </c>
-      <c r="G51" s="3" t="inlineStr">
-        <is>
-          <t>Status / Comments</t>
-        </is>
-      </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>Founder: say whether to show today's money and to tax taxable withdrawals (recommended). Claude: then write both as findings on the master rows (MK-XS-M-002 and the pot/leftover figures) before any code.</t>
-        </is>
-      </c>
-      <c r="I51" s="3" t="inlineStr"/>
-    </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" s="3" t="n">
-        <v>49</v>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>Cash flow</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>Two word collisions found building v08: Cash flow's 'Add by hand' adds an EXPENSE (the same words as the account door), and Settings still says 'Disconnect' beside 'Linked accounts'</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="inlineStr">
-        <is>
-          <t>Workplan</t>
-        </is>
-      </c>
-      <c r="F52" s="3" t="inlineStr">
-        <is>
-          <t>Two word collisions found building v08: Cash flow's 'Add by hand' adds</t>
-        </is>
-      </c>
-      <c r="G52" s="3" t="inlineStr">
-        <is>
-          <t>Status / Comments</t>
-        </is>
-      </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>Founder: say whether Cash flow's door should read differently (for example 'Add an expense by hand') and whether Disconnect becomes 'Unlink'.</t>
-        </is>
-      </c>
-      <c r="I52" s="3" t="inlineStr"/>
-    </row>
-    <row r="53" ht="60" customHeight="1">
-      <c r="A53" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>LAUNCH ANSWER LIST — 61 things need you for Net worth, Cash flow and Performance to be launch-ready</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="inlineStr">
-        <is>
-          <t>Workplan</t>
-        </is>
-      </c>
-      <c r="F53" s="3" t="inlineStr">
-        <is>
-          <t>LAUNCH ANSWER LIST — 61 things need you for Net worth, Cash flow and P</t>
-        </is>
-      </c>
-      <c r="G53" s="3" t="inlineStr">
-        <is>
-          <t>Status / Comments</t>
-        </is>
-      </c>
-      <c r="H53" s="3" t="inlineStr">
-        <is>
-          <t>His ask, 2026-09-29: ‘Give me a list of files, tabs, and rows I need to answer for NW, CF, Performance sections of the app to be complete.’ Open MoneyKeel/documents/other/moneykeel_calc_plan_launch-answer-list_v01.xlsx. Five tabs: Read me, EVERYTHING, and one per module. Every line names its FILE, i</t>
-        </is>
-      </c>
-      <c r="I53" s="3" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I53"/>
+  <autoFilter ref="A1:I40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2693,7 +2155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2710,7 +2172,7 @@
     <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>31 things to answer for Net worth</t>
+          <t>26 things to answer for Net worth</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -2780,7 +2242,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="45" customHeight="1">
+    <row r="4" ht="60" customHeight="1">
       <c r="A4" s="3" t="n">
         <v>1</v>
       </c>
@@ -2791,7 +2253,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>1. Is this row right — the words on screen, the formula, the inputs, the decisions and what it says when it cannot be computed? Say yes, or say what changes.</t>
+          <t>Q17 — "Return on cash + investments" counts money you paid in as a gain. Is the LABEL wrong, or the FORMULA? Fixing the formula means removing deposits and withdrawals before measuring.</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -2806,7 +2268,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-001 — Change in net worth +$X</t>
+          <t>MK-NW-M-002 — Return on cash + investments</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -2821,7 +2283,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr"/>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="45" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>2</v>
       </c>
@@ -2832,7 +2294,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Q17 — "Return on cash + investments" counts money you paid in as a gain. Is the LABEL wrong, or the FORMULA? Fixing the formula means removing deposits and withdrawals before measuring.</t>
+          <t>Q32 — The trend survives on a new device but the walk behind it does not. Should the trend say so, or show quietly?</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -2847,7 +2309,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-002 — Return on cash + investments</t>
+          <t>MK-NW-M-003 — the trend line</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -2872,89 +2334,6 @@
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>1. Is this row right — the words on screen, the formula, the inputs, the decisions and what it says when it cannot be computed? Say yes, or say what changes.
-Q32 — The trend survives on a new device but the walk behind it does not. Should the trend say so, or show quietly?</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>networth</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>MK-NW-M-003 — the trend line</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>YOUR ANSWER — use the same number</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr"/>
-    </row>
-    <row r="7" ht="45" customHeight="1">
-      <c r="A7" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>1. Is this row right — the words on screen, the formula, the inputs, the decisions and what it says when it cannot be computed? Say yes, or say what changes.</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>networth</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>MK-NW-M-006 — 🏠 PERSONAL PROPERTY</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>YOUR ANSWER — use the same number</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr"/>
-    </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Q10 — What order of evidence decides an asset's class? Draft: the institution's own class field, then the shape of the identifier (option symbols, nine-character bond numbers, currency codes), then words in the name, then ask you.
 Q11 — When nothing matches: refuse the line and ask, or park it as unclassified? Parking keeps the totals right and hides a gap; refusing is honest and stops the import.
@@ -2962,6 +2341,88 @@
 Q13 — Commodities: is a fund that </t>
         </is>
       </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>networth</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-M-007 — class rows — by class, institution or type</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>YOUR ANSWER — use the same number</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7" ht="45" customHeight="1">
+      <c r="A7" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Net worth</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Q14 — What should a MIXED account be called on screen, when it holds several classes at once?</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>networth</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-M-008 — each account and its balance</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>YOUR ANSWER — use the same number</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8" ht="45" customHeight="1">
+      <c r="A8" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Net worth</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Q15 — An institution word we do not recognise: refuse the line and ask you, or book it as unclassified with no direction? The old sign-guess is what minted the $1.4 million.</t>
+        </is>
+      </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
           <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
@@ -2974,7 +2435,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-007 — class rows — by class, institution or type</t>
+          <t>MK-NW-M-019 — Income</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -2989,7 +2450,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr"/>
     </row>
-    <row r="9" ht="60" customHeight="1">
+    <row r="9" ht="45" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>6</v>
       </c>
@@ -3000,8 +2461,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>1. Is this row right — the words on screen, the formula, the inputs, the decisions and what it says when it cannot be computed? Say yes, or say what changes.
-Q14 — What should a MIXED account be called on screen, when it holds several classes at once?</t>
+          <t>Q01 — Is Quantity for a bond the FACE amount (e.g. 227,000) with the price quoted per $100 of face, or the number of bonds? It decides how value and gain are worked out.</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -3016,7 +2476,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-008 — each account and its balance</t>
+          <t>MK-NW-M-023 — Face value</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -3031,7 +2491,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr"/>
     </row>
-    <row r="10" ht="60" customHeight="1">
+    <row r="10" ht="45" customHeight="1">
       <c r="A10" s="3" t="n">
         <v>7</v>
       </c>
@@ -3042,7 +2502,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Q53 — "Monthly debt payments" on the Net worth screen: the MINIMUM each debt obliges, or what ACTUALLY leaves your account? They part whenever someone pays more than a minimum. On one card — $200 minimum, paid $600 — the minimum reads $200 and the actual reads $600. Both are real figures: the minimum is the obligation a lender can demand (it is what debt-to-income is measured on), the actual is the money that leaves. The screen shows the MINIMUM today, and the label reads like the actual. Which belongs under those words — or should the line say which it is, or show both?</t>
+          <t>Q04 — "Annual income" on a bond: the last twelve months actually received, or the forward estimate from today\'s coupon? Both are defensible and they differ.</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -3057,7 +2517,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-012 — Monthly debt payments</t>
+          <t>MK-NW-M-024 — Interest payments</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -3083,7 +2543,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>1. Is this row right — the words on screen, the formula, the inputs, the decisions and what it says when it cannot be computed? Say yes, or say what changes.</t>
+          <t>Q05 — Accrued interest: do we work it out ourselves — which needs a day-count rule per bond type — or only show what the institution gives us?</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -3098,7 +2558,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-015 — YOUR RETIREMENT PLAN — on track for $X by age Y</t>
+          <t>MK-NW-M-026 — Yield if held to maturity</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -3113,7 +2573,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr"/>
     </row>
-    <row r="12" ht="45" customHeight="1">
+    <row r="12" ht="60" customHeight="1">
       <c r="A12" s="3" t="n">
         <v>9</v>
       </c>
@@ -3124,7 +2584,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>1. Is this row right — the words on screen, the formula, the inputs, the decisions and what it says when it cannot be computed? Say yes, or say what changes.</t>
+          <t>Q34 — Approve the exact wording for the average-price rule (info dot + column Q): 'Shares with no recorded purchase price are left out of the average. N of your shares are in that position.' — and the refusal: 'Average not available — none of these shares has a recorded price.'</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -3139,7 +2599,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-016 — Net worth so far (setup)</t>
+          <t>MK-NW-M-032 — Price paid (average)</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -3154,7 +2614,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr"/>
     </row>
-    <row r="13" ht="45" customHeight="1">
+    <row r="13" ht="60" customHeight="1">
       <c r="A13" s="3" t="n">
         <v>10</v>
       </c>
@@ -3165,7 +2625,8 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Q15 — An institution word we do not recognise: refuse the line and ask you, or book it as unclassified with no direction? The old sign-guess is what minted the $1.4 million.</t>
+          <t>Q35 — Approve the exact label and the canon phrase for the twelve-month window. Proposed: 'Dividends received (trailing twelve months)' here, and 'trailing twelve months' in the other four places (spelled out — no initialism).
+Q36 — Dividends on this card: THIS account only, matching 'Realized from sales' beside it? Recommended: yes.</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -3180,7 +2641,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-019 — Income</t>
+          <t>MK-NW-M-034 — Dividends received (12 mo)</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -3195,7 +2656,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr"/>
     </row>
-    <row r="14" ht="45" customHeight="1">
+    <row r="14" ht="60" customHeight="1">
       <c r="A14" s="3" t="n">
         <v>11</v>
       </c>
@@ -3206,7 +2667,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Q01 — Is Quantity for a bond the FACE amount (e.g. 227,000) with the price quoted per $100 of face, or the number of bonds? It decides how value and gain are worked out.</t>
+          <t>Q37 — For a connected account: log an 'Opening holding' row per broker lot at first sync (dated the lot's purchase date, at the broker's cost) so every later sale is covered — recommended — or keep 'not counted + say so' for pre-history purchases?</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -3221,7 +2682,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-023 — Face value</t>
+          <t>MK-NW-M-035 — Realized gain from your buys and sells</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -3236,7 +2697,7 @@
       </c>
       <c r="I14" s="3" t="inlineStr"/>
     </row>
-    <row r="15" ht="45" customHeight="1">
+    <row r="15" ht="60" customHeight="1">
       <c r="A15" s="3" t="n">
         <v>12</v>
       </c>
@@ -3247,7 +2708,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Q04 — "Annual income" on a bond: the last twelve months actually received, or the forward estimate from today\'s coupon? Both are defensible and they differ.</t>
+          <t>Q20 — A lot with no recorded purchase price is skipped, so its gain is simply absent. Should the screen SAY so — "gain not counted for N shares, no purchase price on record" — rather than quietly reporting less?</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -3262,7 +2723,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-024 — Interest payments</t>
+          <t>MK-NW-M-036 — Gain — long-term (held over 1 yr)</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -3277,7 +2738,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr"/>
     </row>
-    <row r="16" ht="45" customHeight="1">
+    <row r="16" ht="60" customHeight="1">
       <c r="A16" s="3" t="n">
         <v>13</v>
       </c>
@@ -3288,7 +2749,8 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Q05 — Accrued interest: do we work it out ourselves — which needs a day-count rule per bond type — or only show what the institution gives us?</t>
+          <t>Q03 — Certificates of deposit: under Fixed Income, or their own class? They carry a term, a rate and an early-withdrawal penalty that a bond does not.
+Q38 — Your bond display rule, three specifics before the mock: (1) 'quantity' for a bond = the number of bonds (each of face $1,000), or the total face amount? (2) 'earned interest' = the INTEREST rows recorded in the ledger for this bond — the only source we have — yes? (3) 'current price' = price per $100 of face as brokers quote it, or the dollar value of the position? Then I mock the bond card and screen before any code.</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -3303,7 +2765,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-026 — Yield if held to maturity</t>
+          <t>MK-NW-M-041 — total value of your bonds</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -3329,7 +2791,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Q34 — Approve the exact wording for the average-price rule (info dot + column Q): 'Shares with no recorded purchase price are left out of the average. N of your shares are in that position.' — and the refusal: 'Average not available — none of these shares has a recorded price.'</t>
+          <t>VERIFY 48 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -3344,24 +2806,24 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-032 — Price paid (average)</t>
+          <t>all 48 unverified rows on this tab</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>YOUR ANSWER — use the same number</t>
+          <t>ROW VERIFIED — founder, date and how</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+          <t>The module cannot be called launch-ready: a TESTED row is proved to match the code, not proved to be right.</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr"/>
     </row>
-    <row r="18" ht="60" customHeight="1">
+    <row r="18" ht="30" customHeight="1">
       <c r="A18" s="3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
@@ -3370,13 +2832,12 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Q35 — Approve the exact label and the canon phrase for the twelve-month window. Proposed: 'Dividends received (trailing twelve months)' here, and 'trailing twelve months' in the other four places (spelled out — no initialism).
-Q36 — Dividends on this card: THIS account only, matching 'Realized from sales' beside it? Recommended: yes.</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Plain line - means line graph?</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+          <t>moneykeel_log_decisions_v01.xlsx</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -3386,24 +2847,24 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-034 — Dividends received (12 mo)</t>
+          <t>DEC-0469</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>YOUR ANSWER — use the same number</t>
+          <t>Open question on this decision — for him</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr"/>
     </row>
-    <row r="19" ht="60" customHeight="1">
+    <row r="19" ht="30" customHeight="1">
       <c r="A19" s="3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
@@ -3412,12 +2873,12 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Q37 — For a connected account: log an 'Opening holding' row per broker lot at first sync (dated the lot's purchase date, at the broker's cost) so every later sale is covered — recommended — or keep 'not counted + say so' for pre-history purchases?</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: what does screen look like for manual update?</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+          <t>moneykeel_log_decisions_v01.xlsx</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -3427,24 +2888,24 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-035 — Realized gain from your buys and sells</t>
+          <t>DEC-0470</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>YOUR ANSWER — use the same number</t>
+          <t>Open question on this decision — for him</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr"/>
     </row>
-    <row r="20" ht="60" customHeight="1">
+    <row r="20" ht="45" customHeight="1">
       <c r="A20" s="3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
@@ -3453,12 +2914,12 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Q20 — A lot with no recorded purchase price is skipped, so its gain is simply absent. Should the screen SAY so — "gain not counted for N shares, no purchase price on record" — rather than quietly reporting less?</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: do we capture only balance or all individual portfolio holding e.g. AMZN 100 stocks ….</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+          <t>moneykeel_log_decisions_v01.xlsx</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -3468,24 +2929,24 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-036 — Gain — long-term (held over 1 yr)</t>
+          <t>DEC-0475</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>YOUR ANSWER — use the same number</t>
+          <t>Open question on this decision — for him</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr"/>
     </row>
     <row r="21" ht="60" customHeight="1">
       <c r="A21" s="3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
@@ -3494,13 +2955,12 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Q03 — Certificates of deposit: under Fixed Income, or their own class? They carry a term, a rate and an early-withdrawal penalty that a bond does not.
-Q38 — Your bond display rule, three specifics before the mock: (1) 'quantity' for a bond = the number of bonds (each of face $1,000), or the total face amount? (2) 'earned interest' = the INTEREST rows recorded in the ledger for this bond — the only source we have — yes? (3) 'current price' = price per $100 of face as brokers quote it, or the dollar value of the position? Then I mock the bond card and screen before any code.</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: When dividend is captured is it automatically added to income or cash? Similarly, is there a way captical gain is captured and displayed somewhere?</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+          <t>moneykeel_log_decisions_v01.xlsx</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -3510,24 +2970,24 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-041 — total value of your bonds</t>
+          <t>DEC-0476</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>YOUR ANSWER — use the same number</t>
+          <t>Open question on this decision — for him</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr"/>
     </row>
-    <row r="22" ht="60" customHeight="1">
+    <row r="22" ht="30" customHeight="1">
       <c r="A22" s="3" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
@@ -3536,12 +2996,12 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>VERIFY 48 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Is this manual, imported or connected and captured via Plaid?</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+          <t>moneykeel_log_decisions_v01.xlsx</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -3551,24 +3011,24 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>all 48 unverified rows on this tab</t>
+          <t>DEC-0478</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>ROW VERIFIED — founder, date and how</t>
+          <t>Open question on this decision — for him</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>The module cannot be called launch-ready: a TESTED row is proved to match the code, not proved to be right.</t>
+          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr"/>
     </row>
-    <row r="23" ht="30" customHeight="1">
+    <row r="23" ht="60" customHeight="1">
       <c r="A23" s="3" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
@@ -3577,39 +3037,39 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Plain line - means line graph?</t>
+          <t>Commit — the branch was 278 files behind on 2026-09-14; committed since: 983805a (catch-up), f0e1d6d (Net worth v08), c4f2679 (the Since crash), 727e22a (Performance v14). Nothing is pushed — the branch taxonomy-v1.0.7 is local only.</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
+          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>networth</t>
+          <t>Workplan</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>DEC-0469</t>
+          <t>Commit — the branch was 278 files behind on 2026-09-14; committed sinc</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Open question on this decision — for him</t>
+          <t>Status / Comments</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
+          <t>Founder: say when to PUSH. (Note 2026-09-26: the Xcode licence has not been accepted on this Mac, so the normal git refuses to run — "sudo xcodebuild -license accept" once, then git works everywhere again.)</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr"/>
     </row>
-    <row r="24" ht="30" customHeight="1">
+    <row r="24" ht="60" customHeight="1">
       <c r="A24" s="3" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
@@ -3618,37 +3078,37 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: what does screen look like for manual update?</t>
+          <t>EIGHT live mocks still DRAW words the canon retired (measured 2026-09-26 over the drawn frames, not the commentary): cash-flow this-month v06 ("In (take-home)", "spending") · income end-to-end v07 ("A usual month", "Gross a year") · look-ahead v03 ("/mo") · money-four-tabs v01 ("In (take-home)", "Out (", "/mo", "spending") · account-detail v01 ("Connected ·") · empty-state-pattern v01 ("WHAT YOU O</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
+          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>networth</t>
+          <t>Workplan</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>DEC-0470</t>
+          <t>EIGHT live mocks still DRAW words the canon retired (measured 2026-09-</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Open question on this decision — for him</t>
+          <t>Status / Comments</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
+          <t>Founder: say whether each gets a new version on the canon now (old archived), or at its next change. Plan v05 already carries its list inside the file as mark 14 and is fixed when v06 is drawn.</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr"/>
     </row>
-    <row r="25" ht="45" customHeight="1">
+    <row r="25" ht="60" customHeight="1">
       <c r="A25" s="3" t="n">
         <v>32</v>
       </c>
@@ -3659,32 +3119,32 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: do we capture only balance or all individual portfolio holding e.g. AMZN 100 stocks ….</t>
+          <t>One door, one term: the three ways to add an account read 'Link it (read-only)', 'Add by hand' and 'Import from a file' on every screen, under the heading 'How do you want to add an account?' — Home, Sharpen your plan, the Plan tab, Net worth (first day and the add sheet), the Connect an account screen and Performance</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
+          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>networth</t>
+          <t>Workplan</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>DEC-0475</t>
+          <t>One door, one term: the three ways to add an account read 'Link it (re</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Open question on this decision — for him</t>
+          <t>Status / Comments</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
+          <t>Founder: approve the mock MoneyKeel/documents/home-screen/moneykeel_pres_mock_ways-to-add-an-account_v10.html (every affected screen, before and after). Claude: then build all of it the same day, with the tests and the canon row</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr"/>
@@ -3700,37 +3160,37 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: When dividend is captured is it automatically added to income or cash? Similarly, is there a way captical gain is captured and displayed somewhere?</t>
+          <t>Nothing recorded which design each screen was built from. The Build 53 Net worth and Performance finals (networth-FINAL.html, performance-FINAL.html, the two Net worth PDFs, Net worth screens 01 to 11) were filed under networth-and-performance/archive/ on 2026-09-01, which marks them replaced. They were not replaced. Six hours of mocks then started from the wrong files. CORRECTION 2026-09-14: Buil</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
+          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>networth</t>
+          <t>Workplan</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>DEC-0476</t>
+          <t>Nothing recorded which design each screen was built from. The Build 53</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>Open question on this decision — for him</t>
+          <t>Status / Comments</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
+          <t>Claude: done 2026-09-14 — Build 53 files matched by exact content and recorded in MoneyKeel/documents/standards/moneykeel_pres_spec_design-each-screen-was-built-from_v01.md. Founder: (1) confirm Net worth = v5 + square corners; (2) say whether to draw Net worth v6 from the Build 53 code (v5 with squ</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr"/>
     </row>
-    <row r="27" ht="30" customHeight="1">
+    <row r="27" ht="60" customHeight="1">
       <c r="A27" s="3" t="n">
         <v>34</v>
       </c>
@@ -3741,39 +3201,39 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Is this manual, imported or connected and captured via Plaid?</t>
+          <t>Net worth v07 — the three ways to add an account on Net worth (first day, the add sheet, the add button), plus every ruling since Build 53 that touches the screen (empty state, Debts, Emergency fund, Stocks / Funds, /month, you entered, expenses, odds to the nearest 5), each marked</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
+          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>networth</t>
+          <t>Workplan</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>DEC-0478</t>
+          <t>Net worth v07 — the three ways to add an account on Net worth (first d</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>Open question on this decision — for him</t>
+          <t>Status / Comments</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
+          <t xml:space="preserve">Founder: say yes to v08, or name a mark. Also: today's money for the retirement figures and tax on taxable withdrawals (recommended); whether dark/light bars replace the Plan tab's quiet labels. Claude: once approved, record v08 as the current Net worth design, archive v06, then build marks 1–4 and </t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr"/>
     </row>
     <row r="28" ht="60" customHeight="1">
       <c r="A28" s="3" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
@@ -3782,7 +3242,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Commit — the branch was 278 files behind on 2026-09-14; committed since: 983805a (catch-up), f0e1d6d (Net worth v08), c4f2679 (the Since crash), 727e22a (Performance v14). Nothing is pushed — the branch taxonomy-v1.0.7 is local only.</t>
+          <t>The retirement sentence (Net worth, Plan, Home) prints future dollars without saying so, and the odds calculation charges no tax on withdrawals from taxable accounts — found checking the founder's question on v07 ($4.1M at 65 is about $2.0M in today's money)</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -3797,7 +3257,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Commit — the branch was 278 files behind on 2026-09-14; committed sinc</t>
+          <t xml:space="preserve">The retirement sentence (Net worth, Plan, Home) prints future dollars </t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -3807,14 +3267,14 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Founder: say when to PUSH. (Note 2026-09-26: the Xcode licence has not been accepted on this Mac, so the normal git refuses to run — "sudo xcodebuild -license accept" once, then git works everywhere again.)</t>
+          <t>Founder: say whether to show today's money and to tax taxable withdrawals (recommended). Claude: then write both as findings on the master rows (MK-XS-M-002 and the pot/leftover figures) before any code.</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr"/>
     </row>
     <row r="29" ht="60" customHeight="1">
       <c r="A29" s="3" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
@@ -3823,7 +3283,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>EIGHT live mocks still DRAW words the canon retired (measured 2026-09-26 over the drawn frames, not the commentary): cash-flow this-month v06 ("In (take-home)", "spending") · income end-to-end v07 ("A usual month", "Gross a year") · look-ahead v03 ("/mo") · money-four-tabs v01 ("In (take-home)", "Out (", "/mo", "spending") · account-detail v01 ("Connected ·") · empty-state-pattern v01 ("WHAT YOU O</t>
+          <t>LAUNCH ANSWER LIST — 61 things need you for Net worth, Cash flow and Performance to be launch-ready</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -3838,7 +3298,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>EIGHT live mocks still DRAW words the canon retired (measured 2026-09-</t>
+          <t>LAUNCH ANSWER LIST — 61 things need you for Net worth, Cash flow and P</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -3848,218 +3308,13 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Founder: say whether each gets a new version on the canon now (old archived), or at its next change. Plan v05 already carries its list inside the file as mark 14 and is fixed when v06 is drawn.</t>
+          <t>His ask, 2026-09-29: ‘Give me a list of files, tabs, and rows I need to answer for NW, CF, Performance sections of the app to be complete.’ Open MoneyKeel/documents/other/moneykeel_calc_plan_launch-answer-list_v01.xlsx. Five tabs: Read me, EVERYTHING, and one per module. Every line names its FILE, i</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr"/>
     </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>One door, one term: the three ways to add an account read 'Link it (read-only)', 'Add by hand' and 'Import from a file' on every screen, under the heading 'How do you want to add an account?' — Home, Sharpen your plan, the Plan tab, Net worth (first day and the add sheet), the Connect an account screen and Performance</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>Workplan</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>One door, one term: the three ways to add an account read 'Link it (re</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>Status / Comments</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>Founder: approve the mock MoneyKeel/documents/home-screen/moneykeel_pres_mock_ways-to-add-an-account_v10.html (every affected screen, before and after). Claude: then build all of it the same day, with the tests and the canon row</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="inlineStr"/>
-    </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" s="3" t="n">
-        <v>46</v>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>Nothing recorded which design each screen was built from. The Build 53 Net worth and Performance finals (networth-FINAL.html, performance-FINAL.html, the two Net worth PDFs, Net worth screens 01 to 11) were filed under networth-and-performance/archive/ on 2026-09-01, which marks them replaced. They were not replaced. Six hours of mocks then started from the wrong files. CORRECTION 2026-09-14: Buil</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>Workplan</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>Nothing recorded which design each screen was built from. The Build 53</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>Status / Comments</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>Claude: done 2026-09-14 — Build 53 files matched by exact content and recorded in MoneyKeel/documents/standards/moneykeel_pres_spec_design-each-screen-was-built-from_v01.md. Founder: (1) confirm Net worth = v5 + square corners; (2) say whether to draw Net worth v6 from the Build 53 code (v5 with squ</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="inlineStr"/>
-    </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" s="3" t="n">
-        <v>47</v>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>Net worth v07 — the three ways to add an account on Net worth (first day, the add sheet, the add button), plus every ruling since Build 53 that touches the screen (empty state, Debts, Emergency fund, Stocks / Funds, /month, you entered, expenses, odds to the nearest 5), each marked</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>Workplan</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>Net worth v07 — the three ways to add an account on Net worth (first d</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>Status / Comments</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Founder: say yes to v08, or name a mark. Also: today's money for the retirement figures and tax on taxable withdrawals (recommended); whether dark/light bars replace the Plan tab's quiet labels. Claude: once approved, record v08 as the current Net worth design, archive v06, then build marks 1–4 and </t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr"/>
-    </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>The retirement sentence (Net worth, Plan, Home) prints future dollars without saying so, and the odds calculation charges no tax on withdrawals from taxable accounts — found checking the founder's question on v07 ($4.1M at 65 is about $2.0M in today's money)</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>Workplan</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The retirement sentence (Net worth, Plan, Home) prints future dollars </t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>Status / Comments</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>Founder: say whether to show today's money and to tax taxable withdrawals (recommended). Claude: then write both as findings on the master rows (MK-XS-M-002 and the pot/leftover figures) before any code.</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr"/>
-    </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>LAUNCH ANSWER LIST — 61 things need you for Net worth, Cash flow and Performance to be launch-ready</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>Workplan</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>LAUNCH ANSWER LIST — 61 things need you for Net worth, Cash flow and P</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>Status / Comments</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>His ask, 2026-09-29: ‘Give me a list of files, tabs, and rows I need to answer for NW, CF, Performance sections of the app to be complete.’ Open MoneyKeel/documents/other/moneykeel_calc_plan_launch-answer-list_v01.xlsx. Five tabs: Read me, EVERYTHING, and one per module. Every line names its FILE, i</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I34"/>
+  <autoFilter ref="A1:I29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4070,10 +3325,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
     <col width="51" customWidth="1" min="4" max="4"/>
@@ -4087,7 +3342,7 @@
     <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>12 things to answer for Cash flow</t>
+          <t>6 things to answer for Cash flow</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -4157,9 +3412,9 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="45" customHeight="1">
+    <row r="4" ht="60" customHeight="1">
       <c r="A4" s="3" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
@@ -4168,7 +3423,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>1. Is this row right — the words on screen, the formula, the inputs, the decisions and what it says when it cannot be computed? Say yes, or say what changes.</t>
+          <t>VERIFY 53 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -4183,24 +3438,24 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>MK-CF-M-049 — = Planned surplus</t>
+          <t>all 53 unverified rows on this tab</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>YOUR ANSWER — use the same number</t>
+          <t>ROW VERIFIED — founder, date and how</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+          <t>The module cannot be called launch-ready: a TESTED row is proved to match the code, not proved to be right.</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr"/>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="3" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -4209,12 +3464,12 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>1. Is this row right — the words on screen, the formula, the inputs, the decisions and what it says when it cannot be computed? Say yes, or say what changes.</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: How is income + spending captured, at what frequency, and what about cash / unconnected cards?</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+          <t>moneykeel_log_decisions_v01.xlsx</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -4224,24 +3479,24 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>MK-CF-M-050 — each planned line</t>
+          <t>DEC-0503</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>YOUR ANSWER — use the same number</t>
+          <t>Open question on this decision — for him</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr"/>
     </row>
-    <row r="6" ht="45" customHeight="1">
+    <row r="6" ht="30" customHeight="1">
       <c r="A6" s="3" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -4250,12 +3505,12 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>1. Is this row right — the words on screen, the formula, the inputs, the decisions and what it says when it cannot be computed? Say yes, or say what changes.</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Are the month bars cash flows -- inflow / outflow?</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+          <t>moneykeel_log_decisions_v01.xlsx</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -4265,24 +3520,24 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>MK-CF-M-051 — Inflow</t>
+          <t>DEC-0512</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>YOUR ANSWER — use the same number</t>
+          <t>Open question on this decision — for him</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr"/>
     </row>
-    <row r="7" ht="45" customHeight="1">
+    <row r="7" ht="60" customHeight="1">
       <c r="A7" s="3" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
@@ -4291,39 +3546,39 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>1. Is this row right — the words on screen, the formula, the inputs, the decisions and what it says when it cannot be computed? Say yes, or say what changes.</t>
+          <t>Stand-in ages when the birth year is missing: the Retirement cockpit and Insights assume 45, the cash-flow model and the draw steer assume 68, the onboarding helper 35 (or 65 for the retirement age). Your rule R2 says an unknown input gives no number and a reason.</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>cashflow</t>
+          <t>Workplan</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>MK-CF-M-052 — Outflow (expenses + debt)</t>
+          <t>Stand-in ages when the birth year is missing: the Retirement cockpit a</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>YOUR ANSWER — use the same number</t>
+          <t>Status / Comments</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+          <t>Founder: say what those screens show when the birth year is missing (ask for it in place? show the door?); then Claude: mock first, then code</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr"/>
     </row>
-    <row r="8" ht="45" customHeight="1">
+    <row r="8" ht="60" customHeight="1">
       <c r="A8" s="3" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
@@ -4332,39 +3587,39 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>1. Is this row right — the words on screen, the formula, the inputs, the decisions and what it says when it cannot be computed? Say yes, or say what changes.</t>
+          <t>Q-CF-2 'how much have I spent this month, against the plan, and what is left' — eight figures DRAFTED on MK-CF-O-003 thisMonth: expected inflow, planned outflow, planned surplus, each planned line, inflow so far, outflow so far, surplus so far, each received line (MK-CF-M-047…054)</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>cashflow</t>
+          <t>Workplan</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>MK-CF-M-053 — = Surplus</t>
+          <t>Q-CF-2 'how much have I spent this month, against the plan, and what i</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>YOUR ANSWER — use the same number</t>
+          <t>Status / Comments</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+          <t>Founder: read the eight rows on the master's cashflow tab (Row status says DRAFT) and say yes, or say what changes. Claude: the moment you do, the Cash flow screen, the month detail screen and Home's cell move behind the door and stop working figures out themselves</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr"/>
     </row>
-    <row r="9" ht="45" customHeight="1">
+    <row r="9" ht="60" customHeight="1">
       <c r="A9" s="3" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
@@ -4373,284 +3628,38 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>1. Is this row right — the words on screen, the formula, the inputs, the decisions and what it says when it cannot be computed? Say yes, or say what changes.</t>
+          <t>Two word collisions found building v08: Cash flow's 'Add by hand' adds an EXPENSE (the same words as the account door), and Settings still says 'Disconnect' beside 'Linked accounts'</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>cashflow</t>
+          <t>Workplan</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>MK-CF-M-054 — each received line</t>
+          <t>Two word collisions found building v08: Cash flow's 'Add by hand' adds</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>YOUR ANSWER — use the same number</t>
+          <t>Status / Comments</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+          <t>Founder: say whether Cash flow's door should read differently (for example 'Add an expense by hand') and whether Disconnect becomes 'Unlink'.</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr"/>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Cash flow</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>VERIFY 53 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>cashflow</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>all 53 unverified rows on this tab</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>ROW VERIFIED — founder, date and how</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>The module cannot be called launch-ready: a TESTED row is proved to match the code, not proved to be right.</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr"/>
-    </row>
-    <row r="11" ht="45" customHeight="1">
-      <c r="A11" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Cash flow</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: How is income + spending captured, at what frequency, and what about cash / unconnected cards?</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>cashflow</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>DEC-0503</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>Open question on this decision — for him</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Cash flow</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Are the month bars cash flows -- inflow / outflow?</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>cashflow</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>DEC-0512</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>Open question on this decision — for him</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr"/>
-    </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="3" t="n">
-        <v>43</v>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Cash flow</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Stand-in ages when the birth year is missing: the Retirement cockpit and Insights assume 45, the cash-flow model and the draw steer assume 68, the onboarding helper 35 (or 65 for the retirement age). Your rule R2 says an unknown input gives no number and a reason.</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>Workplan</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>Stand-in ages when the birth year is missing: the Retirement cockpit a</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>Status / Comments</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>Founder: say what those screens show when the birth year is missing (ask for it in place? show the door?); then Claude: mock first, then code</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr"/>
-    </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Cash flow</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Q-CF-2 'how much have I spent this month, against the plan, and what is left' — eight figures DRAFTED on MK-CF-O-003 thisMonth: expected inflow, planned outflow, planned surplus, each planned line, inflow so far, outflow so far, surplus so far, each received line (MK-CF-M-047…054)</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>Workplan</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>Q-CF-2 'how much have I spent this month, against the plan, and what i</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>Status / Comments</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>Founder: read the eight rows on the master's cashflow tab (Row status says DRAFT) and say yes, or say what changes. Claude: the moment you do, the Cash flow screen, the month detail screen and Home's cell move behind the door and stop working figures out themselves</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr"/>
-    </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" s="3" t="n">
-        <v>49</v>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Cash flow</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Two word collisions found building v08: Cash flow's 'Add by hand' adds an EXPENSE (the same words as the account door), and Settings still says 'Disconnect' beside 'Linked accounts'</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>Workplan</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>Two word collisions found building v08: Cash flow's 'Add by hand' adds</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>Status / Comments</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>Founder: say whether Cash flow's door should read differently (for example 'Add an expense by hand') and whether Disconnect becomes 'Unlink'.</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I15"/>
+  <autoFilter ref="A1:I9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4661,15 +3670,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
     <col width="51" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="52" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
     <col width="42" customWidth="1" min="7" max="7"/>
     <col width="52" customWidth="1" min="8" max="8"/>
     <col width="40" customWidth="1" min="9" max="9"/>
@@ -4678,7 +3687,7 @@
     <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>7 things to answer for Performance</t>
+          <t>5 things to answer for Performance</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -4750,7 +3759,7 @@
     </row>
     <row r="4" ht="60" customHeight="1">
       <c r="A4" s="3" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
@@ -4759,9 +3768,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>1. Is this row right — the words on screen, the formula, the inputs, the decisions and what it says when it cannot be computed? Say yes, or say what changes.
-Q33 — Which index should each asset class be compared against, and should the person be able to change it?
-Q51 — Home reads "you +3.69% · market +2.83% · ahead by 0.85%". The two sides are not measured the same way: YOUR figure counts the dividends and interest you received (your ruling of 2026-09-25, one meaning of return), while the MARKET figure is the index's PRICE only, because no price feed we have gives an index's dividends. So "</t>
+          <t>VERIFY 11 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -4776,24 +3783,24 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>MK-PF-M-008 — market +X%</t>
+          <t>all 11 unverified rows on this tab</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>YOUR ANSWER — use the same number</t>
+          <t>ROW VERIFIED — founder, date and how</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+          <t>The module cannot be called launch-ready: a TESTED row is proved to match the code, not proved to be right.</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr"/>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="3" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -4802,40 +3809,39 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>1. Is this row right — the words on screen, the formula, the inputs, the decisions and what it says when it cannot be computed? Say yes, or say what changes.
-Q52 — MK-PF-F-026 moneyWeightedReturn is a true personal return — it solves for the rate that makes what you paid in, on the days you paid it in, equal what you have now. It is built, correct and reached by NO SCREEN: the card that showed it was removed by the Performance design you approved on 2026-09-25. The Return the screen does show is a different calculation (Modified Dietz) that also calls itself money-weighted. Do we delete the u</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Total return captures both realized and unrealized gains? Is there any place we display realized P/L, unrealized P/L, total dividend, and total interest separately?</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+          <t>moneykeel_log_decisions_v01.xlsx</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>multiple_screens</t>
+          <t>performance</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>MK-XS-M-004 — ▲ up/▼ down $X (Y%) this month · Return · YOUR RETURN</t>
+          <t>DEC-0479</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>YOUR ANSWER — use the same number</t>
+          <t>Open question on this decision — for him</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>The figure stays DRAFT, and it is on MORE THAN ONE screen — so the answer settles what every screen showing it says.</t>
+          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr"/>
     </row>
-    <row r="6" ht="60" customHeight="1">
+    <row r="6" ht="30" customHeight="1">
       <c r="A6" s="3" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -4844,12 +3850,12 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>VERIFY 11 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: stocks with dividends - will it also show dividends received?</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+          <t>moneykeel_log_decisions_v01.xlsx</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -4859,24 +3865,24 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>all 11 unverified rows on this tab</t>
+          <t>DEC-0483</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>ROW VERIFIED — founder, date and how</t>
+          <t>Open question on this decision — for him</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>The module cannot be called launch-ready: a TESTED row is proved to match the code, not proved to be right.</t>
+          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr"/>
     </row>
-    <row r="7" ht="60" customHeight="1">
+    <row r="7" ht="30" customHeight="1">
       <c r="A7" s="3" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
@@ -4885,7 +3891,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Total return captures both realized and unrealized gains? Is there any place we display realized P/L, unrealized P/L, total dividend, and total interest separately?</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: What's the level of details displayed and how?r</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -4900,7 +3906,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>DEC-0479</t>
+          <t>DEC-0497</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -4917,7 +3923,7 @@
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="3" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
@@ -4926,7 +3932,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: stocks with dividends - will it also show dividends received?</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Invest: what level of detail, and how?</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -4941,7 +3947,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>DEC-0483</t>
+          <t>DEC-0510</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -4956,90 +3962,8 @@
       </c>
       <c r="I8" s="3" t="inlineStr"/>
     </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="3" t="n">
-        <v>37</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: What's the level of details displayed and how?r</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>performance</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>DEC-0497</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>Open question on this decision — for him</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="3" t="n">
-        <v>38</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Invest: what level of detail, and how?</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>performance</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>DEC-0510</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>Open question on this decision — for him</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I10"/>
+  <autoFilter ref="A1:I8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_launch-answer-list_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_launch-answer-list_v01.xlsx
@@ -14,8 +14,8 @@
     <sheet name="Performance" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'EVERYTHING'!$A$1:$I$40</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Net worth'!$A$1:$I$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'EVERYTHING'!$A$1:$I$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Net worth'!$A$1:$I$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Cash flow'!$A$1:$I$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Performance'!$A$1:$I$8</definedName>
   </definedNames>
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -551,7 +551,7 @@
     <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>37 things to answer</t>
+          <t>33 things to answer</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -621,7 +621,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
+    <row r="4" ht="45" customHeight="1">
       <c r="A4" s="3" t="n">
         <v>1</v>
       </c>
@@ -632,7 +632,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Q17 — "Return on cash + investments" counts money you paid in as a gain. Is the LABEL wrong, or the FORMULA? Fixing the formula means removing deposits and withdrawals before measuring.</t>
+          <t>Q15 — An institution word we do not recognise: refuse the line and ask you, or book it as unclassified with no direction? The old sign-guess is what minted the $1.4 million.</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-002 — Return on cash + investments</t>
+          <t>MK-NW-M-019 — Income</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Q32 — The trend survives on a new device but the walk behind it does not. Should the trend say so, or show quietly?</t>
+          <t>Q01 — Is Quantity for a bond the FACE amount (e.g. 227,000) with the price quoted per $100 of face, or the number of bonds? It decides how value and gain are worked out.</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-003 — the trend line</t>
+          <t>MK-NW-M-023 — Face value</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr"/>
     </row>
-    <row r="6" ht="60" customHeight="1">
+    <row r="6" ht="45" customHeight="1">
       <c r="A6" s="3" t="n">
         <v>3</v>
       </c>
@@ -714,10 +714,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q10 — What order of evidence decides an asset's class? Draft: the institution's own class field, then the shape of the identifier (option symbols, nine-character bond numbers, currency codes), then words in the name, then ask you.
-Q11 — When nothing matches: refuse the line and ask, or park it as unclassified? Parking keeps the totals right and hides a gap; refusing is honest and stops the import.
-Q12 — Does the person's own answer always win and stick, even when the next sync disagrees? That is today's rule for holdings — confirm it holds for every class.
-Q13 — Commodities: is a fund that </t>
+          <t>Q04 — "Annual income" on a bond: the last twelve months actually received, or the forward estimate from today\'s coupon? Both are defensible and they differ.</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -732,7 +729,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-007 — class rows — by class, institution or type</t>
+          <t>MK-NW-M-024 — Interest payments</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -758,7 +755,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Q14 — What should a MIXED account be called on screen, when it holds several classes at once?</t>
+          <t>Q05 — Accrued interest: do we work it out ourselves — which needs a day-count rule per bond type — or only show what the institution gives us?</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -773,7 +770,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-008 — each account and its balance</t>
+          <t>MK-NW-M-026 — Yield if held to maturity</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -788,7 +785,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr"/>
     </row>
-    <row r="8" ht="45" customHeight="1">
+    <row r="8" ht="60" customHeight="1">
       <c r="A8" s="3" t="n">
         <v>5</v>
       </c>
@@ -799,7 +796,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Q15 — An institution word we do not recognise: refuse the line and ask you, or book it as unclassified with no direction? The old sign-guess is what minted the $1.4 million.</t>
+          <t>Q34 — Approve the exact wording for the average-price rule (info dot + column Q): 'Shares with no recorded purchase price are left out of the average. N of your shares are in that position.' — and the refusal: 'Average not available — none of these shares has a recorded price.'</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -814,7 +811,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-019 — Income</t>
+          <t>MK-NW-M-032 — Price paid (average)</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -829,7 +826,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr"/>
     </row>
-    <row r="9" ht="45" customHeight="1">
+    <row r="9" ht="60" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>6</v>
       </c>
@@ -840,7 +837,8 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Q01 — Is Quantity for a bond the FACE amount (e.g. 227,000) with the price quoted per $100 of face, or the number of bonds? It decides how value and gain are worked out.</t>
+          <t>Q35 — Approve the exact label and the canon phrase for the twelve-month window. Proposed: 'Dividends received (trailing twelve months)' here, and 'trailing twelve months' in the other four places (spelled out — no initialism).
+Q36 — Dividends on this card: THIS account only, matching 'Realized from sales' beside it? Recommended: yes.</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -855,7 +853,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-023 — Face value</t>
+          <t>MK-NW-M-034 — Dividends received (12 mo)</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -870,7 +868,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr"/>
     </row>
-    <row r="10" ht="45" customHeight="1">
+    <row r="10" ht="60" customHeight="1">
       <c r="A10" s="3" t="n">
         <v>7</v>
       </c>
@@ -881,7 +879,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Q04 — "Annual income" on a bond: the last twelve months actually received, or the forward estimate from today\'s coupon? Both are defensible and they differ.</t>
+          <t>Q37 — For a connected account: log an 'Opening holding' row per broker lot at first sync (dated the lot's purchase date, at the broker's cost) so every later sale is covered — recommended — or keep 'not counted + say so' for pre-history purchases?</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -896,7 +894,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-024 — Interest payments</t>
+          <t>MK-NW-M-035 — Realized gain from your buys and sells</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -911,7 +909,7 @@
       </c>
       <c r="I10" s="3" t="inlineStr"/>
     </row>
-    <row r="11" ht="45" customHeight="1">
+    <row r="11" ht="60" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>8</v>
       </c>
@@ -922,7 +920,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Q05 — Accrued interest: do we work it out ourselves — which needs a day-count rule per bond type — or only show what the institution gives us?</t>
+          <t>Q20 — A lot with no recorded purchase price is skipped, so its gain is simply absent. Should the screen SAY so — "gain not counted for N shares, no purchase price on record" — rather than quietly reporting less?</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -937,7 +935,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-026 — Yield if held to maturity</t>
+          <t>MK-NW-M-036 — Gain — long-term (held over 1 yr)</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -963,7 +961,8 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Q34 — Approve the exact wording for the average-price rule (info dot + column Q): 'Shares with no recorded purchase price are left out of the average. N of your shares are in that position.' — and the refusal: 'Average not available — none of these shares has a recorded price.'</t>
+          <t>Q03 — Certificates of deposit: under Fixed Income, or their own class? They carry a term, a rate and an early-withdrawal penalty that a bond does not.
+Q38 — Your bond display rule, three specifics before the mock: (1) 'quantity' for a bond = the number of bonds (each of face $1,000), or the total face amount? (2) 'earned interest' = the INTEREST rows recorded in the ledger for this bond — the only source we have — yes? (3) 'current price' = price per $100 of face as brokers quote it, or the dollar value of the position? Then I mock the bond card and screen before any code.</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -978,7 +977,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-032 — Price paid (average)</t>
+          <t>MK-NW-M-041 — total value of your bonds</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -1004,8 +1003,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Q35 — Approve the exact label and the canon phrase for the twelve-month window. Proposed: 'Dividends received (trailing twelve months)' here, and 'trailing twelve months' in the other four places (spelled out — no initialism).
-Q36 — Dividends on this card: THIS account only, matching 'Realized from sales' beside it? Recommended: yes.</t>
+          <t>VERIFY 64 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -1020,17 +1018,17 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-034 — Dividends received (12 mo)</t>
+          <t>all 64 unverified rows on this tab</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>YOUR ANSWER — use the same number</t>
+          <t>ROW VERIFIED — founder, date and how</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+          <t>The module cannot be called launch-ready: a TESTED row is proved to match the code, not proved to be right.</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr"/>
@@ -1041,12 +1039,12 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Net worth</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Q37 — For a connected account: log an 'Opening holding' row per broker lot at first sync (dated the lot's purchase date, at the broker's cost) so every later sale is covered — recommended — or keep 'not counted + say so' for pre-history purchases?</t>
+          <t>VERIFY 19 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -1056,22 +1054,22 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>networth</t>
+          <t>performance</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-035 — Realized gain from your buys and sells</t>
+          <t>all 19 unverified rows on this tab</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>YOUR ANSWER — use the same number</t>
+          <t>ROW VERIFIED — founder, date and how</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+          <t>The module cannot be called launch-ready: a TESTED row is proved to match the code, not proved to be right.</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr"/>
@@ -1082,12 +1080,12 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Net worth</t>
+          <t>Cash flow</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Q20 — A lot with no recorded purchase price is skipped, so its gain is simply absent. Should the screen SAY so — "gain not counted for N shares, no purchase price on record" — rather than quietly reporting less?</t>
+          <t>VERIFY 64 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -1097,27 +1095,27 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>networth</t>
+          <t>cashflow</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-036 — Gain — long-term (held over 1 yr)</t>
+          <t>all 64 unverified rows on this tab</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>YOUR ANSWER — use the same number</t>
+          <t>ROW VERIFIED — founder, date and how</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+          <t>The module cannot be called launch-ready: a TESTED row is proved to match the code, not proved to be right.</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr"/>
     </row>
-    <row r="16" ht="60" customHeight="1">
+    <row r="16" ht="30" customHeight="1">
       <c r="A16" s="3" t="n">
         <v>13</v>
       </c>
@@ -1128,13 +1126,12 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Q03 — Certificates of deposit: under Fixed Income, or their own class? They carry a term, a rate and an early-withdrawal penalty that a bond does not.
-Q38 — Your bond display rule, three specifics before the mock: (1) 'quantity' for a bond = the number of bonds (each of face $1,000), or the total face amount? (2) 'earned interest' = the INTEREST rows recorded in the ledger for this bond — the only source we have — yes? (3) 'current price' = price per $100 of face as brokers quote it, or the dollar value of the position? Then I mock the bond card and screen before any code.</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Plain line - means line graph?</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+          <t>moneykeel_log_decisions_v01.xlsx</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1144,22 +1141,22 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-041 — total value of your bonds</t>
+          <t>DEC-0469</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>YOUR ANSWER — use the same number</t>
+          <t>Open question on this decision — for him</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr"/>
     </row>
-    <row r="17" ht="60" customHeight="1">
+    <row r="17" ht="30" customHeight="1">
       <c r="A17" s="3" t="n">
         <v>14</v>
       </c>
@@ -1170,12 +1167,12 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>VERIFY 48 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: what does screen look like for manual update?</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+          <t>moneykeel_log_decisions_v01.xlsx</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -1185,58 +1182,58 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>all 48 unverified rows on this tab</t>
+          <t>DEC-0470</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>ROW VERIFIED — founder, date and how</t>
+          <t>Open question on this decision — for him</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>The module cannot be called launch-ready: a TESTED row is proved to match the code, not proved to be right.</t>
+          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr"/>
     </row>
-    <row r="18" ht="60" customHeight="1">
+    <row r="18" ht="45" customHeight="1">
       <c r="A18" s="3" t="n">
         <v>15</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Net worth</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>VERIFY 11 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: do we capture only balance or all individual portfolio holding e.g. AMZN 100 stocks ….</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+          <t>moneykeel_log_decisions_v01.xlsx</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>performance</t>
+          <t>networth</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>all 11 unverified rows on this tab</t>
+          <t>DEC-0475</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>ROW VERIFIED — founder, date and how</t>
+          <t>Open question on this decision — for him</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>The module cannot be called launch-ready: a TESTED row is proved to match the code, not proved to be right.</t>
+          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr"/>
@@ -1247,37 +1244,37 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Cash flow</t>
+          <t>Net worth</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>VERIFY 53 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: When dividend is captured is it automatically added to income or cash? Similarly, is there a way captical gain is captured and displayed somewhere?</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+          <t>moneykeel_log_decisions_v01.xlsx</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>cashflow</t>
+          <t>networth</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>all 53 unverified rows on this tab</t>
+          <t>DEC-0476</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>ROW VERIFIED — founder, date and how</t>
+          <t>Open question on this decision — for him</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>The module cannot be called launch-ready: a TESTED row is proved to match the code, not proved to be right.</t>
+          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr"/>
@@ -1293,7 +1290,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Plain line - means line graph?</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Is this manual, imported or connected and captured via Plaid?</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -1308,7 +1305,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>DEC-0469</t>
+          <t>DEC-0478</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -1323,18 +1320,18 @@
       </c>
       <c r="I20" s="3" t="inlineStr"/>
     </row>
-    <row r="21" ht="30" customHeight="1">
+    <row r="21" ht="60" customHeight="1">
       <c r="A21" s="3" t="n">
         <v>18</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Net worth</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: what does screen look like for manual update?</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Total return captures both realized and unrealized gains? Is there any place we display realized P/L, unrealized P/L, total dividend, and total interest separately?</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -1344,12 +1341,12 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>networth</t>
+          <t>performance</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>DEC-0470</t>
+          <t>DEC-0479</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -1364,18 +1361,18 @@
       </c>
       <c r="I21" s="3" t="inlineStr"/>
     </row>
-    <row r="22" ht="45" customHeight="1">
+    <row r="22" ht="30" customHeight="1">
       <c r="A22" s="3" t="n">
         <v>19</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Net worth</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: do we capture only balance or all individual portfolio holding e.g. AMZN 100 stocks ….</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: stocks with dividends - will it also show dividends received?</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -1385,12 +1382,12 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>networth</t>
+          <t>performance</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>DEC-0475</t>
+          <t>DEC-0483</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -1405,18 +1402,18 @@
       </c>
       <c r="I22" s="3" t="inlineStr"/>
     </row>
-    <row r="23" ht="60" customHeight="1">
+    <row r="23" ht="30" customHeight="1">
       <c r="A23" s="3" t="n">
         <v>20</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Net worth</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: When dividend is captured is it automatically added to income or cash? Similarly, is there a way captical gain is captured and displayed somewhere?</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: What's the level of details displayed and how?r</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -1426,12 +1423,12 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>networth</t>
+          <t>performance</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>DEC-0476</t>
+          <t>DEC-0497</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -1452,12 +1449,12 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Net worth</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Is this manual, imported or connected and captured via Plaid?</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Invest: what level of detail, and how?</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -1467,12 +1464,12 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>networth</t>
+          <t>performance</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>DEC-0478</t>
+          <t>DEC-0510</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -1487,18 +1484,18 @@
       </c>
       <c r="I24" s="3" t="inlineStr"/>
     </row>
-    <row r="25" ht="60" customHeight="1">
+    <row r="25" ht="45" customHeight="1">
       <c r="A25" s="3" t="n">
         <v>22</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Cash flow</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Total return captures both realized and unrealized gains? Is there any place we display realized P/L, unrealized P/L, total dividend, and total interest separately?</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: How is income + spending captured, at what frequency, and what about cash / unconnected cards?</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -1508,12 +1505,12 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>performance</t>
+          <t>cashflow</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>DEC-0479</t>
+          <t>DEC-0503</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -1534,12 +1531,12 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Cash flow</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: stocks with dividends - will it also show dividends received?</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Are the month bars cash flows -- inflow / outflow?</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -1549,12 +1546,12 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>performance</t>
+          <t>cashflow</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>DEC-0483</t>
+          <t>DEC-0512</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -1569,89 +1566,89 @@
       </c>
       <c r="I26" s="3" t="inlineStr"/>
     </row>
-    <row r="27" ht="30" customHeight="1">
+    <row r="27" ht="60" customHeight="1">
       <c r="A27" s="3" t="n">
         <v>24</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Net worth</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: What's the level of details displayed and how?r</t>
+          <t>Commit — the branch was 278 files behind on 2026-09-14; committed since: 983805a (catch-up), f0e1d6d (Net worth v08), c4f2679 (the Since crash), 727e22a (Performance v14). Nothing is pushed — the branch taxonomy-v1.0.7 is local only.</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
+          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>performance</t>
+          <t>Workplan</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>DEC-0497</t>
+          <t>Commit — the branch was 278 files behind on 2026-09-14; committed sinc</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>Open question on this decision — for him</t>
+          <t>Status / Comments</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
+          <t>Founder: say when to PUSH. (Note 2026-09-26: the Xcode licence has not been accepted on this Mac, so the normal git refuses to run — "sudo xcodebuild -license accept" once, then git works everywhere again.)</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr"/>
     </row>
-    <row r="28" ht="30" customHeight="1">
+    <row r="28" ht="60" customHeight="1">
       <c r="A28" s="3" t="n">
         <v>25</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Net worth</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Invest: what level of detail, and how?</t>
+          <t>EIGHT live mocks still DRAW words the canon retired (measured 2026-09-26 over the drawn frames, not the commentary): cash-flow this-month v06 ("In (take-home)", "spending") · income end-to-end v07 ("A usual month", "Gross a year") · look-ahead v03 ("/mo") · money-four-tabs v01 ("In (take-home)", "Out (", "/mo", "spending") · account-detail v01 ("Connected ·") · empty-state-pattern v01 ("WHAT YOU O</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
+          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>performance</t>
+          <t>Workplan</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>DEC-0510</t>
+          <t>EIGHT live mocks still DRAW words the canon retired (measured 2026-09-</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>Open question on this decision — for him</t>
+          <t>Status / Comments</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
+          <t>Founder: say whether each gets a new version on the canon now (old archived), or at its next change. Plan v05 already carries its list inside the file as mark 14 and is fixed when v06 is drawn.</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr"/>
     </row>
-    <row r="29" ht="45" customHeight="1">
+    <row r="29" ht="60" customHeight="1">
       <c r="A29" s="3" t="n">
         <v>26</v>
       </c>
@@ -1662,37 +1659,37 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: How is income + spending captured, at what frequency, and what about cash / unconnected cards?</t>
+          <t>Stand-in ages when the birth year is missing: the Retirement cockpit and Insights assume 45, the cash-flow model and the draw steer assume 68, the onboarding helper 35 (or 65 for the retirement age). Your rule R2 says an unknown input gives no number and a reason.</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
+          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>cashflow</t>
+          <t>Workplan</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>DEC-0503</t>
+          <t>Stand-in ages when the birth year is missing: the Retirement cockpit a</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>Open question on this decision — for him</t>
+          <t>Status / Comments</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
+          <t>Founder: say what those screens show when the birth year is missing (ask for it in place? show the door?); then Claude: mock first, then code</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr"/>
     </row>
-    <row r="30" ht="30" customHeight="1">
+    <row r="30" ht="60" customHeight="1">
       <c r="A30" s="3" t="n">
         <v>27</v>
       </c>
@@ -1703,32 +1700,32 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Are the month bars cash flows -- inflow / outflow?</t>
+          <t>Q-CF-2 'how much have I spent this month, against the plan, and what is left' — eight figures DRAFTED on MK-CF-O-003 thisMonth: expected inflow, planned outflow, planned surplus, each planned line, inflow so far, outflow so far, surplus so far, each received line (MK-CF-M-047…054)</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
+          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>cashflow</t>
+          <t>Workplan</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>DEC-0512</t>
+          <t>Q-CF-2 'how much have I spent this month, against the plan, and what i</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>Open question on this decision — for him</t>
+          <t>Status / Comments</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
+          <t>Founder: read the eight rows on the master's cashflow tab (Row status says DRAFT) and say yes, or say what changes. Claude: the moment you do, the Cash flow screen, the month detail screen and Home's cell move behind the door and stop working figures out themselves</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr"/>
@@ -1744,7 +1741,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Commit — the branch was 278 files behind on 2026-09-14; committed since: 983805a (catch-up), f0e1d6d (Net worth v08), c4f2679 (the Since crash), 727e22a (Performance v14). Nothing is pushed — the branch taxonomy-v1.0.7 is local only.</t>
+          <t>One door, one term: the three ways to add an account read 'Link it (read-only)', 'Add by hand' and 'Import from a file' on every screen, under the heading 'How do you want to add an account?' — Home, Sharpen your plan, the Plan tab, Net worth (first day and the add sheet), the Connect an account screen and Performance</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -1759,7 +1756,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>Commit — the branch was 278 files behind on 2026-09-14; committed sinc</t>
+          <t>One door, one term: the three ways to add an account read 'Link it (re</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -1769,7 +1766,7 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>Founder: say when to PUSH. (Note 2026-09-26: the Xcode licence has not been accepted on this Mac, so the normal git refuses to run — "sudo xcodebuild -license accept" once, then git works everywhere again.)</t>
+          <t>Founder: approve the mock MoneyKeel/documents/home-screen/moneykeel_pres_mock_ways-to-add-an-account_v10.html (every affected screen, before and after). Claude: then build all of it the same day, with the tests and the canon row</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr"/>
@@ -1785,7 +1782,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>EIGHT live mocks still DRAW words the canon retired (measured 2026-09-26 over the drawn frames, not the commentary): cash-flow this-month v06 ("In (take-home)", "spending") · income end-to-end v07 ("A usual month", "Gross a year") · look-ahead v03 ("/mo") · money-four-tabs v01 ("In (take-home)", "Out (", "/mo", "spending") · account-detail v01 ("Connected ·") · empty-state-pattern v01 ("WHAT YOU O</t>
+          <t>Nothing recorded which design each screen was built from. The Build 53 Net worth and Performance finals (networth-FINAL.html, performance-FINAL.html, the two Net worth PDFs, Net worth screens 01 to 11) were filed under networth-and-performance/archive/ on 2026-09-01, which marks them replaced. They were not replaced. Six hours of mocks then started from the wrong files. CORRECTION 2026-09-14: Buil</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -1800,7 +1797,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>EIGHT live mocks still DRAW words the canon retired (measured 2026-09-</t>
+          <t>Nothing recorded which design each screen was built from. The Build 53</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -1810,7 +1807,7 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Founder: say whether each gets a new version on the canon now (old archived), or at its next change. Plan v05 already carries its list inside the file as mark 14 and is fixed when v06 is drawn.</t>
+          <t>Claude: done 2026-09-14 — Build 53 files matched by exact content and recorded in MoneyKeel/documents/standards/moneykeel_pres_spec_design-each-screen-was-built-from_v01.md. Founder: (1) confirm Net worth = v5 + square corners; (2) say whether to draw Net worth v6 from the Build 53 code (v5 with squ</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr"/>
@@ -1821,12 +1818,12 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Cash flow</t>
+          <t>Net worth</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Stand-in ages when the birth year is missing: the Retirement cockpit and Insights assume 45, the cash-flow model and the draw steer assume 68, the onboarding helper 35 (or 65 for the retirement age). Your rule R2 says an unknown input gives no number and a reason.</t>
+          <t>Net worth v07 — the three ways to add an account on Net worth (first day, the add sheet, the add button), plus every ruling since Build 53 that touches the screen (empty state, Debts, Emergency fund, Stocks / Funds, /month, you entered, expenses, odds to the nearest 5), each marked</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -1841,7 +1838,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>Stand-in ages when the birth year is missing: the Retirement cockpit a</t>
+          <t>Net worth v07 — the three ways to add an account on Net worth (first d</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -1851,7 +1848,7 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>Founder: say what those screens show when the birth year is missing (ask for it in place? show the door?); then Claude: mock first, then code</t>
+          <t xml:space="preserve">Founder: say yes to v08, or name a mark. Also: today's money for the retirement figures and tax on taxable withdrawals (recommended); whether dark/light bars replace the Plan tab's quiet labels. Claude: once approved, record v08 as the current Net worth design, archive v06, then build marks 1–4 and </t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr"/>
@@ -1862,12 +1859,12 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Cash flow</t>
+          <t>Net worth</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Q-CF-2 'how much have I spent this month, against the plan, and what is left' — eight figures DRAFTED on MK-CF-O-003 thisMonth: expected inflow, planned outflow, planned surplus, each planned line, inflow so far, outflow so far, surplus so far, each received line (MK-CF-M-047…054)</t>
+          <t>The retirement sentence (Net worth, Plan, Home) prints future dollars without saying so, and the odds calculation charges no tax on withdrawals from taxable accounts — found checking the founder's question on v07 ($4.1M at 65 is about $2.0M in today's money)</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -1882,7 +1879,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Q-CF-2 'how much have I spent this month, against the plan, and what i</t>
+          <t xml:space="preserve">The retirement sentence (Net worth, Plan, Home) prints future dollars </t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -1892,7 +1889,7 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Founder: read the eight rows on the master's cashflow tab (Row status says DRAFT) and say yes, or say what changes. Claude: the moment you do, the Cash flow screen, the month detail screen and Home's cell move behind the door and stop working figures out themselves</t>
+          <t>Founder: say whether to show today's money and to tax taxable withdrawals (recommended). Claude: then write both as findings on the master rows (MK-XS-M-002 and the pot/leftover figures) before any code.</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr"/>
@@ -1903,12 +1900,12 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Net worth</t>
+          <t>Cash flow</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>One door, one term: the three ways to add an account read 'Link it (read-only)', 'Add by hand' and 'Import from a file' on every screen, under the heading 'How do you want to add an account?' — Home, Sharpen your plan, the Plan tab, Net worth (first day and the add sheet), the Connect an account screen and Performance</t>
+          <t>Two word collisions found building v08: Cash flow's 'Add by hand' adds an EXPENSE (the same words as the account door), and Settings still says 'Disconnect' beside 'Linked accounts'</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -1923,7 +1920,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>One door, one term: the three ways to add an account read 'Link it (re</t>
+          <t>Two word collisions found building v08: Cash flow's 'Add by hand' adds</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -1933,7 +1930,7 @@
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>Founder: approve the mock MoneyKeel/documents/home-screen/moneykeel_pres_mock_ways-to-add-an-account_v10.html (every affected screen, before and after). Claude: then build all of it the same day, with the tests and the canon row</t>
+          <t>Founder: say whether Cash flow's door should read differently (for example 'Add an expense by hand') and whether Disconnect becomes 'Unlink'.</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr"/>
@@ -1949,7 +1946,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Nothing recorded which design each screen was built from. The Build 53 Net worth and Performance finals (networth-FINAL.html, performance-FINAL.html, the two Net worth PDFs, Net worth screens 01 to 11) were filed under networth-and-performance/archive/ on 2026-09-01, which marks them replaced. They were not replaced. Six hours of mocks then started from the wrong files. CORRECTION 2026-09-14: Buil</t>
+          <t>LAUNCH ANSWER LIST — 61 things need you for Net worth, Cash flow and Performance to be launch-ready</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -1964,7 +1961,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Nothing recorded which design each screen was built from. The Build 53</t>
+          <t>LAUNCH ANSWER LIST — 61 things need you for Net worth, Cash flow and P</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -1974,177 +1971,13 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Claude: done 2026-09-14 — Build 53 files matched by exact content and recorded in MoneyKeel/documents/standards/moneykeel_pres_spec_design-each-screen-was-built-from_v01.md. Founder: (1) confirm Net worth = v5 + square corners; (2) say whether to draw Net worth v6 from the Build 53 code (v5 with squ</t>
+          <t>His ask, 2026-09-29: ‘Give me a list of files, tabs, and rows I need to answer for NW, CF, Performance sections of the app to be complete.’ Open MoneyKeel/documents/other/moneykeel_calc_plan_launch-answer-list_v01.xlsx. Five tabs: Read me, EVERYTHING, and one per module. Every line names its FILE, i</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr"/>
     </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>Net worth v07 — the three ways to add an account on Net worth (first day, the add sheet, the add button), plus every ruling since Build 53 that touches the screen (empty state, Debts, Emergency fund, Stocks / Funds, /month, you entered, expenses, odds to the nearest 5), each marked</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>Workplan</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>Net worth v07 — the three ways to add an account on Net worth (first d</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>Status / Comments</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Founder: say yes to v08, or name a mark. Also: today's money for the retirement figures and tax on taxable withdrawals (recommended); whether dark/light bars replace the Plan tab's quiet labels. Claude: once approved, record v08 as the current Net worth design, archive v06, then build marks 1–4 and </t>
-        </is>
-      </c>
-      <c r="I37" s="3" t="inlineStr"/>
-    </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>The retirement sentence (Net worth, Plan, Home) prints future dollars without saying so, and the odds calculation charges no tax on withdrawals from taxable accounts — found checking the founder's question on v07 ($4.1M at 65 is about $2.0M in today's money)</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>Workplan</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The retirement sentence (Net worth, Plan, Home) prints future dollars </t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>Status / Comments</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>Founder: say whether to show today's money and to tax taxable withdrawals (recommended). Claude: then write both as findings on the master rows (MK-XS-M-002 and the pot/leftover figures) before any code.</t>
-        </is>
-      </c>
-      <c r="I38" s="3" t="inlineStr"/>
-    </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" s="3" t="n">
-        <v>36</v>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>Cash flow</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>Two word collisions found building v08: Cash flow's 'Add by hand' adds an EXPENSE (the same words as the account door), and Settings still says 'Disconnect' beside 'Linked accounts'</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>Workplan</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>Two word collisions found building v08: Cash flow's 'Add by hand' adds</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>Status / Comments</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>Founder: say whether Cash flow's door should read differently (for example 'Add an expense by hand') and whether Disconnect becomes 'Unlink'.</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr"/>
-    </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" s="3" t="n">
-        <v>37</v>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>LAUNCH ANSWER LIST — 61 things need you for Net worth, Cash flow and Performance to be launch-ready</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>Workplan</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>LAUNCH ANSWER LIST — 61 things need you for Net worth, Cash flow and P</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t>Status / Comments</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>His ask, 2026-09-29: ‘Give me a list of files, tabs, and rows I need to answer for NW, CF, Performance sections of the app to be complete.’ Open MoneyKeel/documents/other/moneykeel_calc_plan_launch-answer-list_v01.xlsx. Five tabs: Read me, EVERYTHING, and one per module. Every line names its FILE, i</t>
-        </is>
-      </c>
-      <c r="I40" s="3" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I40"/>
+  <autoFilter ref="A1:I36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2155,7 +1988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2172,7 +2005,7 @@
     <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>26 things to answer for Net worth</t>
+          <t>22 things to answer for Net worth</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -2242,7 +2075,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
+    <row r="4" ht="45" customHeight="1">
       <c r="A4" s="3" t="n">
         <v>1</v>
       </c>
@@ -2253,7 +2086,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Q17 — "Return on cash + investments" counts money you paid in as a gain. Is the LABEL wrong, or the FORMULA? Fixing the formula means removing deposits and withdrawals before measuring.</t>
+          <t>Q15 — An institution word we do not recognise: refuse the line and ask you, or book it as unclassified with no direction? The old sign-guess is what minted the $1.4 million.</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -2268,7 +2101,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-002 — Return on cash + investments</t>
+          <t>MK-NW-M-019 — Income</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -2294,7 +2127,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Q32 — The trend survives on a new device but the walk behind it does not. Should the trend say so, or show quietly?</t>
+          <t>Q01 — Is Quantity for a bond the FACE amount (e.g. 227,000) with the price quoted per $100 of face, or the number of bonds? It decides how value and gain are worked out.</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -2309,7 +2142,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-003 — the trend line</t>
+          <t>MK-NW-M-023 — Face value</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -2324,7 +2157,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr"/>
     </row>
-    <row r="6" ht="60" customHeight="1">
+    <row r="6" ht="45" customHeight="1">
       <c r="A6" s="3" t="n">
         <v>3</v>
       </c>
@@ -2335,10 +2168,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q10 — What order of evidence decides an asset's class? Draft: the institution's own class field, then the shape of the identifier (option symbols, nine-character bond numbers, currency codes), then words in the name, then ask you.
-Q11 — When nothing matches: refuse the line and ask, or park it as unclassified? Parking keeps the totals right and hides a gap; refusing is honest and stops the import.
-Q12 — Does the person's own answer always win and stick, even when the next sync disagrees? That is today's rule for holdings — confirm it holds for every class.
-Q13 — Commodities: is a fund that </t>
+          <t>Q04 — "Annual income" on a bond: the last twelve months actually received, or the forward estimate from today\'s coupon? Both are defensible and they differ.</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -2353,7 +2183,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-007 — class rows — by class, institution or type</t>
+          <t>MK-NW-M-024 — Interest payments</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -2379,7 +2209,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Q14 — What should a MIXED account be called on screen, when it holds several classes at once?</t>
+          <t>Q05 — Accrued interest: do we work it out ourselves — which needs a day-count rule per bond type — or only show what the institution gives us?</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -2394,7 +2224,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-008 — each account and its balance</t>
+          <t>MK-NW-M-026 — Yield if held to maturity</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -2409,7 +2239,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr"/>
     </row>
-    <row r="8" ht="45" customHeight="1">
+    <row r="8" ht="60" customHeight="1">
       <c r="A8" s="3" t="n">
         <v>5</v>
       </c>
@@ -2420,7 +2250,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Q15 — An institution word we do not recognise: refuse the line and ask you, or book it as unclassified with no direction? The old sign-guess is what minted the $1.4 million.</t>
+          <t>Q34 — Approve the exact wording for the average-price rule (info dot + column Q): 'Shares with no recorded purchase price are left out of the average. N of your shares are in that position.' — and the refusal: 'Average not available — none of these shares has a recorded price.'</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -2435,7 +2265,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-019 — Income</t>
+          <t>MK-NW-M-032 — Price paid (average)</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -2450,7 +2280,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr"/>
     </row>
-    <row r="9" ht="45" customHeight="1">
+    <row r="9" ht="60" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>6</v>
       </c>
@@ -2461,7 +2291,8 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Q01 — Is Quantity for a bond the FACE amount (e.g. 227,000) with the price quoted per $100 of face, or the number of bonds? It decides how value and gain are worked out.</t>
+          <t>Q35 — Approve the exact label and the canon phrase for the twelve-month window. Proposed: 'Dividends received (trailing twelve months)' here, and 'trailing twelve months' in the other four places (spelled out — no initialism).
+Q36 — Dividends on this card: THIS account only, matching 'Realized from sales' beside it? Recommended: yes.</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -2476,7 +2307,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-023 — Face value</t>
+          <t>MK-NW-M-034 — Dividends received (12 mo)</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -2491,7 +2322,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr"/>
     </row>
-    <row r="10" ht="45" customHeight="1">
+    <row r="10" ht="60" customHeight="1">
       <c r="A10" s="3" t="n">
         <v>7</v>
       </c>
@@ -2502,7 +2333,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Q04 — "Annual income" on a bond: the last twelve months actually received, or the forward estimate from today\'s coupon? Both are defensible and they differ.</t>
+          <t>Q37 — For a connected account: log an 'Opening holding' row per broker lot at first sync (dated the lot's purchase date, at the broker's cost) so every later sale is covered — recommended — or keep 'not counted + say so' for pre-history purchases?</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -2517,7 +2348,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-024 — Interest payments</t>
+          <t>MK-NW-M-035 — Realized gain from your buys and sells</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -2532,7 +2363,7 @@
       </c>
       <c r="I10" s="3" t="inlineStr"/>
     </row>
-    <row r="11" ht="45" customHeight="1">
+    <row r="11" ht="60" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>8</v>
       </c>
@@ -2543,7 +2374,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Q05 — Accrued interest: do we work it out ourselves — which needs a day-count rule per bond type — or only show what the institution gives us?</t>
+          <t>Q20 — A lot with no recorded purchase price is skipped, so its gain is simply absent. Should the screen SAY so — "gain not counted for N shares, no purchase price on record" — rather than quietly reporting less?</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -2558,7 +2389,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-026 — Yield if held to maturity</t>
+          <t>MK-NW-M-036 — Gain — long-term (held over 1 yr)</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -2584,7 +2415,8 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Q34 — Approve the exact wording for the average-price rule (info dot + column Q): 'Shares with no recorded purchase price are left out of the average. N of your shares are in that position.' — and the refusal: 'Average not available — none of these shares has a recorded price.'</t>
+          <t>Q03 — Certificates of deposit: under Fixed Income, or their own class? They carry a term, a rate and an early-withdrawal penalty that a bond does not.
+Q38 — Your bond display rule, three specifics before the mock: (1) 'quantity' for a bond = the number of bonds (each of face $1,000), or the total face amount? (2) 'earned interest' = the INTEREST rows recorded in the ledger for this bond — the only source we have — yes? (3) 'current price' = price per $100 of face as brokers quote it, or the dollar value of the position? Then I mock the bond card and screen before any code.</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -2599,7 +2431,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-032 — Price paid (average)</t>
+          <t>MK-NW-M-041 — total value of your bonds</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -2625,8 +2457,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Q35 — Approve the exact label and the canon phrase for the twelve-month window. Proposed: 'Dividends received (trailing twelve months)' here, and 'trailing twelve months' in the other four places (spelled out — no initialism).
-Q36 — Dividends on this card: THIS account only, matching 'Realized from sales' beside it? Recommended: yes.</t>
+          <t>VERIFY 64 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -2641,24 +2472,24 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-034 — Dividends received (12 mo)</t>
+          <t>all 64 unverified rows on this tab</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>YOUR ANSWER — use the same number</t>
+          <t>ROW VERIFIED — founder, date and how</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+          <t>The module cannot be called launch-ready: a TESTED row is proved to match the code, not proved to be right.</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr"/>
     </row>
-    <row r="14" ht="60" customHeight="1">
+    <row r="14" ht="30" customHeight="1">
       <c r="A14" s="3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
@@ -2667,12 +2498,12 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Q37 — For a connected account: log an 'Opening holding' row per broker lot at first sync (dated the lot's purchase date, at the broker's cost) so every later sale is covered — recommended — or keep 'not counted + say so' for pre-history purchases?</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Plain line - means line graph?</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+          <t>moneykeel_log_decisions_v01.xlsx</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -2682,24 +2513,24 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-035 — Realized gain from your buys and sells</t>
+          <t>DEC-0469</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>YOUR ANSWER — use the same number</t>
+          <t>Open question on this decision — for him</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr"/>
     </row>
-    <row r="15" ht="60" customHeight="1">
+    <row r="15" ht="30" customHeight="1">
       <c r="A15" s="3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
@@ -2708,12 +2539,12 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Q20 — A lot with no recorded purchase price is skipped, so its gain is simply absent. Should the screen SAY so — "gain not counted for N shares, no purchase price on record" — rather than quietly reporting less?</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: what does screen look like for manual update?</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+          <t>moneykeel_log_decisions_v01.xlsx</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -2723,24 +2554,24 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-036 — Gain — long-term (held over 1 yr)</t>
+          <t>DEC-0470</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>YOUR ANSWER — use the same number</t>
+          <t>Open question on this decision — for him</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr"/>
     </row>
-    <row r="16" ht="60" customHeight="1">
+    <row r="16" ht="45" customHeight="1">
       <c r="A16" s="3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
@@ -2749,13 +2580,12 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Q03 — Certificates of deposit: under Fixed Income, or their own class? They carry a term, a rate and an early-withdrawal penalty that a bond does not.
-Q38 — Your bond display rule, three specifics before the mock: (1) 'quantity' for a bond = the number of bonds (each of face $1,000), or the total face amount? (2) 'earned interest' = the INTEREST rows recorded in the ledger for this bond — the only source we have — yes? (3) 'current price' = price per $100 of face as brokers quote it, or the dollar value of the position? Then I mock the bond card and screen before any code.</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: do we capture only balance or all individual portfolio holding e.g. AMZN 100 stocks ….</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+          <t>moneykeel_log_decisions_v01.xlsx</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -2765,24 +2595,24 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-041 — total value of your bonds</t>
+          <t>DEC-0475</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>YOUR ANSWER — use the same number</t>
+          <t>Open question on this decision — for him</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr"/>
     </row>
     <row r="17" ht="60" customHeight="1">
       <c r="A17" s="3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
@@ -2791,12 +2621,12 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>VERIFY 48 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: When dividend is captured is it automatically added to income or cash? Similarly, is there a way captical gain is captured and displayed somewhere?</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+          <t>moneykeel_log_decisions_v01.xlsx</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -2806,17 +2636,17 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>all 48 unverified rows on this tab</t>
+          <t>DEC-0476</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>ROW VERIFIED — founder, date and how</t>
+          <t>Open question on this decision — for him</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>The module cannot be called launch-ready: a TESTED row is proved to match the code, not proved to be right.</t>
+          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr"/>
@@ -2832,7 +2662,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Plain line - means line graph?</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Is this manual, imported or connected and captured via Plaid?</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -2847,7 +2677,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>DEC-0469</t>
+          <t>DEC-0478</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -2862,9 +2692,9 @@
       </c>
       <c r="I18" s="3" t="inlineStr"/>
     </row>
-    <row r="19" ht="30" customHeight="1">
+    <row r="19" ht="60" customHeight="1">
       <c r="A19" s="3" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
@@ -2873,39 +2703,39 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: what does screen look like for manual update?</t>
+          <t>Commit — the branch was 278 files behind on 2026-09-14; committed since: 983805a (catch-up), f0e1d6d (Net worth v08), c4f2679 (the Since crash), 727e22a (Performance v14). Nothing is pushed — the branch taxonomy-v1.0.7 is local only.</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
+          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>networth</t>
+          <t>Workplan</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>DEC-0470</t>
+          <t>Commit — the branch was 278 files behind on 2026-09-14; committed sinc</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Open question on this decision — for him</t>
+          <t>Status / Comments</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
+          <t>Founder: say when to PUSH. (Note 2026-09-26: the Xcode licence has not been accepted on this Mac, so the normal git refuses to run — "sudo xcodebuild -license accept" once, then git works everywhere again.)</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr"/>
     </row>
-    <row r="20" ht="45" customHeight="1">
+    <row r="20" ht="60" customHeight="1">
       <c r="A20" s="3" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
@@ -2914,39 +2744,39 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: do we capture only balance or all individual portfolio holding e.g. AMZN 100 stocks ….</t>
+          <t>EIGHT live mocks still DRAW words the canon retired (measured 2026-09-26 over the drawn frames, not the commentary): cash-flow this-month v06 ("In (take-home)", "spending") · income end-to-end v07 ("A usual month", "Gross a year") · look-ahead v03 ("/mo") · money-four-tabs v01 ("In (take-home)", "Out (", "/mo", "spending") · account-detail v01 ("Connected ·") · empty-state-pattern v01 ("WHAT YOU O</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
+          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>networth</t>
+          <t>Workplan</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>DEC-0475</t>
+          <t>EIGHT live mocks still DRAW words the canon retired (measured 2026-09-</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Open question on this decision — for him</t>
+          <t>Status / Comments</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
+          <t>Founder: say whether each gets a new version on the canon now (old archived), or at its next change. Plan v05 already carries its list inside the file as mark 14 and is fixed when v06 is drawn.</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr"/>
     </row>
     <row r="21" ht="60" customHeight="1">
       <c r="A21" s="3" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
@@ -2955,39 +2785,39 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: When dividend is captured is it automatically added to income or cash? Similarly, is there a way captical gain is captured and displayed somewhere?</t>
+          <t>One door, one term: the three ways to add an account read 'Link it (read-only)', 'Add by hand' and 'Import from a file' on every screen, under the heading 'How do you want to add an account?' — Home, Sharpen your plan, the Plan tab, Net worth (first day and the add sheet), the Connect an account screen and Performance</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
+          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>networth</t>
+          <t>Workplan</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>DEC-0476</t>
+          <t>One door, one term: the three ways to add an account read 'Link it (re</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Open question on this decision — for him</t>
+          <t>Status / Comments</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
+          <t>Founder: approve the mock MoneyKeel/documents/home-screen/moneykeel_pres_mock_ways-to-add-an-account_v10.html (every affected screen, before and after). Claude: then build all of it the same day, with the tests and the canon row</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr"/>
     </row>
-    <row r="22" ht="30" customHeight="1">
+    <row r="22" ht="60" customHeight="1">
       <c r="A22" s="3" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
@@ -2996,39 +2826,39 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Is this manual, imported or connected and captured via Plaid?</t>
+          <t>Nothing recorded which design each screen was built from. The Build 53 Net worth and Performance finals (networth-FINAL.html, performance-FINAL.html, the two Net worth PDFs, Net worth screens 01 to 11) were filed under networth-and-performance/archive/ on 2026-09-01, which marks them replaced. They were not replaced. Six hours of mocks then started from the wrong files. CORRECTION 2026-09-14: Buil</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
+          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>networth</t>
+          <t>Workplan</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>DEC-0478</t>
+          <t>Nothing recorded which design each screen was built from. The Build 53</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>Open question on this decision — for him</t>
+          <t>Status / Comments</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
+          <t>Claude: done 2026-09-14 — Build 53 files matched by exact content and recorded in MoneyKeel/documents/standards/moneykeel_pres_spec_design-each-screen-was-built-from_v01.md. Founder: (1) confirm Net worth = v5 + square corners; (2) say whether to draw Net worth v6 from the Build 53 code (v5 with squ</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr"/>
     </row>
     <row r="23" ht="60" customHeight="1">
       <c r="A23" s="3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
@@ -3037,7 +2867,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Commit — the branch was 278 files behind on 2026-09-14; committed since: 983805a (catch-up), f0e1d6d (Net worth v08), c4f2679 (the Since crash), 727e22a (Performance v14). Nothing is pushed — the branch taxonomy-v1.0.7 is local only.</t>
+          <t>Net worth v07 — the three ways to add an account on Net worth (first day, the add sheet, the add button), plus every ruling since Build 53 that touches the screen (empty state, Debts, Emergency fund, Stocks / Funds, /month, you entered, expenses, odds to the nearest 5), each marked</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -3052,7 +2882,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Commit — the branch was 278 files behind on 2026-09-14; committed sinc</t>
+          <t>Net worth v07 — the three ways to add an account on Net worth (first d</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -3062,14 +2892,14 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Founder: say when to PUSH. (Note 2026-09-26: the Xcode licence has not been accepted on this Mac, so the normal git refuses to run — "sudo xcodebuild -license accept" once, then git works everywhere again.)</t>
+          <t xml:space="preserve">Founder: say yes to v08, or name a mark. Also: today's money for the retirement figures and tax on taxable withdrawals (recommended); whether dark/light bars replace the Plan tab's quiet labels. Claude: once approved, record v08 as the current Net worth design, archive v06, then build marks 1–4 and </t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr"/>
     </row>
     <row r="24" ht="60" customHeight="1">
       <c r="A24" s="3" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
@@ -3078,7 +2908,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>EIGHT live mocks still DRAW words the canon retired (measured 2026-09-26 over the drawn frames, not the commentary): cash-flow this-month v06 ("In (take-home)", "spending") · income end-to-end v07 ("A usual month", "Gross a year") · look-ahead v03 ("/mo") · money-four-tabs v01 ("In (take-home)", "Out (", "/mo", "spending") · account-detail v01 ("Connected ·") · empty-state-pattern v01 ("WHAT YOU O</t>
+          <t>The retirement sentence (Net worth, Plan, Home) prints future dollars without saying so, and the odds calculation charges no tax on withdrawals from taxable accounts — found checking the founder's question on v07 ($4.1M at 65 is about $2.0M in today's money)</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -3093,7 +2923,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>EIGHT live mocks still DRAW words the canon retired (measured 2026-09-</t>
+          <t xml:space="preserve">The retirement sentence (Net worth, Plan, Home) prints future dollars </t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -3103,14 +2933,14 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Founder: say whether each gets a new version on the canon now (old archived), or at its next change. Plan v05 already carries its list inside the file as mark 14 and is fixed when v06 is drawn.</t>
+          <t>Founder: say whether to show today's money and to tax taxable withdrawals (recommended). Claude: then write both as findings on the master rows (MK-XS-M-002 and the pot/leftover figures) before any code.</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr"/>
     </row>
     <row r="25" ht="60" customHeight="1">
       <c r="A25" s="3" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
@@ -3119,7 +2949,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>One door, one term: the three ways to add an account read 'Link it (read-only)', 'Add by hand' and 'Import from a file' on every screen, under the heading 'How do you want to add an account?' — Home, Sharpen your plan, the Plan tab, Net worth (first day and the add sheet), the Connect an account screen and Performance</t>
+          <t>LAUNCH ANSWER LIST — 61 things need you for Net worth, Cash flow and Performance to be launch-ready</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -3134,7 +2964,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>One door, one term: the three ways to add an account read 'Link it (re</t>
+          <t>LAUNCH ANSWER LIST — 61 things need you for Net worth, Cash flow and P</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -3144,177 +2974,13 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Founder: approve the mock MoneyKeel/documents/home-screen/moneykeel_pres_mock_ways-to-add-an-account_v10.html (every affected screen, before and after). Claude: then build all of it the same day, with the tests and the canon row</t>
+          <t>His ask, 2026-09-29: ‘Give me a list of files, tabs, and rows I need to answer for NW, CF, Performance sections of the app to be complete.’ Open MoneyKeel/documents/other/moneykeel_calc_plan_launch-answer-list_v01.xlsx. Five tabs: Read me, EVERYTHING, and one per module. Every line names its FILE, i</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr"/>
     </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>Nothing recorded which design each screen was built from. The Build 53 Net worth and Performance finals (networth-FINAL.html, performance-FINAL.html, the two Net worth PDFs, Net worth screens 01 to 11) were filed under networth-and-performance/archive/ on 2026-09-01, which marks them replaced. They were not replaced. Six hours of mocks then started from the wrong files. CORRECTION 2026-09-14: Buil</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>Workplan</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>Nothing recorded which design each screen was built from. The Build 53</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>Status / Comments</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>Claude: done 2026-09-14 — Build 53 files matched by exact content and recorded in MoneyKeel/documents/standards/moneykeel_pres_spec_design-each-screen-was-built-from_v01.md. Founder: (1) confirm Net worth = v5 + square corners; (2) say whether to draw Net worth v6 from the Build 53 code (v5 with squ</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr"/>
-    </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>Net worth v07 — the three ways to add an account on Net worth (first day, the add sheet, the add button), plus every ruling since Build 53 that touches the screen (empty state, Debts, Emergency fund, Stocks / Funds, /month, you entered, expenses, odds to the nearest 5), each marked</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>Workplan</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>Net worth v07 — the three ways to add an account on Net worth (first d</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>Status / Comments</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Founder: say yes to v08, or name a mark. Also: today's money for the retirement figures and tax on taxable withdrawals (recommended); whether dark/light bars replace the Plan tab's quiet labels. Claude: once approved, record v08 as the current Net worth design, archive v06, then build marks 1–4 and </t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr"/>
-    </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>The retirement sentence (Net worth, Plan, Home) prints future dollars without saying so, and the odds calculation charges no tax on withdrawals from taxable accounts — found checking the founder's question on v07 ($4.1M at 65 is about $2.0M in today's money)</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>Workplan</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The retirement sentence (Net worth, Plan, Home) prints future dollars </t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>Status / Comments</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>Founder: say whether to show today's money and to tax taxable withdrawals (recommended). Claude: then write both as findings on the master rows (MK-XS-M-002 and the pot/leftover figures) before any code.</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr"/>
-    </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" s="3" t="n">
-        <v>37</v>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>LAUNCH ANSWER LIST — 61 things need you for Net worth, Cash flow and Performance to be launch-ready</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>Workplan</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>LAUNCH ANSWER LIST — 61 things need you for Net worth, Cash flow and P</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>Status / Comments</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>His ask, 2026-09-29: ‘Give me a list of files, tabs, and rows I need to answer for NW, CF, Performance sections of the app to be complete.’ Open MoneyKeel/documents/other/moneykeel_calc_plan_launch-answer-list_v01.xlsx. Five tabs: Read me, EVERYTHING, and one per module. Every line names its FILE, i</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I29"/>
+  <autoFilter ref="A1:I25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3414,7 +3080,7 @@
     </row>
     <row r="4" ht="60" customHeight="1">
       <c r="A4" s="3" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
@@ -3423,7 +3089,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>VERIFY 53 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
+          <t>VERIFY 64 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -3438,7 +3104,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>all 53 unverified rows on this tab</t>
+          <t>all 64 unverified rows on this tab</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -3455,7 +3121,7 @@
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="3" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -3496,7 +3162,7 @@
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="3" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -3537,7 +3203,7 @@
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="3" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
@@ -3578,7 +3244,7 @@
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="3" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
@@ -3619,7 +3285,7 @@
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="3" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
@@ -3759,7 +3425,7 @@
     </row>
     <row r="4" ht="60" customHeight="1">
       <c r="A4" s="3" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
@@ -3768,7 +3434,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>VERIFY 11 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
+          <t>VERIFY 19 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -3783,7 +3449,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>all 11 unverified rows on this tab</t>
+          <t>all 19 unverified rows on this tab</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -3800,7 +3466,7 @@
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="3" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -3841,7 +3507,7 @@
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="3" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -3882,7 +3548,7 @@
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="3" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
@@ -3923,7 +3589,7 @@
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="3" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>

--- a/MoneyKeel/documents/other/moneykeel_calc_plan_launch-answer-list_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_launch-answer-list_v01.xlsx
@@ -14,8 +14,8 @@
     <sheet name="Performance" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'EVERYTHING'!$A$1:$I$36</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Net worth'!$A$1:$I$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'EVERYTHING'!$A$1:$I$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Net worth'!$A$1:$I$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Cash flow'!$A$1:$I$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Performance'!$A$1:$I$8</definedName>
   </definedNames>
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -551,7 +551,7 @@
     <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>33 things to answer</t>
+          <t>18 things to answer</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -621,7 +621,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="45" customHeight="1">
+    <row r="4" ht="60" customHeight="1">
       <c r="A4" s="3" t="n">
         <v>1</v>
       </c>
@@ -632,7 +632,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Q15 — An institution word we do not recognise: refuse the line and ask you, or book it as unclassified with no direction? The old sign-guess is what minted the $1.4 million.</t>
+          <t>Q34 — Approve the exact wording for the average-price rule (info dot + column Q): 'Shares with no recorded purchase price are left out of the average. N of your shares are in that position.' — and the refusal: 'Average not available — none of these shares has a recorded price.'</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-019 — Income</t>
+          <t>MK-NW-M-032 — Price paid (average)</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr"/>
     </row>
-    <row r="5" ht="45" customHeight="1">
+    <row r="5" ht="60" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>2</v>
       </c>
@@ -673,7 +673,8 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Q01 — Is Quantity for a bond the FACE amount (e.g. 227,000) with the price quoted per $100 of face, or the number of bonds? It decides how value and gain are worked out.</t>
+          <t>Q35 — Approve the exact label and the canon phrase for the twelve-month window. Proposed: 'Dividends received (trailing twelve months)' here, and 'trailing twelve months' in the other four places (spelled out — no initialism).
+Q36 — Dividends on this card: THIS account only, matching 'Realized from sales' beside it? Recommended: yes.</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -688,7 +689,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-023 — Face value</t>
+          <t>MK-NW-M-034 — Dividends received (12 mo)</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -703,7 +704,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr"/>
     </row>
-    <row r="6" ht="45" customHeight="1">
+    <row r="6" ht="60" customHeight="1">
       <c r="A6" s="3" t="n">
         <v>3</v>
       </c>
@@ -714,7 +715,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Q04 — "Annual income" on a bond: the last twelve months actually received, or the forward estimate from today\'s coupon? Both are defensible and they differ.</t>
+          <t>VERIFY 65 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -729,33 +730,33 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-024 — Interest payments</t>
+          <t>all 65 unverified rows on this tab</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>YOUR ANSWER — use the same number</t>
+          <t>ROW VERIFIED — founder, date and how</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+          <t>The module cannot be called launch-ready: a TESTED row is proved to match the code, not proved to be right.</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr"/>
     </row>
-    <row r="7" ht="45" customHeight="1">
+    <row r="7" ht="60" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>4</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Net worth</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Q05 — Accrued interest: do we work it out ourselves — which needs a day-count rule per bond type — or only show what the institution gives us?</t>
+          <t>VERIFY 21 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -765,22 +766,22 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>networth</t>
+          <t>performance</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-026 — Yield if held to maturity</t>
+          <t>all 21 unverified rows on this tab</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>YOUR ANSWER — use the same number</t>
+          <t>ROW VERIFIED — founder, date and how</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+          <t>The module cannot be called launch-ready: a TESTED row is proved to match the code, not proved to be right.</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr"/>
@@ -791,12 +792,12 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Net worth</t>
+          <t>Cash flow</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Q34 — Approve the exact wording for the average-price rule (info dot + column Q): 'Shares with no recorded purchase price are left out of the average. N of your shares are in that position.' — and the refusal: 'Average not available — none of these shares has a recorded price.'</t>
+          <t>VERIFY 64 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -806,27 +807,27 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>networth</t>
+          <t>cashflow</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-032 — Price paid (average)</t>
+          <t>all 64 unverified rows on this tab</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>YOUR ANSWER — use the same number</t>
+          <t>ROW VERIFIED — founder, date and how</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+          <t>The module cannot be called launch-ready: a TESTED row is proved to match the code, not proved to be right.</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr"/>
     </row>
-    <row r="9" ht="60" customHeight="1">
+    <row r="9" ht="30" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>6</v>
       </c>
@@ -837,13 +838,12 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Q35 — Approve the exact label and the canon phrase for the twelve-month window. Proposed: 'Dividends received (trailing twelve months)' here, and 'trailing twelve months' in the other four places (spelled out — no initialism).
-Q36 — Dividends on this card: THIS account only, matching 'Realized from sales' beside it? Recommended: yes.</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: what does screen look like for manual update?</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+          <t>moneykeel_log_decisions_v01.xlsx</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -853,17 +853,17 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-034 — Dividends received (12 mo)</t>
+          <t>DEC-0470</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>YOUR ANSWER — use the same number</t>
+          <t>Open question on this decision — for him</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr"/>
@@ -874,207 +874,206 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Net worth</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Q37 — For a connected account: log an 'Opening holding' row per broker lot at first sync (dated the lot's purchase date, at the broker's cost) so every later sale is covered — recommended — or keep 'not counted + say so' for pre-history purchases?</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Total return captures both realized and unrealized gains? Is there any place we display realized P/L, unrealized P/L, total dividend, and total interest separately?</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+          <t>moneykeel_log_decisions_v01.xlsx</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>networth</t>
+          <t>performance</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-035 — Realized gain from your buys and sells</t>
+          <t>DEC-0479</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>YOUR ANSWER — use the same number</t>
+          <t>Open question on this decision — for him</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr"/>
     </row>
-    <row r="11" ht="60" customHeight="1">
+    <row r="11" ht="30" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>8</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Net worth</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Q20 — A lot with no recorded purchase price is skipped, so its gain is simply absent. Should the screen SAY so — "gain not counted for N shares, no purchase price on record" — rather than quietly reporting less?</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: stocks with dividends - will it also show dividends received?</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+          <t>moneykeel_log_decisions_v01.xlsx</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>networth</t>
+          <t>performance</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-036 — Gain — long-term (held over 1 yr)</t>
+          <t>DEC-0483</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>YOUR ANSWER — use the same number</t>
+          <t>Open question on this decision — for him</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr"/>
     </row>
-    <row r="12" ht="60" customHeight="1">
+    <row r="12" ht="30" customHeight="1">
       <c r="A12" s="3" t="n">
         <v>9</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Net worth</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Q03 — Certificates of deposit: under Fixed Income, or their own class? They carry a term, a rate and an early-withdrawal penalty that a bond does not.
-Q38 — Your bond display rule, three specifics before the mock: (1) 'quantity' for a bond = the number of bonds (each of face $1,000), or the total face amount? (2) 'earned interest' = the INTEREST rows recorded in the ledger for this bond — the only source we have — yes? (3) 'current price' = price per $100 of face as brokers quote it, or the dollar value of the position? Then I mock the bond card and screen before any code.</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: What's the level of details displayed and how?r</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+          <t>moneykeel_log_decisions_v01.xlsx</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>networth</t>
+          <t>performance</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-041 — total value of your bonds</t>
+          <t>DEC-0497</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>YOUR ANSWER — use the same number</t>
+          <t>Open question on this decision — for him</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr"/>
     </row>
-    <row r="13" ht="60" customHeight="1">
+    <row r="13" ht="30" customHeight="1">
       <c r="A13" s="3" t="n">
         <v>10</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Net worth</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>VERIFY 64 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Invest: what level of detail, and how?</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+          <t>moneykeel_log_decisions_v01.xlsx</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>networth</t>
+          <t>performance</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>all 64 unverified rows on this tab</t>
+          <t>DEC-0510</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>ROW VERIFIED — founder, date and how</t>
+          <t>Open question on this decision — for him</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>The module cannot be called launch-ready: a TESTED row is proved to match the code, not proved to be right.</t>
+          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr"/>
     </row>
-    <row r="14" ht="60" customHeight="1">
+    <row r="14" ht="45" customHeight="1">
       <c r="A14" s="3" t="n">
         <v>11</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Cash flow</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>VERIFY 19 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: How is income + spending captured, at what frequency, and what about cash / unconnected cards?</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+          <t>moneykeel_log_decisions_v01.xlsx</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>performance</t>
+          <t>cashflow</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>all 19 unverified rows on this tab</t>
+          <t>DEC-0503</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>ROW VERIFIED — founder, date and how</t>
+          <t>Open question on this decision — for him</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>The module cannot be called launch-ready: a TESTED row is proved to match the code, not proved to be right.</t>
+          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr"/>
     </row>
-    <row r="15" ht="60" customHeight="1">
+    <row r="15" ht="30" customHeight="1">
       <c r="A15" s="3" t="n">
         <v>12</v>
       </c>
@@ -1085,12 +1084,12 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>VERIFY 64 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Are the month bars cash flows -- inflow / outflow?</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+          <t>moneykeel_log_decisions_v01.xlsx</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1100,22 +1099,22 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>all 64 unverified rows on this tab</t>
+          <t>DEC-0512</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>ROW VERIFIED — founder, date and how</t>
+          <t>Open question on this decision — for him</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>The module cannot be called launch-ready: a TESTED row is proved to match the code, not proved to be right.</t>
+          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr"/>
     </row>
-    <row r="16" ht="30" customHeight="1">
+    <row r="16" ht="60" customHeight="1">
       <c r="A16" s="3" t="n">
         <v>13</v>
       </c>
@@ -1126,114 +1125,114 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Plain line - means line graph?</t>
+          <t>Commit — the branch was 278 files behind on 2026-09-14; committed since: 983805a (catch-up), f0e1d6d (Net worth v08), c4f2679 (the Since crash), 727e22a (Performance v14). Nothing is pushed — the branch taxonomy-v1.0.7 is local only.</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
+          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>networth</t>
+          <t>Workplan</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>DEC-0469</t>
+          <t>Commit — the branch was 278 files behind on 2026-09-14; committed sinc</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>Open question on this decision — for him</t>
+          <t>Status / Comments</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
+          <t>Founder: say when to PUSH. (Note 2026-09-26: the Xcode licence has not been accepted on this Mac, so the normal git refuses to run — "sudo xcodebuild -license accept" once, then git works everywhere again.)</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr"/>
     </row>
-    <row r="17" ht="30" customHeight="1">
+    <row r="17" ht="60" customHeight="1">
       <c r="A17" s="3" t="n">
         <v>14</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Net worth</t>
+          <t>Cash flow</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: what does screen look like for manual update?</t>
+          <t>Stand-in ages when the birth year is missing: the Retirement cockpit and Insights assume 45, the cash-flow model and the draw steer assume 68, the onboarding helper 35 (or 65 for the retirement age). Your rule R2 says an unknown input gives no number and a reason.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
+          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>networth</t>
+          <t>Workplan</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>DEC-0470</t>
+          <t>Stand-in ages when the birth year is missing: the Retirement cockpit a</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Open question on this decision — for him</t>
+          <t>Status / Comments</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
+          <t>Founder: say what those screens show when the birth year is missing (ask for it in place? show the door?); then Claude: mock first, then code</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr"/>
     </row>
-    <row r="18" ht="45" customHeight="1">
+    <row r="18" ht="60" customHeight="1">
       <c r="A18" s="3" t="n">
         <v>15</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Net worth</t>
+          <t>Cash flow</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: do we capture only balance or all individual portfolio holding e.g. AMZN 100 stocks ….</t>
+          <t>Q-CF-2 'how much have I spent this month, against the plan, and what is left' — eight figures DRAFTED on MK-CF-O-003 thisMonth: expected inflow, planned outflow, planned surplus, each planned line, inflow so far, outflow so far, surplus so far, each received line (MK-CF-M-047…054)</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
+          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>networth</t>
+          <t>Workplan</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>DEC-0475</t>
+          <t>Q-CF-2 'how much have I spent this month, against the plan, and what i</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Open question on this decision — for him</t>
+          <t>Status / Comments</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
+          <t>Founder: read the eight rows on the master's cashflow tab (Row status says DRAFT) and say yes, or say what changes. Claude: the moment you do, the Cash flow screen, the month detail screen and Home's cell move behind the door and stop working figures out themselves</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr"/>
@@ -1249,73 +1248,73 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: When dividend is captured is it automatically added to income or cash? Similarly, is there a way captical gain is captured and displayed somewhere?</t>
+          <t>One door, one term: the three ways to add an account read 'Link it (read-only)', 'Add by hand' and 'Import from a file' on every screen, under the heading 'How do you want to add an account?' — Home, Sharpen your plan, the Plan tab, Net worth (first day and the add sheet), the Connect an account screen and Performance</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
+          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>networth</t>
+          <t>Workplan</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>DEC-0476</t>
+          <t>One door, one term: the three ways to add an account read 'Link it (re</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Open question on this decision — for him</t>
+          <t>Status / Comments</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
+          <t>Founder: approve the mock MoneyKeel/documents/home-screen/moneykeel_pres_mock_ways-to-add-an-account_v10.html (every affected screen, before and after). Claude: then build all of it the same day, with the tests and the canon row</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr"/>
     </row>
-    <row r="20" ht="30" customHeight="1">
+    <row r="20" ht="60" customHeight="1">
       <c r="A20" s="3" t="n">
         <v>17</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Net worth</t>
+          <t>Cash flow</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Is this manual, imported or connected and captured via Plaid?</t>
+          <t>Two word collisions found building v08: Cash flow's 'Add by hand' adds an EXPENSE (the same words as the account door), and Settings still says 'Disconnect' beside 'Linked accounts'</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
+          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>networth</t>
+          <t>Workplan</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>DEC-0478</t>
+          <t>Two word collisions found building v08: Cash flow's 'Add by hand' adds</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Open question on this decision — for him</t>
+          <t>Status / Comments</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
+          <t>Founder: say whether Cash flow's door should read differently (for example 'Add an expense by hand') and whether Disconnect becomes 'Unlink'.</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr"/>
@@ -1326,658 +1325,43 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Net worth</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Total return captures both realized and unrealized gains? Is there any place we display realized P/L, unrealized P/L, total dividend, and total interest separately?</t>
+          <t>LAUNCH ANSWER LIST — 61 things need you for Net worth, Cash flow and Performance to be launch-ready</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
+          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>performance</t>
+          <t>Workplan</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>DEC-0479</t>
+          <t>LAUNCH ANSWER LIST — 61 things need you for Net worth, Cash flow and P</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Open question on this decision — for him</t>
+          <t>Status / Comments</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
+          <t>His ask, 2026-09-29: ‘Give me a list of files, tabs, and rows I need to answer for NW, CF, Performance sections of the app to be complete.’ Open MoneyKeel/documents/other/moneykeel_calc_plan_launch-answer-list_v01.xlsx. Five tabs: Read me, EVERYTHING, and one per module. Every line names its FILE, i</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr"/>
     </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: stocks with dividends - will it also show dividends received?</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>performance</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>DEC-0483</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>Open question on this decision — for him</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr"/>
-    </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: What's the level of details displayed and how?r</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>performance</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>DEC-0497</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>Open question on this decision — for him</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr"/>
-    </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Invest: what level of detail, and how?</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>performance</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>DEC-0510</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>Open question on this decision — for him</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr"/>
-    </row>
-    <row r="25" ht="45" customHeight="1">
-      <c r="A25" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>Cash flow</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: How is income + spending captured, at what frequency, and what about cash / unconnected cards?</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>cashflow</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>DEC-0503</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>Open question on this decision — for him</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr"/>
-    </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Cash flow</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Are the month bars cash flows -- inflow / outflow?</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>cashflow</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>DEC-0512</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>Open question on this decision — for him</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr"/>
-    </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>Commit — the branch was 278 files behind on 2026-09-14; committed since: 983805a (catch-up), f0e1d6d (Net worth v08), c4f2679 (the Since crash), 727e22a (Performance v14). Nothing is pushed — the branch taxonomy-v1.0.7 is local only.</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>Workplan</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>Commit — the branch was 278 files behind on 2026-09-14; committed sinc</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>Status / Comments</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>Founder: say when to PUSH. (Note 2026-09-26: the Xcode licence has not been accepted on this Mac, so the normal git refuses to run — "sudo xcodebuild -license accept" once, then git works everywhere again.)</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr"/>
-    </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>EIGHT live mocks still DRAW words the canon retired (measured 2026-09-26 over the drawn frames, not the commentary): cash-flow this-month v06 ("In (take-home)", "spending") · income end-to-end v07 ("A usual month", "Gross a year") · look-ahead v03 ("/mo") · money-four-tabs v01 ("In (take-home)", "Out (", "/mo", "spending") · account-detail v01 ("Connected ·") · empty-state-pattern v01 ("WHAT YOU O</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>Workplan</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>EIGHT live mocks still DRAW words the canon retired (measured 2026-09-</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>Status / Comments</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>Founder: say whether each gets a new version on the canon now (old archived), or at its next change. Plan v05 already carries its list inside the file as mark 14 and is fixed when v06 is drawn.</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr"/>
-    </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>Cash flow</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>Stand-in ages when the birth year is missing: the Retirement cockpit and Insights assume 45, the cash-flow model and the draw steer assume 68, the onboarding helper 35 (or 65 for the retirement age). Your rule R2 says an unknown input gives no number and a reason.</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>Workplan</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>Stand-in ages when the birth year is missing: the Retirement cockpit a</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>Status / Comments</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>Founder: say what those screens show when the birth year is missing (ask for it in place? show the door?); then Claude: mock first, then code</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr"/>
-    </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>Cash flow</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>Q-CF-2 'how much have I spent this month, against the plan, and what is left' — eight figures DRAFTED on MK-CF-O-003 thisMonth: expected inflow, planned outflow, planned surplus, each planned line, inflow so far, outflow so far, surplus so far, each received line (MK-CF-M-047…054)</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>Workplan</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>Q-CF-2 'how much have I spent this month, against the plan, and what i</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>Status / Comments</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>Founder: read the eight rows on the master's cashflow tab (Row status says DRAFT) and say yes, or say what changes. Claude: the moment you do, the Cash flow screen, the month detail screen and Home's cell move behind the door and stop working figures out themselves</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="inlineStr"/>
-    </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>One door, one term: the three ways to add an account read 'Link it (read-only)', 'Add by hand' and 'Import from a file' on every screen, under the heading 'How do you want to add an account?' — Home, Sharpen your plan, the Plan tab, Net worth (first day and the add sheet), the Connect an account screen and Performance</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>Workplan</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>One door, one term: the three ways to add an account read 'Link it (re</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>Status / Comments</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>Founder: approve the mock MoneyKeel/documents/home-screen/moneykeel_pres_mock_ways-to-add-an-account_v10.html (every affected screen, before and after). Claude: then build all of it the same day, with the tests and the canon row</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="inlineStr"/>
-    </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>Nothing recorded which design each screen was built from. The Build 53 Net worth and Performance finals (networth-FINAL.html, performance-FINAL.html, the two Net worth PDFs, Net worth screens 01 to 11) were filed under networth-and-performance/archive/ on 2026-09-01, which marks them replaced. They were not replaced. Six hours of mocks then started from the wrong files. CORRECTION 2026-09-14: Buil</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>Workplan</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>Nothing recorded which design each screen was built from. The Build 53</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>Status / Comments</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>Claude: done 2026-09-14 — Build 53 files matched by exact content and recorded in MoneyKeel/documents/standards/moneykeel_pres_spec_design-each-screen-was-built-from_v01.md. Founder: (1) confirm Net worth = v5 + square corners; (2) say whether to draw Net worth v6 from the Build 53 code (v5 with squ</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr"/>
-    </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>Net worth v07 — the three ways to add an account on Net worth (first day, the add sheet, the add button), plus every ruling since Build 53 that touches the screen (empty state, Debts, Emergency fund, Stocks / Funds, /month, you entered, expenses, odds to the nearest 5), each marked</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>Workplan</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>Net worth v07 — the three ways to add an account on Net worth (first d</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>Status / Comments</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Founder: say yes to v08, or name a mark. Also: today's money for the retirement figures and tax on taxable withdrawals (recommended); whether dark/light bars replace the Plan tab's quiet labels. Claude: once approved, record v08 as the current Net worth design, archive v06, then build marks 1–4 and </t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr"/>
-    </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>The retirement sentence (Net worth, Plan, Home) prints future dollars without saying so, and the odds calculation charges no tax on withdrawals from taxable accounts — found checking the founder's question on v07 ($4.1M at 65 is about $2.0M in today's money)</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>Workplan</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The retirement sentence (Net worth, Plan, Home) prints future dollars </t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>Status / Comments</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>Founder: say whether to show today's money and to tax taxable withdrawals (recommended). Claude: then write both as findings on the master rows (MK-XS-M-002 and the pot/leftover figures) before any code.</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr"/>
-    </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>Cash flow</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>Two word collisions found building v08: Cash flow's 'Add by hand' adds an EXPENSE (the same words as the account door), and Settings still says 'Disconnect' beside 'Linked accounts'</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>Workplan</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>Two word collisions found building v08: Cash flow's 'Add by hand' adds</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>Status / Comments</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>Founder: say whether Cash flow's door should read differently (for example 'Add an expense by hand') and whether Disconnect becomes 'Unlink'.</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="inlineStr"/>
-    </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>LAUNCH ANSWER LIST — 61 things need you for Net worth, Cash flow and Performance to be launch-ready</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>Workplan</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>LAUNCH ANSWER LIST — 61 things need you for Net worth, Cash flow and P</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>Status / Comments</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>His ask, 2026-09-29: ‘Give me a list of files, tabs, and rows I need to answer for NW, CF, Performance sections of the app to be complete.’ Open MoneyKeel/documents/other/moneykeel_calc_plan_launch-answer-list_v01.xlsx. Five tabs: Read me, EVERYTHING, and one per module. Every line names its FILE, i</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I36"/>
+  <autoFilter ref="A1:I21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1988,10 +1372,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
     <col width="51" customWidth="1" min="4" max="4"/>
@@ -2005,7 +1389,7 @@
     <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>22 things to answer for Net worth</t>
+          <t>7 things to answer for Net worth</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -2075,7 +1459,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="45" customHeight="1">
+    <row r="4" ht="60" customHeight="1">
       <c r="A4" s="3" t="n">
         <v>1</v>
       </c>
@@ -2086,7 +1470,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Q15 — An institution word we do not recognise: refuse the line and ask you, or book it as unclassified with no direction? The old sign-guess is what minted the $1.4 million.</t>
+          <t>Q34 — Approve the exact wording for the average-price rule (info dot + column Q): 'Shares with no recorded purchase price are left out of the average. N of your shares are in that position.' — and the refusal: 'Average not available — none of these shares has a recorded price.'</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -2101,7 +1485,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-019 — Income</t>
+          <t>MK-NW-M-032 — Price paid (average)</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -2116,7 +1500,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr"/>
     </row>
-    <row r="5" ht="45" customHeight="1">
+    <row r="5" ht="60" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>2</v>
       </c>
@@ -2127,7 +1511,8 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Q01 — Is Quantity for a bond the FACE amount (e.g. 227,000) with the price quoted per $100 of face, or the number of bonds? It decides how value and gain are worked out.</t>
+          <t>Q35 — Approve the exact label and the canon phrase for the twelve-month window. Proposed: 'Dividends received (trailing twelve months)' here, and 'trailing twelve months' in the other four places (spelled out — no initialism).
+Q36 — Dividends on this card: THIS account only, matching 'Realized from sales' beside it? Recommended: yes.</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -2142,7 +1527,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-023 — Face value</t>
+          <t>MK-NW-M-034 — Dividends received (12 mo)</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -2157,7 +1542,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr"/>
     </row>
-    <row r="6" ht="45" customHeight="1">
+    <row r="6" ht="60" customHeight="1">
       <c r="A6" s="3" t="n">
         <v>3</v>
       </c>
@@ -2168,7 +1553,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Q04 — "Annual income" on a bond: the last twelve months actually received, or the forward estimate from today\'s coupon? Both are defensible and they differ.</t>
+          <t>VERIFY 65 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -2183,24 +1568,24 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-024 — Interest payments</t>
+          <t>all 65 unverified rows on this tab</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>YOUR ANSWER — use the same number</t>
+          <t>ROW VERIFIED — founder, date and how</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+          <t>The module cannot be called launch-ready: a TESTED row is proved to match the code, not proved to be right.</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr"/>
     </row>
-    <row r="7" ht="45" customHeight="1">
+    <row r="7" ht="30" customHeight="1">
       <c r="A7" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
@@ -2209,12 +1594,12 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Q05 — Accrued interest: do we work it out ourselves — which needs a day-count rule per bond type — or only show what the institution gives us?</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: what does screen look like for manual update?</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+          <t>moneykeel_log_decisions_v01.xlsx</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -2224,24 +1609,24 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-026 — Yield if held to maturity</t>
+          <t>DEC-0470</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>YOUR ANSWER — use the same number</t>
+          <t>Open question on this decision — for him</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr"/>
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="3" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
@@ -2250,39 +1635,39 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Q34 — Approve the exact wording for the average-price rule (info dot + column Q): 'Shares with no recorded purchase price are left out of the average. N of your shares are in that position.' — and the refusal: 'Average not available — none of these shares has a recorded price.'</t>
+          <t>Commit — the branch was 278 files behind on 2026-09-14; committed since: 983805a (catch-up), f0e1d6d (Net worth v08), c4f2679 (the Since crash), 727e22a (Performance v14). Nothing is pushed — the branch taxonomy-v1.0.7 is local only.</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>networth</t>
+          <t>Workplan</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-032 — Price paid (average)</t>
+          <t>Commit — the branch was 278 files behind on 2026-09-14; committed sinc</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>YOUR ANSWER — use the same number</t>
+          <t>Status / Comments</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+          <t>Founder: say when to PUSH. (Note 2026-09-26: the Xcode licence has not been accepted on this Mac, so the normal git refuses to run — "sudo xcodebuild -license accept" once, then git works everywhere again.)</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr"/>
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="3" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
@@ -2291,40 +1676,39 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Q35 — Approve the exact label and the canon phrase for the twelve-month window. Proposed: 'Dividends received (trailing twelve months)' here, and 'trailing twelve months' in the other four places (spelled out — no initialism).
-Q36 — Dividends on this card: THIS account only, matching 'Realized from sales' beside it? Recommended: yes.</t>
+          <t>One door, one term: the three ways to add an account read 'Link it (read-only)', 'Add by hand' and 'Import from a file' on every screen, under the heading 'How do you want to add an account?' — Home, Sharpen your plan, the Plan tab, Net worth (first day and the add sheet), the Connect an account screen and Performance</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>networth</t>
+          <t>Workplan</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-034 — Dividends received (12 mo)</t>
+          <t>One door, one term: the three ways to add an account read 'Link it (re</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>YOUR ANSWER — use the same number</t>
+          <t>Status / Comments</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+          <t>Founder: approve the mock MoneyKeel/documents/home-screen/moneykeel_pres_mock_ways-to-add-an-account_v10.html (every affected screen, before and after). Claude: then build all of it the same day, with the tests and the canon row</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr"/>
     </row>
     <row r="10" ht="60" customHeight="1">
       <c r="A10" s="3" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
@@ -2333,654 +1717,38 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Q37 — For a connected account: log an 'Opening holding' row per broker lot at first sync (dated the lot's purchase date, at the broker's cost) so every later sale is covered — recommended — or keep 'not counted + say so' for pre-history purchases?</t>
+          <t>LAUNCH ANSWER LIST — 61 things need you for Net worth, Cash flow and Performance to be launch-ready</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>networth</t>
+          <t>Workplan</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-035 — Realized gain from your buys and sells</t>
+          <t>LAUNCH ANSWER LIST — 61 things need you for Net worth, Cash flow and P</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>YOUR ANSWER — use the same number</t>
+          <t>Status / Comments</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+          <t>His ask, 2026-09-29: ‘Give me a list of files, tabs, and rows I need to answer for NW, CF, Performance sections of the app to be complete.’ Open MoneyKeel/documents/other/moneykeel_calc_plan_launch-answer-list_v01.xlsx. Five tabs: Read me, EVERYTHING, and one per module. Every line names its FILE, i</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr"/>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Q20 — A lot with no recorded purchase price is skipped, so its gain is simply absent. Should the screen SAY so — "gain not counted for N shares, no purchase price on record" — rather than quietly reporting less?</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>networth</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>MK-NW-M-036 — Gain — long-term (held over 1 yr)</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>YOUR ANSWER — use the same number</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr"/>
-    </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Q03 — Certificates of deposit: under Fixed Income, or their own class? They carry a term, a rate and an early-withdrawal penalty that a bond does not.
-Q38 — Your bond display rule, three specifics before the mock: (1) 'quantity' for a bond = the number of bonds (each of face $1,000), or the total face amount? (2) 'earned interest' = the INTEREST rows recorded in the ledger for this bond — the only source we have — yes? (3) 'current price' = price per $100 of face as brokers quote it, or the dollar value of the position? Then I mock the bond card and screen before any code.</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>networth</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>MK-NW-M-041 — total value of your bonds</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>YOUR ANSWER — use the same number</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr"/>
-    </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>VERIFY 64 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>networth</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>all 64 unverified rows on this tab</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>ROW VERIFIED — founder, date and how</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>The module cannot be called launch-ready: a TESTED row is proved to match the code, not proved to be right.</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr"/>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Plain line - means line graph?</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>networth</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>DEC-0469</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>Open question on this decision — for him</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr"/>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: what does screen look like for manual update?</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>networth</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>DEC-0470</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>Open question on this decision — for him</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr"/>
-    </row>
-    <row r="16" ht="45" customHeight="1">
-      <c r="A16" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: do we capture only balance or all individual portfolio holding e.g. AMZN 100 stocks ….</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>networth</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>DEC-0475</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>Open question on this decision — for him</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr"/>
-    </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: When dividend is captured is it automatically added to income or cash? Similarly, is there a way captical gain is captured and displayed somewhere?</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>networth</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>DEC-0476</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>Open question on this decision — for him</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr"/>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Is this manual, imported or connected and captured via Plaid?</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>networth</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>DEC-0478</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>Open question on this decision — for him</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr"/>
-    </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Commit — the branch was 278 files behind on 2026-09-14; committed since: 983805a (catch-up), f0e1d6d (Net worth v08), c4f2679 (the Since crash), 727e22a (Performance v14). Nothing is pushed — the branch taxonomy-v1.0.7 is local only.</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>Workplan</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>Commit — the branch was 278 files behind on 2026-09-14; committed sinc</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>Status / Comments</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>Founder: say when to PUSH. (Note 2026-09-26: the Xcode licence has not been accepted on this Mac, so the normal git refuses to run — "sudo xcodebuild -license accept" once, then git works everywhere again.)</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr"/>
-    </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>EIGHT live mocks still DRAW words the canon retired (measured 2026-09-26 over the drawn frames, not the commentary): cash-flow this-month v06 ("In (take-home)", "spending") · income end-to-end v07 ("A usual month", "Gross a year") · look-ahead v03 ("/mo") · money-four-tabs v01 ("In (take-home)", "Out (", "/mo", "spending") · account-detail v01 ("Connected ·") · empty-state-pattern v01 ("WHAT YOU O</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>Workplan</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>EIGHT live mocks still DRAW words the canon retired (measured 2026-09-</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>Status / Comments</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>Founder: say whether each gets a new version on the canon now (old archived), or at its next change. Plan v05 already carries its list inside the file as mark 14 and is fixed when v06 is drawn.</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr"/>
-    </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>One door, one term: the three ways to add an account read 'Link it (read-only)', 'Add by hand' and 'Import from a file' on every screen, under the heading 'How do you want to add an account?' — Home, Sharpen your plan, the Plan tab, Net worth (first day and the add sheet), the Connect an account screen and Performance</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>Workplan</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>One door, one term: the three ways to add an account read 'Link it (re</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>Status / Comments</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>Founder: approve the mock MoneyKeel/documents/home-screen/moneykeel_pres_mock_ways-to-add-an-account_v10.html (every affected screen, before and after). Claude: then build all of it the same day, with the tests and the canon row</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr"/>
-    </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Nothing recorded which design each screen was built from. The Build 53 Net worth and Performance finals (networth-FINAL.html, performance-FINAL.html, the two Net worth PDFs, Net worth screens 01 to 11) were filed under networth-and-performance/archive/ on 2026-09-01, which marks them replaced. They were not replaced. Six hours of mocks then started from the wrong files. CORRECTION 2026-09-14: Buil</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>Workplan</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>Nothing recorded which design each screen was built from. The Build 53</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>Status / Comments</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>Claude: done 2026-09-14 — Build 53 files matched by exact content and recorded in MoneyKeel/documents/standards/moneykeel_pres_spec_design-each-screen-was-built-from_v01.md. Founder: (1) confirm Net worth = v5 + square corners; (2) say whether to draw Net worth v6 from the Build 53 code (v5 with squ</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr"/>
-    </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>Net worth v07 — the three ways to add an account on Net worth (first day, the add sheet, the add button), plus every ruling since Build 53 that touches the screen (empty state, Debts, Emergency fund, Stocks / Funds, /month, you entered, expenses, odds to the nearest 5), each marked</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>Workplan</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>Net worth v07 — the three ways to add an account on Net worth (first d</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>Status / Comments</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Founder: say yes to v08, or name a mark. Also: today's money for the retirement figures and tax on taxable withdrawals (recommended); whether dark/light bars replace the Plan tab's quiet labels. Claude: once approved, record v08 as the current Net worth design, archive v06, then build marks 1–4 and </t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr"/>
-    </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>The retirement sentence (Net worth, Plan, Home) prints future dollars without saying so, and the odds calculation charges no tax on withdrawals from taxable accounts — found checking the founder's question on v07 ($4.1M at 65 is about $2.0M in today's money)</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>Workplan</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The retirement sentence (Net worth, Plan, Home) prints future dollars </t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>Status / Comments</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>Founder: say whether to show today's money and to tax taxable withdrawals (recommended). Claude: then write both as findings on the master rows (MK-XS-M-002 and the pot/leftover figures) before any code.</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr"/>
-    </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>LAUNCH ANSWER LIST — 61 things need you for Net worth, Cash flow and Performance to be launch-ready</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>Workplan</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>LAUNCH ANSWER LIST — 61 things need you for Net worth, Cash flow and P</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>Status / Comments</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>His ask, 2026-09-29: ‘Give me a list of files, tabs, and rows I need to answer for NW, CF, Performance sections of the app to be complete.’ Open MoneyKeel/documents/other/moneykeel_calc_plan_launch-answer-list_v01.xlsx. Five tabs: Read me, EVERYTHING, and one per module. Every line names its FILE, i</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I25"/>
+  <autoFilter ref="A1:I10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3080,7 +1848,7 @@
     </row>
     <row r="4" ht="60" customHeight="1">
       <c r="A4" s="3" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
@@ -3121,7 +1889,7 @@
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="3" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -3162,7 +1930,7 @@
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="3" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -3203,7 +1971,7 @@
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="3" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
@@ -3244,7 +2012,7 @@
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="3" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
@@ -3285,7 +2053,7 @@
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="3" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
@@ -3425,7 +2193,7 @@
     </row>
     <row r="4" ht="60" customHeight="1">
       <c r="A4" s="3" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
@@ -3434,7 +2202,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>VERIFY 19 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
+          <t>VERIFY 21 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -3449,7 +2217,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>all 19 unverified rows on this tab</t>
+          <t>all 21 unverified rows on this tab</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -3466,7 +2234,7 @@
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="3" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -3507,7 +2275,7 @@
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="3" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -3548,7 +2316,7 @@
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="3" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
@@ -3589,7 +2357,7 @@
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="3" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>

--- a/MoneyKeel/documents/other/moneykeel_calc_plan_launch-answer-list_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_launch-answer-list_v01.xlsx
@@ -14,10 +14,10 @@
     <sheet name="Performance" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'EVERYTHING'!$A$1:$I$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Net worth'!$A$1:$I$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'EVERYTHING'!$A$1:$I$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Net worth'!$A$1:$I$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Cash flow'!$A$1:$I$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Performance'!$A$1:$I$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Performance'!$A$1:$I$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -551,7 +551,7 @@
     <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>18 things to answer</t>
+          <t>11 things to answer</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -632,7 +632,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Q34 — Approve the exact wording for the average-price rule (info dot + column Q): 'Shares with no recorded purchase price are left out of the average. N of your shares are in that position.' — and the refusal: 'Average not available — none of these shares has a recorded price.'</t>
+          <t>VERIFY 71 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -647,17 +647,17 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-032 — Price paid (average)</t>
+          <t>all 71 unverified rows on this tab</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>YOUR ANSWER — use the same number</t>
+          <t>ROW VERIFIED — founder, date and how</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+          <t>The module cannot be called launch-ready: a TESTED row is proved to match the code, not proved to be right.</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr"/>
@@ -668,13 +668,12 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Net worth</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Q35 — Approve the exact label and the canon phrase for the twelve-month window. Proposed: 'Dividends received (trailing twelve months)' here, and 'trailing twelve months' in the other four places (spelled out — no initialism).
-Q36 — Dividends on this card: THIS account only, matching 'Realized from sales' beside it? Recommended: yes.</t>
+          <t>VERIFY 26 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -684,22 +683,22 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>networth</t>
+          <t>performance</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-034 — Dividends received (12 mo)</t>
+          <t>all 26 unverified rows on this tab</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>YOUR ANSWER — use the same number</t>
+          <t>ROW VERIFIED — founder, date and how</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+          <t>The module cannot be called launch-ready: a TESTED row is proved to match the code, not proved to be right.</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr"/>
@@ -710,12 +709,12 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Net worth</t>
+          <t>Cash flow</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>VERIFY 65 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
+          <t>VERIFY 64 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -725,12 +724,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>networth</t>
+          <t>cashflow</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>all 65 unverified rows on this tab</t>
+          <t>all 64 unverified rows on this tab</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -745,48 +744,48 @@
       </c>
       <c r="I6" s="3" t="inlineStr"/>
     </row>
-    <row r="7" ht="60" customHeight="1">
+    <row r="7" ht="45" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>4</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Cash flow</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>VERIFY 21 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: How is income + spending captured, at what frequency, and what about cash / unconnected cards?</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+          <t>moneykeel_log_decisions_v01.xlsx</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>performance</t>
+          <t>cashflow</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>all 21 unverified rows on this tab</t>
+          <t>DEC-0503</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>ROW VERIFIED — founder, date and how</t>
+          <t>Open question on this decision — for him</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>The module cannot be called launch-ready: a TESTED row is proved to match the code, not proved to be right.</t>
+          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr"/>
     </row>
-    <row r="8" ht="60" customHeight="1">
+    <row r="8" ht="30" customHeight="1">
       <c r="A8" s="3" t="n">
         <v>5</v>
       </c>
@@ -797,12 +796,12 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>VERIFY 64 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
+          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Are the month bars cash flows -- inflow / outflow?</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+          <t>moneykeel_log_decisions_v01.xlsx</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -812,22 +811,22 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>all 64 unverified rows on this tab</t>
+          <t>DEC-0512</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>ROW VERIFIED — founder, date and how</t>
+          <t>Open question on this decision — for him</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>The module cannot be called launch-ready: a TESTED row is proved to match the code, not proved to be right.</t>
+          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr"/>
     </row>
-    <row r="9" ht="30" customHeight="1">
+    <row r="9" ht="60" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>6</v>
       </c>
@@ -838,32 +837,32 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: what does screen look like for manual update?</t>
+          <t>Commit — the branch was 278 files behind on 2026-09-14; committed since: 983805a (catch-up), f0e1d6d (Net worth v08), c4f2679 (the Since crash), 727e22a (Performance v14). Nothing is pushed — the branch taxonomy-v1.0.7 is local only.</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
+          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>networth</t>
+          <t>Workplan</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>DEC-0470</t>
+          <t>Commit — the branch was 278 files behind on 2026-09-14; committed sinc</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Open question on this decision — for him</t>
+          <t>Status / Comments</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
+          <t>Founder: say when to PUSH. (Note 2026-09-26: the Xcode licence has not been accepted on this Mac, so the normal git refuses to run — "sudo xcodebuild -license accept" once, then git works everywhere again.)</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr"/>
@@ -874,494 +873,207 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Cash flow</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Total return captures both realized and unrealized gains? Is there any place we display realized P/L, unrealized P/L, total dividend, and total interest separately?</t>
+          <t>Stand-in ages when the birth year is missing: the Retirement cockpit and Insights assume 45, the cash-flow model and the draw steer assume 68, the onboarding helper 35 (or 65 for the retirement age). Your rule R2 says an unknown input gives no number and a reason.</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
+          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>performance</t>
+          <t>Workplan</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>DEC-0479</t>
+          <t>Stand-in ages when the birth year is missing: the Retirement cockpit a</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>Open question on this decision — for him</t>
+          <t>Status / Comments</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
+          <t>Founder: say what those screens show when the birth year is missing (ask for it in place? show the door?); then Claude: mock first, then code</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr"/>
     </row>
-    <row r="11" ht="30" customHeight="1">
+    <row r="11" ht="60" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>8</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Cash flow</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: stocks with dividends - will it also show dividends received?</t>
+          <t>Q-CF-2 'how much have I spent this month, against the plan, and what is left' — eight figures DRAFTED on MK-CF-O-003 thisMonth: expected inflow, planned outflow, planned surplus, each planned line, inflow so far, outflow so far, surplus so far, each received line (MK-CF-M-047…054)</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
+          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>performance</t>
+          <t>Workplan</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>DEC-0483</t>
+          <t>Q-CF-2 'how much have I spent this month, against the plan, and what i</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Open question on this decision — for him</t>
+          <t>Status / Comments</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
+          <t>Founder: read the eight rows on the master's cashflow tab (Row status says DRAFT) and say yes, or say what changes. Claude: the moment you do, the Cash flow screen, the month detail screen and Home's cell move behind the door and stop working figures out themselves</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr"/>
     </row>
-    <row r="12" ht="30" customHeight="1">
+    <row r="12" ht="60" customHeight="1">
       <c r="A12" s="3" t="n">
         <v>9</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Net worth</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: What's the level of details displayed and how?r</t>
+          <t>One door, one term: the three ways to add an account read 'Link it (read-only)', 'Add by hand' and 'Import from a file' on every screen, under the heading 'How do you want to add an account?' — Home, Sharpen your plan, the Plan tab, Net worth (first day and the add sheet), the Connect an account screen and Performance</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
+          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>performance</t>
+          <t>Workplan</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>DEC-0497</t>
+          <t>One door, one term: the three ways to add an account read 'Link it (re</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Open question on this decision — for him</t>
+          <t>Status / Comments</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
+          <t>Founder: approve the mock MoneyKeel/documents/home-screen/moneykeel_pres_mock_ways-to-add-an-account_v10.html (every affected screen, before and after). Claude: then build all of it the same day, with the tests and the canon row</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr"/>
     </row>
-    <row r="13" ht="30" customHeight="1">
+    <row r="13" ht="60" customHeight="1">
       <c r="A13" s="3" t="n">
         <v>10</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Cash flow</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Invest: what level of detail, and how?</t>
+          <t>Two word collisions found building v08: Cash flow's 'Add by hand' adds an EXPENSE (the same words as the account door), and Settings still says 'Disconnect' beside 'Linked accounts'</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
+          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>performance</t>
+          <t>Workplan</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>DEC-0510</t>
+          <t>Two word collisions found building v08: Cash flow's 'Add by hand' adds</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Open question on this decision — for him</t>
+          <t>Status / Comments</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
+          <t>Founder: say whether Cash flow's door should read differently (for example 'Add an expense by hand') and whether Disconnect becomes 'Unlink'.</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr"/>
     </row>
-    <row r="14" ht="45" customHeight="1">
+    <row r="14" ht="60" customHeight="1">
       <c r="A14" s="3" t="n">
         <v>11</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Cash flow</t>
+          <t>Net worth</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: How is income + spending captured, at what frequency, and what about cash / unconnected cards?</t>
+          <t>LAUNCH ANSWER LIST — 61 things need you for Net worth, Cash flow and Performance to be launch-ready</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
+          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>cashflow</t>
+          <t>Workplan</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>DEC-0503</t>
+          <t>LAUNCH ANSWER LIST — 61 things need you for Net worth, Cash flow and P</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>Open question on this decision — for him</t>
+          <t>Status / Comments</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
+          <t>His ask, 2026-09-29: ‘Give me a list of files, tabs, and rows I need to answer for NW, CF, Performance sections of the app to be complete.’ Open MoneyKeel/documents/other/moneykeel_calc_plan_launch-answer-list_v01.xlsx. Five tabs: Read me, EVERYTHING, and one per module. Every line names its FILE, i</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr"/>
     </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Cash flow</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Are the month bars cash flows -- inflow / outflow?</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>cashflow</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>DEC-0512</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>Open question on this decision — for him</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr"/>
-    </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Commit — the branch was 278 files behind on 2026-09-14; committed since: 983805a (catch-up), f0e1d6d (Net worth v08), c4f2679 (the Since crash), 727e22a (Performance v14). Nothing is pushed — the branch taxonomy-v1.0.7 is local only.</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>Workplan</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>Commit — the branch was 278 files behind on 2026-09-14; committed sinc</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>Status / Comments</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>Founder: say when to PUSH. (Note 2026-09-26: the Xcode licence has not been accepted on this Mac, so the normal git refuses to run — "sudo xcodebuild -license accept" once, then git works everywhere again.)</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr"/>
-    </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Cash flow</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>Stand-in ages when the birth year is missing: the Retirement cockpit and Insights assume 45, the cash-flow model and the draw steer assume 68, the onboarding helper 35 (or 65 for the retirement age). Your rule R2 says an unknown input gives no number and a reason.</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>Workplan</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>Stand-in ages when the birth year is missing: the Retirement cockpit a</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>Status / Comments</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>Founder: say what those screens show when the birth year is missing (ask for it in place? show the door?); then Claude: mock first, then code</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr"/>
-    </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Cash flow</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>Q-CF-2 'how much have I spent this month, against the plan, and what is left' — eight figures DRAFTED on MK-CF-O-003 thisMonth: expected inflow, planned outflow, planned surplus, each planned line, inflow so far, outflow so far, surplus so far, each received line (MK-CF-M-047…054)</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>Workplan</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>Q-CF-2 'how much have I spent this month, against the plan, and what i</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>Status / Comments</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>Founder: read the eight rows on the master's cashflow tab (Row status says DRAFT) and say yes, or say what changes. Claude: the moment you do, the Cash flow screen, the month detail screen and Home's cell move behind the door and stop working figures out themselves</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr"/>
-    </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>One door, one term: the three ways to add an account read 'Link it (read-only)', 'Add by hand' and 'Import from a file' on every screen, under the heading 'How do you want to add an account?' — Home, Sharpen your plan, the Plan tab, Net worth (first day and the add sheet), the Connect an account screen and Performance</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>Workplan</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>One door, one term: the three ways to add an account read 'Link it (re</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>Status / Comments</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>Founder: approve the mock MoneyKeel/documents/home-screen/moneykeel_pres_mock_ways-to-add-an-account_v10.html (every affected screen, before and after). Claude: then build all of it the same day, with the tests and the canon row</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr"/>
-    </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Cash flow</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Two word collisions found building v08: Cash flow's 'Add by hand' adds an EXPENSE (the same words as the account door), and Settings still says 'Disconnect' beside 'Linked accounts'</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>Workplan</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>Two word collisions found building v08: Cash flow's 'Add by hand' adds</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>Status / Comments</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>Founder: say whether Cash flow's door should read differently (for example 'Add an expense by hand') and whether Disconnect becomes 'Unlink'.</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr"/>
-    </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>LAUNCH ANSWER LIST — 61 things need you for Net worth, Cash flow and Performance to be launch-ready</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>Workplan</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>LAUNCH ANSWER LIST — 61 things need you for Net worth, Cash flow and P</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>Status / Comments</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>His ask, 2026-09-29: ‘Give me a list of files, tabs, and rows I need to answer for NW, CF, Performance sections of the app to be complete.’ Open MoneyKeel/documents/other/moneykeel_calc_plan_launch-answer-list_v01.xlsx. Five tabs: Read me, EVERYTHING, and one per module. Every line names its FILE, i</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I21"/>
+  <autoFilter ref="A1:I14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1372,7 +1084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1381,7 +1093,7 @@
     <col width="51" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="52" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
     <col width="52" customWidth="1" min="8" max="8"/>
     <col width="40" customWidth="1" min="9" max="9"/>
   </cols>
@@ -1389,7 +1101,7 @@
     <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>7 things to answer for Net worth</t>
+          <t>4 things to answer for Net worth</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -1470,7 +1182,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Q34 — Approve the exact wording for the average-price rule (info dot + column Q): 'Shares with no recorded purchase price are left out of the average. N of your shares are in that position.' — and the refusal: 'Average not available — none of these shares has a recorded price.'</t>
+          <t>VERIFY 71 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1485,24 +1197,24 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-032 — Price paid (average)</t>
+          <t>all 71 unverified rows on this tab</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>YOUR ANSWER — use the same number</t>
+          <t>ROW VERIFIED — founder, date and how</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+          <t>The module cannot be called launch-ready: a TESTED row is proved to match the code, not proved to be right.</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr"/>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -1511,40 +1223,39 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Q35 — Approve the exact label and the canon phrase for the twelve-month window. Proposed: 'Dividends received (trailing twelve months)' here, and 'trailing twelve months' in the other four places (spelled out — no initialism).
-Q36 — Dividends on this card: THIS account only, matching 'Realized from sales' beside it? Recommended: yes.</t>
+          <t>Commit — the branch was 278 files behind on 2026-09-14; committed since: 983805a (catch-up), f0e1d6d (Net worth v08), c4f2679 (the Since crash), 727e22a (Performance v14). Nothing is pushed — the branch taxonomy-v1.0.7 is local only.</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>networth</t>
+          <t>Workplan</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-034 — Dividends received (12 mo)</t>
+          <t>Commit — the branch was 278 files behind on 2026-09-14; committed sinc</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>YOUR ANSWER — use the same number</t>
+          <t>Status / Comments</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>The figure stays DRAFT: it is declared and printed, and nothing moves behind its door until you rule.</t>
+          <t>Founder: say when to PUSH. (Note 2026-09-26: the Xcode licence has not been accepted on this Mac, so the normal git refuses to run — "sudo xcodebuild -license accept" once, then git works everywhere again.)</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="60" customHeight="1">
       <c r="A6" s="3" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -1553,39 +1264,39 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>VERIFY 65 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
+          <t>One door, one term: the three ways to add an account read 'Link it (read-only)', 'Add by hand' and 'Import from a file' on every screen, under the heading 'How do you want to add an account?' — Home, Sharpen your plan, the Plan tab, Net worth (first day and the add sheet), the Connect an account screen and Performance</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx</t>
+          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>networth</t>
+          <t>Workplan</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>all 65 unverified rows on this tab</t>
+          <t>One door, one term: the three ways to add an account read 'Link it (re</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>ROW VERIFIED — founder, date and how</t>
+          <t>Status / Comments</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>The module cannot be called launch-ready: a TESTED row is proved to match the code, not proved to be right.</t>
+          <t>Founder: approve the mock MoneyKeel/documents/home-screen/moneykeel_pres_mock_ways-to-add-an-account_v10.html (every affected screen, before and after). Claude: then build all of it the same day, with the tests and the canon row</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr"/>
     </row>
-    <row r="7" ht="30" customHeight="1">
+    <row r="7" ht="60" customHeight="1">
       <c r="A7" s="3" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
@@ -1594,161 +1305,38 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: what does screen look like for manual update?</t>
+          <t>LAUNCH ANSWER LIST — 61 things need you for Net worth, Cash flow and Performance to be launch-ready</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
+          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>networth</t>
+          <t>Workplan</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>DEC-0470</t>
+          <t>LAUNCH ANSWER LIST — 61 things need you for Net worth, Cash flow and P</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Open question on this decision — for him</t>
+          <t>Status / Comments</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
+          <t>His ask, 2026-09-29: ‘Give me a list of files, tabs, and rows I need to answer for NW, CF, Performance sections of the app to be complete.’ Open MoneyKeel/documents/other/moneykeel_calc_plan_launch-answer-list_v01.xlsx. Five tabs: Read me, EVERYTHING, and one per module. Every line names its FILE, i</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr"/>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Commit — the branch was 278 files behind on 2026-09-14; committed since: 983805a (catch-up), f0e1d6d (Net worth v08), c4f2679 (the Since crash), 727e22a (Performance v14). Nothing is pushed — the branch taxonomy-v1.0.7 is local only.</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>Workplan</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>Commit — the branch was 278 files behind on 2026-09-14; committed sinc</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>Status / Comments</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>Founder: say when to PUSH. (Note 2026-09-26: the Xcode licence has not been accepted on this Mac, so the normal git refuses to run — "sudo xcodebuild -license accept" once, then git works everywhere again.)</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr"/>
-    </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>One door, one term: the three ways to add an account read 'Link it (read-only)', 'Add by hand' and 'Import from a file' on every screen, under the heading 'How do you want to add an account?' — Home, Sharpen your plan, the Plan tab, Net worth (first day and the add sheet), the Connect an account screen and Performance</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>Workplan</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>One door, one term: the three ways to add an account read 'Link it (re</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>Status / Comments</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>Founder: approve the mock MoneyKeel/documents/home-screen/moneykeel_pres_mock_ways-to-add-an-account_v10.html (every affected screen, before and after). Claude: then build all of it the same day, with the tests and the canon row</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>LAUNCH ANSWER LIST — 61 things need you for Net worth, Cash flow and Performance to be launch-ready</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_plan_workplan_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>Workplan</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>LAUNCH ANSWER LIST — 61 things need you for Net worth, Cash flow and P</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>Status / Comments</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>His ask, 2026-09-29: ‘Give me a list of files, tabs, and rows I need to answer for NW, CF, Performance sections of the app to be complete.’ Open MoneyKeel/documents/other/moneykeel_calc_plan_launch-answer-list_v01.xlsx. Five tabs: Read me, EVERYTHING, and one per module. Every line names its FILE, i</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I10"/>
+  <autoFilter ref="A1:I7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1848,7 +1436,7 @@
     </row>
     <row r="4" ht="60" customHeight="1">
       <c r="A4" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
@@ -1889,7 +1477,7 @@
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="3" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -1930,7 +1518,7 @@
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="3" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -1971,7 +1559,7 @@
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="3" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
@@ -2012,7 +1600,7 @@
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="3" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
@@ -2053,7 +1641,7 @@
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="3" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
@@ -2104,7 +1692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -2113,7 +1701,7 @@
     <col width="51" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
     <col width="52" customWidth="1" min="8" max="8"/>
     <col width="40" customWidth="1" min="9" max="9"/>
   </cols>
@@ -2121,7 +1709,7 @@
     <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>5 things to answer for Performance</t>
+          <t>1 things to answer for Performance</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -2193,7 +1781,7 @@
     </row>
     <row r="4" ht="60" customHeight="1">
       <c r="A4" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
@@ -2202,7 +1790,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>VERIFY 21 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
+          <t>VERIFY 26 rows — read each row and mark it VERIFIED, or say what is wrong. Only your mark makes a row VERIFIED; my tests can say a figure is what the code gives, never that it is the figure you wanted.</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -2217,7 +1805,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>all 21 unverified rows on this tab</t>
+          <t>all 26 unverified rows on this tab</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -2232,172 +1820,8 @@
       </c>
       <c r="I4" s="3" t="inlineStr"/>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Total return captures both realized and unrealized gains? Is there any place we display realized P/L, unrealized P/L, total dividend, and total interest separately?</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>performance</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>DEC-0479</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>Open question on this decision — for him</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr"/>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: stocks with dividends - will it also show dividends received?</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>performance</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>DEC-0483</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>Open question on this decision — for him</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr"/>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: What's the level of details displayed and how?r</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>performance</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>DEC-0497</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>Open question on this decision — for him</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>A QUESTION YOU ASKED AND NOBODY ANSWERED: Invest: what level of detail, and how?</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>moneykeel_log_decisions_v01.xlsx</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>performance</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>DEC-0510</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>Open question on this decision — for him</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>It is not a decision until it is answered, so nothing can be built or tested against it.</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I8"/>
+  <autoFilter ref="A1:I4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>